--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326438</v>
+        <v>121326921</v>
       </c>
       <c r="B2" t="n">
-        <v>78335</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483043</v>
+        <v>483134</v>
       </c>
       <c r="R2" t="n">
-        <v>6834195</v>
+        <v>6833995</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326179</v>
+        <v>121326404</v>
       </c>
       <c r="B3" t="n">
-        <v>78335</v>
+        <v>78338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482925</v>
+        <v>483018</v>
       </c>
       <c r="R3" t="n">
-        <v>6834028</v>
+        <v>6834214</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326921</v>
+        <v>121326179</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483134</v>
+        <v>482925</v>
       </c>
       <c r="R4" t="n">
-        <v>6833995</v>
+        <v>6834028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>121326800</v>
       </c>
       <c r="B5" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>121326737</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>121326433</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326404</v>
+        <v>121326438</v>
       </c>
       <c r="B8" t="n">
-        <v>78335</v>
+        <v>78338</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483018</v>
+        <v>483043</v>
       </c>
       <c r="R8" t="n">
-        <v>6834214</v>
+        <v>6834195</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326921</v>
+        <v>121326179</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78338</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483134</v>
+        <v>482925</v>
       </c>
       <c r="R2" t="n">
-        <v>6833995</v>
+        <v>6834028</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326404</v>
+        <v>121326438</v>
       </c>
       <c r="B3" t="n">
         <v>78338</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483018</v>
+        <v>483043</v>
       </c>
       <c r="R3" t="n">
-        <v>6834214</v>
+        <v>6834195</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326179</v>
+        <v>121326433</v>
       </c>
       <c r="B4" t="n">
-        <v>78338</v>
+        <v>79190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482925</v>
+        <v>483040</v>
       </c>
       <c r="R4" t="n">
-        <v>6834028</v>
+        <v>6834198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326800</v>
+        <v>121326737</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483205</v>
+        <v>483242</v>
       </c>
       <c r="R5" t="n">
-        <v>6834165</v>
+        <v>6834570</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326737</v>
+        <v>121326404</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483242</v>
+        <v>483018</v>
       </c>
       <c r="R6" t="n">
-        <v>6834570</v>
+        <v>6834214</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326433</v>
+        <v>121326800</v>
       </c>
       <c r="B7" t="n">
-        <v>79190</v>
+        <v>78337</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483040</v>
+        <v>483205</v>
       </c>
       <c r="R7" t="n">
-        <v>6834198</v>
+        <v>6834165</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326438</v>
+        <v>121326921</v>
       </c>
       <c r="B8" t="n">
-        <v>78338</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483043</v>
+        <v>483134</v>
       </c>
       <c r="R8" t="n">
-        <v>6834195</v>
+        <v>6833995</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,6 +1387,9184 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121469108</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>482925</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6833910</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121469149</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483268</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6834459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121469119</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6834572</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121469110</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483144</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6833875</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121469350</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483033</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6834458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121469347</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483261</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6834535</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121469152</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>483169</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6834491</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121469155</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>482892</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6834282</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121469156</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>353</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>482876</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6834258</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121465246</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78337</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483187</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6833888</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121469133</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483241</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6834112</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121469348</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>483153</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6834505</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121469117</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>483119</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6834405</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121469100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483211</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6834254</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121469127</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483514</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6834064</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121469147</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>353</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483181</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6834299</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121469144</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>353</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483402</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6834000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121469124</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>482865</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6834254</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121469344</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>483119</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6834405</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121469101</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483168</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6834333</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121469069</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79193</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483031</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6834458</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121469120</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483153</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6834504</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121465664</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78337</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>483498</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6834031</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121465159</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78337</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483204</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6833925</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121465189</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78338</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483204</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6833925</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121469338</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>483246</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6834122</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121469349</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483065</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6834469</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121469097</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483408</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6833852</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121469140</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>483106</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6834495</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121469154</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>483081</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6834496</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121469341</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>483181</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6834299</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121465160</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>483115</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6833942</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121465556</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78338</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>483536</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6833990</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121467080</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>483038</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6834006</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121469134</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>483277</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6834451</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121469131</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>483261</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6834030</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121465604</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78337</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>483179</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6833973</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121469150</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>353</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>483294</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6834475</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121469335</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>483483</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6833854</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121469337</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>483413</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6834033</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121469340</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>483211</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6834254</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121469339</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>483213</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6834252</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121469342</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>483160</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6834377</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121469136</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>483198</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6834484</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121469343</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>483155</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6834382</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121469158</v>
+      </c>
+      <c r="B54" t="n">
+        <v>77988</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>482967</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6834339</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121469336</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>483492</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6834084</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121469146</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>353</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>483260</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6834060</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121469139</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>483149</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6834501</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121469115</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>483445</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6833857</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121469122</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>482967</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6834340</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121469102</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>483161</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6834377</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121469137</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>483198</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6834476</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121465615</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>483179</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6833973</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121467007</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>483082</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6834003</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121469145</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>353</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>483387</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6833994</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121469105</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>483153</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6834504</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121469148</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78249</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>353</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>483160</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6834438</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121469142</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>483076</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6834476</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121469098</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>483445</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6833857</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121469107</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>482865</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6834255</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121469132</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>483255</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6834077</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121469118</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>483210</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6834456</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121469103</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>483145</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6834394</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121469126</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>483476</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6834017</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>121469334</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>483084</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6833901</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>121465202</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78246</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>353</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>483084</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6833930</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121469071</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6834571</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121469112</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>483408</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6833852</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121469135</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>483205</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6834490</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121469125</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>483307</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6833983</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121469096</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>483058</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6833926</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121469130</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>483307</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6833983</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121469333</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>483059</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6833927</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121469114</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>483434</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6833855</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121469095</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>482925</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6833909</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>121469070</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79193</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>483031</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6834425</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121469143</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>483038</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6834461</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121465603</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78338</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>483561</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6833992</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121467022</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>483082</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6834003</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>121466253</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78338</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>483464</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6833910</v>
+      </c>
+      <c r="S89" t="n">
+        <v>20</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>121469116</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>483484</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6833901</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>121469099</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>483482</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6833855</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>121469157</v>
+      </c>
+      <c r="B92" t="n">
+        <v>77988</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>483143</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6833875</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121469128</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>483524</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6834071</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121469345</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>483210</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6834457</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121469106</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>482967</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6834340</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>121469351</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>482864</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6834255</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>121469104</v>
+      </c>
+      <c r="B97" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6834572</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326179</v>
+        <v>121326438</v>
       </c>
       <c r="B2" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482925</v>
+        <v>483043</v>
       </c>
       <c r="R2" t="n">
-        <v>6834028</v>
+        <v>6834195</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326438</v>
+        <v>121326433</v>
       </c>
       <c r="B3" t="n">
-        <v>78338</v>
+        <v>79193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483043</v>
+        <v>483040</v>
       </c>
       <c r="R3" t="n">
-        <v>6834195</v>
+        <v>6834198</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326433</v>
+        <v>121326737</v>
       </c>
       <c r="B4" t="n">
-        <v>79190</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483040</v>
+        <v>483242</v>
       </c>
       <c r="R4" t="n">
-        <v>6834198</v>
+        <v>6834570</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326737</v>
+        <v>121326404</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483242</v>
+        <v>483018</v>
       </c>
       <c r="R5" t="n">
-        <v>6834570</v>
+        <v>6834214</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326404</v>
+        <v>121326179</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483018</v>
+        <v>482925</v>
       </c>
       <c r="R6" t="n">
-        <v>6834214</v>
+        <v>6834028</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>121326800</v>
       </c>
       <c r="B7" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>121326921</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469108</v>
+        <v>121469342</v>
       </c>
       <c r="B9" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482925</v>
+        <v>483160</v>
       </c>
       <c r="R9" t="n">
-        <v>6833910</v>
+        <v>6834377</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469149</v>
+        <v>121469157</v>
       </c>
       <c r="B10" t="n">
-        <v>78249</v>
+        <v>77988</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483268</v>
+        <v>483143</v>
       </c>
       <c r="R10" t="n">
-        <v>6834459</v>
+        <v>6833875</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469119</v>
+        <v>121469158</v>
       </c>
       <c r="B11" t="n">
-        <v>78340</v>
+        <v>77988</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483265</v>
+        <v>482967</v>
       </c>
       <c r="R11" t="n">
-        <v>6834572</v>
+        <v>6834339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469110</v>
+        <v>121465556</v>
       </c>
       <c r="B12" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483144</v>
+        <v>483536</v>
       </c>
       <c r="R12" t="n">
-        <v>6833875</v>
+        <v>6833990</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469350</v>
+        <v>121469156</v>
       </c>
       <c r="B13" t="n">
-        <v>79222</v>
+        <v>78249</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483033</v>
+        <v>482876</v>
       </c>
       <c r="R13" t="n">
-        <v>6834458</v>
+        <v>6834258</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469347</v>
+        <v>121469101</v>
       </c>
       <c r="B14" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483261</v>
+        <v>483168</v>
       </c>
       <c r="R14" t="n">
-        <v>6834535</v>
+        <v>6834333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469152</v>
+        <v>121469095</v>
       </c>
       <c r="B15" t="n">
-        <v>78249</v>
+        <v>78341</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483169</v>
+        <v>482925</v>
       </c>
       <c r="R15" t="n">
-        <v>6834491</v>
+        <v>6833909</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469155</v>
+        <v>121469146</v>
       </c>
       <c r="B16" t="n">
         <v>78249</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482892</v>
+        <v>483260</v>
       </c>
       <c r="R16" t="n">
-        <v>6834282</v>
+        <v>6834060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469156</v>
+        <v>121469135</v>
       </c>
       <c r="B17" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482876</v>
+        <v>483205</v>
       </c>
       <c r="R17" t="n">
-        <v>6834258</v>
+        <v>6834490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121465246</v>
+        <v>121469137</v>
       </c>
       <c r="B18" t="n">
-        <v>78337</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,37 +2323,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483187</v>
+        <v>483198</v>
       </c>
       <c r="R18" t="n">
-        <v>6833888</v>
+        <v>6834476</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,19 +2380,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469133</v>
+        <v>121469347</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483241</v>
+        <v>483261</v>
       </c>
       <c r="R19" t="n">
-        <v>6834112</v>
+        <v>6834535</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469348</v>
+        <v>121469335</v>
       </c>
       <c r="B20" t="n">
         <v>79222</v>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483153</v>
+        <v>483483</v>
       </c>
       <c r="R20" t="n">
-        <v>6834505</v>
+        <v>6833854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469117</v>
+        <v>121469344</v>
       </c>
       <c r="B21" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469100</v>
+        <v>121469339</v>
       </c>
       <c r="B22" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483211</v>
+        <v>483213</v>
       </c>
       <c r="R22" t="n">
-        <v>6834254</v>
+        <v>6834252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469127</v>
+        <v>121469114</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483514</v>
+        <v>483434</v>
       </c>
       <c r="R23" t="n">
-        <v>6834064</v>
+        <v>6833855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469147</v>
+        <v>121469128</v>
       </c>
       <c r="B24" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483181</v>
+        <v>483524</v>
       </c>
       <c r="R24" t="n">
-        <v>6834299</v>
+        <v>6834071</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469144</v>
+        <v>121469124</v>
       </c>
       <c r="B25" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483402</v>
+        <v>482865</v>
       </c>
       <c r="R25" t="n">
-        <v>6834000</v>
+        <v>6834254</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469124</v>
+        <v>121469071</v>
       </c>
       <c r="B26" t="n">
-        <v>78340</v>
+        <v>57504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482865</v>
+        <v>483265</v>
       </c>
       <c r="R26" t="n">
-        <v>6834254</v>
+        <v>6834571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469344</v>
+        <v>121469338</v>
       </c>
       <c r="B27" t="n">
         <v>79222</v>
@@ -3275,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483119</v>
+        <v>483246</v>
       </c>
       <c r="R27" t="n">
-        <v>6834405</v>
+        <v>6834122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469101</v>
+        <v>121465189</v>
       </c>
       <c r="B28" t="n">
         <v>78341</v>
@@ -3373,17 +3363,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483168</v>
+        <v>483204</v>
       </c>
       <c r="R28" t="n">
-        <v>6834333</v>
+        <v>6833925</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3410,9 +3400,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469069</v>
+        <v>121469132</v>
       </c>
       <c r="B29" t="n">
-        <v>79193</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483031</v>
+        <v>483255</v>
       </c>
       <c r="R29" t="n">
-        <v>6834458</v>
+        <v>6834077</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469120</v>
+        <v>121469134</v>
       </c>
       <c r="B30" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483153</v>
+        <v>483277</v>
       </c>
       <c r="R30" t="n">
-        <v>6834504</v>
+        <v>6834451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121465664</v>
+        <v>121469142</v>
       </c>
       <c r="B31" t="n">
-        <v>78337</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,37 +3659,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483498</v>
+        <v>483076</v>
       </c>
       <c r="R31" t="n">
-        <v>6834031</v>
+        <v>6834476</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3733,22 +3733,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121465159</v>
+        <v>121469333</v>
       </c>
       <c r="B32" t="n">
-        <v>78337</v>
+        <v>79222</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,37 +3761,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483204</v>
+        <v>483059</v>
       </c>
       <c r="R32" t="n">
-        <v>6833925</v>
+        <v>6833927</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3818,19 +3818,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3845,22 +3835,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121465189</v>
+        <v>121469126</v>
       </c>
       <c r="B33" t="n">
-        <v>78338</v>
+        <v>78604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,37 +3863,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483204</v>
+        <v>483476</v>
       </c>
       <c r="R33" t="n">
-        <v>6833925</v>
+        <v>6834017</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3930,19 +3920,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3957,22 +3937,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469338</v>
+        <v>121469107</v>
       </c>
       <c r="B34" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3985,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483246</v>
+        <v>482865</v>
       </c>
       <c r="R34" t="n">
-        <v>6834122</v>
+        <v>6834255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469349</v>
+        <v>121467007</v>
       </c>
       <c r="B35" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4067,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,13 +4091,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483065</v>
+        <v>483082</v>
       </c>
       <c r="R35" t="n">
-        <v>6834469</v>
+        <v>6834003</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4144,9 +4124,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4161,22 +4151,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469097</v>
+        <v>121469343</v>
       </c>
       <c r="B36" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483408</v>
+        <v>483155</v>
       </c>
       <c r="R36" t="n">
-        <v>6833852</v>
+        <v>6834382</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469140</v>
+        <v>121469341</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483106</v>
+        <v>483181</v>
       </c>
       <c r="R37" t="n">
-        <v>6834495</v>
+        <v>6834299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469154</v>
+        <v>121469115</v>
       </c>
       <c r="B38" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483081</v>
+        <v>483445</v>
       </c>
       <c r="R38" t="n">
-        <v>6834496</v>
+        <v>6833857</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469341</v>
+        <v>121469130</v>
       </c>
       <c r="B39" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4519,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483181</v>
+        <v>483307</v>
       </c>
       <c r="R39" t="n">
-        <v>6834299</v>
+        <v>6833983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121465160</v>
+        <v>121469096</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>78341</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,13 +4611,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483115</v>
+        <v>483058</v>
       </c>
       <c r="R40" t="n">
-        <v>6833942</v>
+        <v>6833926</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4654,19 +4644,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4681,22 +4661,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121465556</v>
+        <v>121469139</v>
       </c>
       <c r="B41" t="n">
-        <v>78338</v>
+        <v>78604</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4709,37 +4689,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483536</v>
+        <v>483149</v>
       </c>
       <c r="R41" t="n">
-        <v>6833990</v>
+        <v>6834501</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4783,22 +4763,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121467080</v>
+        <v>121469345</v>
       </c>
       <c r="B42" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,37 +4791,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483038</v>
+        <v>483210</v>
       </c>
       <c r="R42" t="n">
-        <v>6834006</v>
+        <v>6834457</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4885,22 +4865,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469134</v>
+        <v>121469350</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4893,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483277</v>
+        <v>483033</v>
       </c>
       <c r="R43" t="n">
-        <v>6834451</v>
+        <v>6834458</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469131</v>
+        <v>121469152</v>
       </c>
       <c r="B44" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483261</v>
+        <v>483169</v>
       </c>
       <c r="R44" t="n">
-        <v>6834030</v>
+        <v>6834491</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121465604</v>
+        <v>121469122</v>
       </c>
       <c r="B45" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5137,17 +5117,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483179</v>
+        <v>482967</v>
       </c>
       <c r="R45" t="n">
-        <v>6833973</v>
+        <v>6834340</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5174,19 +5154,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5201,22 +5171,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469150</v>
+        <v>121469112</v>
       </c>
       <c r="B46" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5229,21 +5199,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5253,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483294</v>
+        <v>483408</v>
       </c>
       <c r="R46" t="n">
-        <v>6834475</v>
+        <v>6833852</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469335</v>
+        <v>121469103</v>
       </c>
       <c r="B47" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,21 +5301,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5355,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483483</v>
+        <v>483145</v>
       </c>
       <c r="R47" t="n">
-        <v>6833854</v>
+        <v>6834394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469337</v>
+        <v>121469118</v>
       </c>
       <c r="B48" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,21 +5403,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5457,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483413</v>
+        <v>483210</v>
       </c>
       <c r="R48" t="n">
-        <v>6834033</v>
+        <v>6834456</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469340</v>
+        <v>121469140</v>
       </c>
       <c r="B49" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483211</v>
+        <v>483106</v>
       </c>
       <c r="R49" t="n">
-        <v>6834254</v>
+        <v>6834495</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469339</v>
+        <v>121469069</v>
       </c>
       <c r="B50" t="n">
-        <v>79222</v>
+        <v>79193</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483213</v>
+        <v>483031</v>
       </c>
       <c r="R50" t="n">
-        <v>6834252</v>
+        <v>6834458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469342</v>
+        <v>121469108</v>
       </c>
       <c r="B51" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483160</v>
+        <v>482925</v>
       </c>
       <c r="R51" t="n">
-        <v>6834377</v>
+        <v>6833910</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469136</v>
+        <v>121466253</v>
       </c>
       <c r="B52" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,37 +5811,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483198</v>
+        <v>483464</v>
       </c>
       <c r="R52" t="n">
-        <v>6834484</v>
+        <v>6833910</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5915,19 +5885,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469343</v>
+        <v>121469351</v>
       </c>
       <c r="B53" t="n">
         <v>79222</v>
@@ -5967,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483155</v>
+        <v>482864</v>
       </c>
       <c r="R53" t="n">
-        <v>6834382</v>
+        <v>6834255</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469158</v>
+        <v>121465246</v>
       </c>
       <c r="B54" t="n">
-        <v>77988</v>
+        <v>78340</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,37 +6015,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>482967</v>
+        <v>483187</v>
       </c>
       <c r="R54" t="n">
-        <v>6834339</v>
+        <v>6833888</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6102,9 +6072,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6119,22 +6099,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469336</v>
+        <v>121465159</v>
       </c>
       <c r="B55" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,37 +6127,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483492</v>
+        <v>483204</v>
       </c>
       <c r="R55" t="n">
-        <v>6834084</v>
+        <v>6833925</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6204,9 +6184,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6221,22 +6211,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469146</v>
+        <v>121469120</v>
       </c>
       <c r="B56" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6239,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483260</v>
+        <v>483153</v>
       </c>
       <c r="R56" t="n">
-        <v>6834060</v>
+        <v>6834504</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469139</v>
+        <v>121469155</v>
       </c>
       <c r="B57" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,21 +6341,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483149</v>
+        <v>482892</v>
       </c>
       <c r="R57" t="n">
-        <v>6834501</v>
+        <v>6834282</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6437,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469115</v>
+        <v>121469097</v>
       </c>
       <c r="B58" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,21 +6443,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6477,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483445</v>
+        <v>483408</v>
       </c>
       <c r="R58" t="n">
-        <v>6833857</v>
+        <v>6833852</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6539,7 +6529,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469122</v>
+        <v>121465604</v>
       </c>
       <c r="B59" t="n">
         <v>78340</v>
@@ -6575,17 +6565,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>482967</v>
+        <v>483179</v>
       </c>
       <c r="R59" t="n">
-        <v>6834340</v>
+        <v>6833973</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6612,9 +6602,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6629,19 +6629,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469102</v>
+        <v>121469100</v>
       </c>
       <c r="B60" t="n">
         <v>78341</v>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483161</v>
+        <v>483211</v>
       </c>
       <c r="R60" t="n">
-        <v>6834377</v>
+        <v>6834254</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469137</v>
+        <v>121469145</v>
       </c>
       <c r="B61" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,21 +6759,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6783,10 +6783,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483198</v>
+        <v>483387</v>
       </c>
       <c r="R61" t="n">
-        <v>6834476</v>
+        <v>6833994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121465615</v>
+        <v>121469334</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>79222</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6861,34 +6861,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483179</v>
+        <v>483084</v>
       </c>
       <c r="R62" t="n">
-        <v>6833973</v>
+        <v>6833901</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6918,19 +6918,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6945,22 +6935,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121467007</v>
+        <v>121469127</v>
       </c>
       <c r="B63" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6973,21 +6963,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6997,13 +6987,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483082</v>
+        <v>483514</v>
       </c>
       <c r="R63" t="n">
-        <v>6834003</v>
+        <v>6834064</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7030,19 +7020,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7057,22 +7037,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469145</v>
+        <v>121465615</v>
       </c>
       <c r="B64" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,34 +7065,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483387</v>
+        <v>483179</v>
       </c>
       <c r="R64" t="n">
-        <v>6833994</v>
+        <v>6833973</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7142,9 +7122,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7159,22 +7149,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469105</v>
+        <v>121469336</v>
       </c>
       <c r="B65" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7177,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483153</v>
+        <v>483492</v>
       </c>
       <c r="R65" t="n">
-        <v>6834504</v>
+        <v>6834084</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469148</v>
+        <v>121469104</v>
       </c>
       <c r="B66" t="n">
-        <v>78249</v>
+        <v>78341</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7279,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7303,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483160</v>
+        <v>483265</v>
       </c>
       <c r="R66" t="n">
-        <v>6834438</v>
+        <v>6834572</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7365,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469142</v>
+        <v>121469098</v>
       </c>
       <c r="B67" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7381,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483076</v>
+        <v>483445</v>
       </c>
       <c r="R67" t="n">
-        <v>6834476</v>
+        <v>6833857</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,7 +7467,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469098</v>
+        <v>121469102</v>
       </c>
       <c r="B68" t="n">
         <v>78341</v>
@@ -7517,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483445</v>
+        <v>483161</v>
       </c>
       <c r="R68" t="n">
-        <v>6833857</v>
+        <v>6834377</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469107</v>
+        <v>121469125</v>
       </c>
       <c r="B69" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7595,21 +7585,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7619,10 +7609,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>482865</v>
+        <v>483307</v>
       </c>
       <c r="R69" t="n">
-        <v>6834255</v>
+        <v>6833983</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7671,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469132</v>
+        <v>121465603</v>
       </c>
       <c r="B70" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7697,37 +7687,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483255</v>
+        <v>483561</v>
       </c>
       <c r="R70" t="n">
-        <v>6834077</v>
+        <v>6833992</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7754,9 +7744,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7771,22 +7771,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469118</v>
+        <v>121469136</v>
       </c>
       <c r="B71" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7799,21 +7799,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483210</v>
+        <v>483198</v>
       </c>
       <c r="R71" t="n">
-        <v>6834456</v>
+        <v>6834484</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,7 +7885,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469103</v>
+        <v>121469106</v>
       </c>
       <c r="B72" t="n">
         <v>78341</v>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483145</v>
+        <v>482967</v>
       </c>
       <c r="R72" t="n">
-        <v>6834394</v>
+        <v>6834340</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469126</v>
+        <v>121469149</v>
       </c>
       <c r="B73" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483476</v>
+        <v>483268</v>
       </c>
       <c r="R73" t="n">
-        <v>6834017</v>
+        <v>6834459</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469334</v>
+        <v>121469150</v>
       </c>
       <c r="B74" t="n">
-        <v>79222</v>
+        <v>78249</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8105,21 +8105,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483084</v>
+        <v>483294</v>
       </c>
       <c r="R74" t="n">
-        <v>6833901</v>
+        <v>6834475</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,10 +8191,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121465202</v>
+        <v>121469117</v>
       </c>
       <c r="B75" t="n">
-        <v>78246</v>
+        <v>78340</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,37 +8207,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483084</v>
+        <v>483119</v>
       </c>
       <c r="R75" t="n">
-        <v>6833930</v>
+        <v>6834405</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8264,19 +8264,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8291,22 +8281,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469071</v>
+        <v>121469148</v>
       </c>
       <c r="B76" t="n">
-        <v>57504</v>
+        <v>78249</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483265</v>
+        <v>483160</v>
       </c>
       <c r="R76" t="n">
-        <v>6834571</v>
+        <v>6834438</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,10 +8395,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469112</v>
+        <v>121469144</v>
       </c>
       <c r="B77" t="n">
-        <v>78340</v>
+        <v>78249</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8421,21 +8411,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8445,10 +8435,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483408</v>
+        <v>483402</v>
       </c>
       <c r="R77" t="n">
-        <v>6833852</v>
+        <v>6834000</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8497,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469135</v>
+        <v>121469070</v>
       </c>
       <c r="B78" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8523,21 +8513,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8547,10 +8537,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483205</v>
+        <v>483031</v>
       </c>
       <c r="R78" t="n">
-        <v>6834490</v>
+        <v>6834425</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8609,10 +8599,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469125</v>
+        <v>121465160</v>
       </c>
       <c r="B79" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8625,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,13 +8639,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483307</v>
+        <v>483115</v>
       </c>
       <c r="R79" t="n">
-        <v>6833983</v>
+        <v>6833942</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8682,9 +8672,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8699,22 +8699,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469096</v>
+        <v>121467022</v>
       </c>
       <c r="B80" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8727,21 +8727,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483058</v>
+        <v>483082</v>
       </c>
       <c r="R80" t="n">
-        <v>6833926</v>
+        <v>6834003</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8784,9 +8784,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8801,22 +8811,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469130</v>
+        <v>121469116</v>
       </c>
       <c r="B81" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8829,21 +8839,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8853,10 +8863,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483307</v>
+        <v>483484</v>
       </c>
       <c r="R81" t="n">
-        <v>6833983</v>
+        <v>6833901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8915,7 +8925,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469333</v>
+        <v>121469348</v>
       </c>
       <c r="B82" t="n">
         <v>79222</v>
@@ -8955,10 +8965,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483059</v>
+        <v>483153</v>
       </c>
       <c r="R82" t="n">
-        <v>6833927</v>
+        <v>6834505</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9017,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469114</v>
+        <v>121469340</v>
       </c>
       <c r="B83" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9033,21 +9043,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9057,10 +9067,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483434</v>
+        <v>483211</v>
       </c>
       <c r="R83" t="n">
-        <v>6833855</v>
+        <v>6834254</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9119,10 +9129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469095</v>
+        <v>121465202</v>
       </c>
       <c r="B84" t="n">
-        <v>78341</v>
+        <v>78249</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9135,37 +9145,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>482925</v>
+        <v>483084</v>
       </c>
       <c r="R84" t="n">
-        <v>6833909</v>
+        <v>6833930</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9192,9 +9202,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9209,22 +9229,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469070</v>
+        <v>121467080</v>
       </c>
       <c r="B85" t="n">
-        <v>79193</v>
+        <v>78341</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9237,37 +9257,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483031</v>
+        <v>483038</v>
       </c>
       <c r="R85" t="n">
-        <v>6834425</v>
+        <v>6834006</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9311,12 +9331,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9425,10 +9445,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121465603</v>
+        <v>121469131</v>
       </c>
       <c r="B87" t="n">
-        <v>78338</v>
+        <v>78604</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9441,37 +9461,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483561</v>
+        <v>483261</v>
       </c>
       <c r="R87" t="n">
-        <v>6833992</v>
+        <v>6834030</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9498,19 +9518,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9525,19 +9535,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121467022</v>
+        <v>121469119</v>
       </c>
       <c r="B88" t="n">
         <v>78340</v>
@@ -9577,13 +9587,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483082</v>
+        <v>483265</v>
       </c>
       <c r="R88" t="n">
-        <v>6834003</v>
+        <v>6834572</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9610,19 +9620,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9637,22 +9637,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121466253</v>
+        <v>121469133</v>
       </c>
       <c r="B89" t="n">
-        <v>78338</v>
+        <v>78604</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9665,37 +9665,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483464</v>
+        <v>483241</v>
       </c>
       <c r="R89" t="n">
-        <v>6833910</v>
+        <v>6834112</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9739,22 +9739,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469116</v>
+        <v>121469154</v>
       </c>
       <c r="B90" t="n">
-        <v>78340</v>
+        <v>78249</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483484</v>
+        <v>483081</v>
       </c>
       <c r="R90" t="n">
-        <v>6833901</v>
+        <v>6834496</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9853,10 +9853,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469099</v>
+        <v>121465664</v>
       </c>
       <c r="B91" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9869,37 +9869,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483482</v>
+        <v>483498</v>
       </c>
       <c r="R91" t="n">
-        <v>6833855</v>
+        <v>6834031</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9943,22 +9943,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469157</v>
+        <v>121469147</v>
       </c>
       <c r="B92" t="n">
-        <v>77988</v>
+        <v>78249</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483143</v>
+        <v>483181</v>
       </c>
       <c r="R92" t="n">
-        <v>6833875</v>
+        <v>6834299</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10057,10 +10057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469128</v>
+        <v>121469337</v>
       </c>
       <c r="B93" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10073,21 +10073,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10097,10 +10097,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483524</v>
+        <v>483413</v>
       </c>
       <c r="R93" t="n">
-        <v>6834071</v>
+        <v>6834033</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10159,7 +10159,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469345</v>
+        <v>121469349</v>
       </c>
       <c r="B94" t="n">
         <v>79222</v>
@@ -10199,10 +10199,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483210</v>
+        <v>483065</v>
       </c>
       <c r="R94" t="n">
-        <v>6834457</v>
+        <v>6834469</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469106</v>
+        <v>121469110</v>
       </c>
       <c r="B95" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,21 +10277,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>482967</v>
+        <v>483144</v>
       </c>
       <c r="R95" t="n">
-        <v>6834340</v>
+        <v>6833875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10363,10 +10363,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469351</v>
+        <v>121469105</v>
       </c>
       <c r="B96" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482864</v>
+        <v>483153</v>
       </c>
       <c r="R96" t="n">
-        <v>6834255</v>
+        <v>6834504</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10465,7 +10465,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469104</v>
+        <v>121469099</v>
       </c>
       <c r="B97" t="n">
         <v>78341</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483265</v>
+        <v>483482</v>
       </c>
       <c r="R97" t="n">
-        <v>6834572</v>
+        <v>6833855</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10564,6 +10564,1238 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>121465024</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>482987</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6833950</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>121465991</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79714</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>483306</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6834009</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>121465412</v>
+      </c>
+      <c r="B100" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>483177</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6833971</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>121465017</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>482987</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6833950</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>121466059</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>483350</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6834071</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>121464931</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>482985</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6833943</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>121466096</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>483350</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6834071</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>121465052</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>482987</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6833950</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>121465234</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>483201</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6833961</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>121465266</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79193</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>483204</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6833967</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>121465426</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>483209</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6833990</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326433</v>
+        <v>121326737</v>
       </c>
       <c r="B3" t="n">
-        <v>79193</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483040</v>
+        <v>483242</v>
       </c>
       <c r="R3" t="n">
-        <v>6834198</v>
+        <v>6834570</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326737</v>
+        <v>121326179</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483242</v>
+        <v>482925</v>
       </c>
       <c r="R4" t="n">
-        <v>6834570</v>
+        <v>6834028</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326404</v>
+        <v>121326921</v>
       </c>
       <c r="B5" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483018</v>
+        <v>483134</v>
       </c>
       <c r="R5" t="n">
-        <v>6834214</v>
+        <v>6833995</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326179</v>
+        <v>121326404</v>
       </c>
       <c r="B6" t="n">
         <v>78341</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482925</v>
+        <v>483018</v>
       </c>
       <c r="R6" t="n">
-        <v>6834028</v>
+        <v>6834214</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326800</v>
+        <v>121326433</v>
       </c>
       <c r="B7" t="n">
-        <v>78340</v>
+        <v>79193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483205</v>
+        <v>483040</v>
       </c>
       <c r="R7" t="n">
-        <v>6834165</v>
+        <v>6834198</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326921</v>
+        <v>121326800</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483134</v>
+        <v>483205</v>
       </c>
       <c r="R8" t="n">
-        <v>6833995</v>
+        <v>6834165</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469342</v>
+        <v>121469130</v>
       </c>
       <c r="B9" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483160</v>
+        <v>483307</v>
       </c>
       <c r="R9" t="n">
-        <v>6834377</v>
+        <v>6833983</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469157</v>
+        <v>121469124</v>
       </c>
       <c r="B10" t="n">
-        <v>77988</v>
+        <v>78340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483143</v>
+        <v>482865</v>
       </c>
       <c r="R10" t="n">
-        <v>6833875</v>
+        <v>6834254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469158</v>
+        <v>121469136</v>
       </c>
       <c r="B11" t="n">
-        <v>77988</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482967</v>
+        <v>483198</v>
       </c>
       <c r="R11" t="n">
-        <v>6834339</v>
+        <v>6834484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121465556</v>
+        <v>121469145</v>
       </c>
       <c r="B12" t="n">
-        <v>78341</v>
+        <v>78249</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483536</v>
+        <v>483387</v>
       </c>
       <c r="R12" t="n">
-        <v>6833990</v>
+        <v>6833994</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469156</v>
+        <v>121469098</v>
       </c>
       <c r="B13" t="n">
-        <v>78249</v>
+        <v>78341</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482876</v>
+        <v>483445</v>
       </c>
       <c r="R13" t="n">
-        <v>6834258</v>
+        <v>6833857</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469101</v>
+        <v>121469349</v>
       </c>
       <c r="B14" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483168</v>
+        <v>483065</v>
       </c>
       <c r="R14" t="n">
-        <v>6834333</v>
+        <v>6834469</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469095</v>
+        <v>121469146</v>
       </c>
       <c r="B15" t="n">
-        <v>78341</v>
+        <v>78249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482925</v>
+        <v>483260</v>
       </c>
       <c r="R15" t="n">
-        <v>6833909</v>
+        <v>6834060</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469146</v>
+        <v>121469096</v>
       </c>
       <c r="B16" t="n">
-        <v>78249</v>
+        <v>78341</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483260</v>
+        <v>483058</v>
       </c>
       <c r="R16" t="n">
-        <v>6834060</v>
+        <v>6833926</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469135</v>
+        <v>121466253</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,37 +2221,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483205</v>
+        <v>483464</v>
       </c>
       <c r="R17" t="n">
-        <v>6834490</v>
+        <v>6833910</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,22 +2295,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469137</v>
+        <v>121469347</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483198</v>
+        <v>483261</v>
       </c>
       <c r="R18" t="n">
-        <v>6834476</v>
+        <v>6834535</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469347</v>
+        <v>121469342</v>
       </c>
       <c r="B19" t="n">
         <v>79222</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483261</v>
+        <v>483160</v>
       </c>
       <c r="R19" t="n">
-        <v>6834535</v>
+        <v>6834377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469335</v>
+        <v>121469334</v>
       </c>
       <c r="B20" t="n">
         <v>79222</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483483</v>
+        <v>483084</v>
       </c>
       <c r="R20" t="n">
-        <v>6833854</v>
+        <v>6833901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469344</v>
+        <v>121469110</v>
       </c>
       <c r="B21" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483119</v>
+        <v>483144</v>
       </c>
       <c r="R21" t="n">
-        <v>6834405</v>
+        <v>6833875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469339</v>
+        <v>121469118</v>
       </c>
       <c r="B22" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483213</v>
+        <v>483210</v>
       </c>
       <c r="R22" t="n">
-        <v>6834252</v>
+        <v>6834456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469114</v>
+        <v>121469155</v>
       </c>
       <c r="B23" t="n">
-        <v>78340</v>
+        <v>78249</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483434</v>
+        <v>482892</v>
       </c>
       <c r="R23" t="n">
-        <v>6833855</v>
+        <v>6834282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469128</v>
+        <v>121469117</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483524</v>
+        <v>483119</v>
       </c>
       <c r="R24" t="n">
-        <v>6834071</v>
+        <v>6834405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469124</v>
+        <v>121465664</v>
       </c>
       <c r="B25" t="n">
         <v>78340</v>
@@ -3057,17 +3057,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482865</v>
+        <v>483498</v>
       </c>
       <c r="R25" t="n">
-        <v>6834254</v>
+        <v>6834031</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3111,22 +3111,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469071</v>
+        <v>121469147</v>
       </c>
       <c r="B26" t="n">
-        <v>57504</v>
+        <v>78249</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483265</v>
+        <v>483181</v>
       </c>
       <c r="R26" t="n">
-        <v>6834571</v>
+        <v>6834299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469338</v>
+        <v>121469127</v>
       </c>
       <c r="B27" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483246</v>
+        <v>483514</v>
       </c>
       <c r="R27" t="n">
-        <v>6834122</v>
+        <v>6834064</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121465189</v>
+        <v>121465615</v>
       </c>
       <c r="B28" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483204</v>
+        <v>483179</v>
       </c>
       <c r="R28" t="n">
-        <v>6833925</v>
+        <v>6833973</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469132</v>
+        <v>121467007</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483255</v>
+        <v>483082</v>
       </c>
       <c r="R29" t="n">
-        <v>6834077</v>
+        <v>6834003</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3512,9 +3512,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3529,22 +3539,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469134</v>
+        <v>121469107</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483277</v>
+        <v>482865</v>
       </c>
       <c r="R30" t="n">
-        <v>6834451</v>
+        <v>6834255</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469142</v>
+        <v>121469144</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483076</v>
+        <v>483402</v>
       </c>
       <c r="R31" t="n">
-        <v>6834476</v>
+        <v>6834000</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469333</v>
+        <v>121469115</v>
       </c>
       <c r="B32" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483059</v>
+        <v>483445</v>
       </c>
       <c r="R32" t="n">
-        <v>6833927</v>
+        <v>6833857</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3857,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469126</v>
+        <v>121469128</v>
       </c>
       <c r="B33" t="n">
         <v>78604</v>
@@ -3887,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483476</v>
+        <v>483524</v>
       </c>
       <c r="R33" t="n">
-        <v>6834017</v>
+        <v>6834071</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,7 +3959,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469107</v>
+        <v>121469106</v>
       </c>
       <c r="B34" t="n">
         <v>78341</v>
@@ -3989,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>482865</v>
+        <v>482967</v>
       </c>
       <c r="R34" t="n">
-        <v>6834255</v>
+        <v>6834340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121467007</v>
+        <v>121469156</v>
       </c>
       <c r="B35" t="n">
-        <v>78341</v>
+        <v>78249</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,13 +4101,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483082</v>
+        <v>482876</v>
       </c>
       <c r="R35" t="n">
-        <v>6834003</v>
+        <v>6834258</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4124,19 +4134,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4151,19 +4151,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469343</v>
+        <v>121469336</v>
       </c>
       <c r="B36" t="n">
         <v>79222</v>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483155</v>
+        <v>483492</v>
       </c>
       <c r="R36" t="n">
-        <v>6834382</v>
+        <v>6834084</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469341</v>
+        <v>121469348</v>
       </c>
       <c r="B37" t="n">
         <v>79222</v>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483181</v>
+        <v>483153</v>
       </c>
       <c r="R37" t="n">
-        <v>6834299</v>
+        <v>6834505</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469115</v>
+        <v>121469097</v>
       </c>
       <c r="B38" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483445</v>
+        <v>483408</v>
       </c>
       <c r="R38" t="n">
-        <v>6833857</v>
+        <v>6833852</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469130</v>
+        <v>121465160</v>
       </c>
       <c r="B39" t="n">
         <v>78604</v>
@@ -4509,13 +4509,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483307</v>
+        <v>483115</v>
       </c>
       <c r="R39" t="n">
-        <v>6833983</v>
+        <v>6833942</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4542,9 +4542,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,22 +4569,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469096</v>
+        <v>121469116</v>
       </c>
       <c r="B40" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483058</v>
+        <v>483484</v>
       </c>
       <c r="R40" t="n">
-        <v>6833926</v>
+        <v>6833901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469139</v>
+        <v>121469112</v>
       </c>
       <c r="B41" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,21 +4699,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483149</v>
+        <v>483408</v>
       </c>
       <c r="R41" t="n">
-        <v>6834501</v>
+        <v>6833852</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,7 +4785,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469345</v>
+        <v>121469339</v>
       </c>
       <c r="B42" t="n">
         <v>79222</v>
@@ -4815,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483210</v>
+        <v>483213</v>
       </c>
       <c r="R42" t="n">
-        <v>6834457</v>
+        <v>6834252</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469350</v>
+        <v>121469105</v>
       </c>
       <c r="B43" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,21 +4903,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483033</v>
+        <v>483153</v>
       </c>
       <c r="R43" t="n">
-        <v>6834458</v>
+        <v>6834504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469152</v>
+        <v>121469157</v>
       </c>
       <c r="B44" t="n">
-        <v>78249</v>
+        <v>77988</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483169</v>
+        <v>483143</v>
       </c>
       <c r="R44" t="n">
-        <v>6834491</v>
+        <v>6833875</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469122</v>
+        <v>121465189</v>
       </c>
       <c r="B45" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,37 +5107,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482967</v>
+        <v>483204</v>
       </c>
       <c r="R45" t="n">
-        <v>6834340</v>
+        <v>6833925</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5154,9 +5164,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,22 +5191,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469112</v>
+        <v>121469333</v>
       </c>
       <c r="B46" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483408</v>
+        <v>483059</v>
       </c>
       <c r="R46" t="n">
-        <v>6833852</v>
+        <v>6833927</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469103</v>
+        <v>121469345</v>
       </c>
       <c r="B47" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483145</v>
+        <v>483210</v>
       </c>
       <c r="R47" t="n">
-        <v>6834394</v>
+        <v>6834457</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469118</v>
+        <v>121469350</v>
       </c>
       <c r="B48" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483210</v>
+        <v>483033</v>
       </c>
       <c r="R48" t="n">
-        <v>6834456</v>
+        <v>6834458</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469140</v>
+        <v>121469119</v>
       </c>
       <c r="B49" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5525,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483106</v>
+        <v>483265</v>
       </c>
       <c r="R49" t="n">
-        <v>6834495</v>
+        <v>6834572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469069</v>
+        <v>121469133</v>
       </c>
       <c r="B50" t="n">
-        <v>79193</v>
+        <v>78604</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5627,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5651,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483031</v>
+        <v>483241</v>
       </c>
       <c r="R50" t="n">
-        <v>6834458</v>
+        <v>6834112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5713,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469108</v>
+        <v>121469071</v>
       </c>
       <c r="B51" t="n">
-        <v>78340</v>
+        <v>57504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5729,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>482925</v>
+        <v>483265</v>
       </c>
       <c r="R51" t="n">
-        <v>6833910</v>
+        <v>6834571</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,7 +5815,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121466253</v>
+        <v>121469101</v>
       </c>
       <c r="B52" t="n">
         <v>78341</v>
@@ -5831,17 +5851,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483464</v>
+        <v>483168</v>
       </c>
       <c r="R52" t="n">
-        <v>6833910</v>
+        <v>6834333</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5885,22 +5905,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469351</v>
+        <v>121469103</v>
       </c>
       <c r="B53" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5933,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5957,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>482864</v>
+        <v>483145</v>
       </c>
       <c r="R53" t="n">
-        <v>6834255</v>
+        <v>6834394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +6019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121465246</v>
+        <v>121469351</v>
       </c>
       <c r="B54" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,37 +6035,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483187</v>
+        <v>482864</v>
       </c>
       <c r="R54" t="n">
-        <v>6833888</v>
+        <v>6834255</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6072,19 +6092,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6099,22 +6109,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121465159</v>
+        <v>121469335</v>
       </c>
       <c r="B55" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,37 +6137,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483204</v>
+        <v>483483</v>
       </c>
       <c r="R55" t="n">
-        <v>6833925</v>
+        <v>6833854</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6184,19 +6194,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,22 +6211,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469120</v>
+        <v>121469158</v>
       </c>
       <c r="B56" t="n">
-        <v>78340</v>
+        <v>77988</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6239,21 +6239,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483153</v>
+        <v>482967</v>
       </c>
       <c r="R56" t="n">
-        <v>6834504</v>
+        <v>6834339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469155</v>
+        <v>121469135</v>
       </c>
       <c r="B57" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>482892</v>
+        <v>483205</v>
       </c>
       <c r="R57" t="n">
-        <v>6834282</v>
+        <v>6834490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469097</v>
+        <v>121469140</v>
       </c>
       <c r="B58" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6443,21 +6443,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483408</v>
+        <v>483106</v>
       </c>
       <c r="R58" t="n">
-        <v>6833852</v>
+        <v>6834495</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,10 +6529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121465604</v>
+        <v>121469134</v>
       </c>
       <c r="B59" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6545,37 +6545,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483179</v>
+        <v>483277</v>
       </c>
       <c r="R59" t="n">
-        <v>6833973</v>
+        <v>6834451</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6602,19 +6602,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6629,12 +6619,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6743,10 +6733,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469145</v>
+        <v>121465556</v>
       </c>
       <c r="B61" t="n">
-        <v>78249</v>
+        <v>78341</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,37 +6749,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483387</v>
+        <v>483536</v>
       </c>
       <c r="R61" t="n">
-        <v>6833994</v>
+        <v>6833990</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6833,22 +6823,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469334</v>
+        <v>121469102</v>
       </c>
       <c r="B62" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6861,21 +6851,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6885,10 +6875,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483084</v>
+        <v>483161</v>
       </c>
       <c r="R62" t="n">
-        <v>6833901</v>
+        <v>6834377</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,7 +6937,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469127</v>
+        <v>121469143</v>
       </c>
       <c r="B63" t="n">
         <v>78604</v>
@@ -6987,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483514</v>
+        <v>483038</v>
       </c>
       <c r="R63" t="n">
-        <v>6834064</v>
+        <v>6834461</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7049,10 +7039,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121465615</v>
+        <v>121465202</v>
       </c>
       <c r="B64" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7065,21 +7055,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7089,13 +7079,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483179</v>
+        <v>483084</v>
       </c>
       <c r="R64" t="n">
-        <v>6833973</v>
+        <v>6833930</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7124,7 +7114,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7134,7 +7124,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7161,7 +7151,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469336</v>
+        <v>121469338</v>
       </c>
       <c r="B65" t="n">
         <v>79222</v>
@@ -7201,10 +7191,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483492</v>
+        <v>483246</v>
       </c>
       <c r="R65" t="n">
-        <v>6834084</v>
+        <v>6834122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,10 +7253,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469104</v>
+        <v>121469341</v>
       </c>
       <c r="B66" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7279,21 +7269,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7303,10 +7293,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483265</v>
+        <v>483181</v>
       </c>
       <c r="R66" t="n">
-        <v>6834572</v>
+        <v>6834299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7365,10 +7355,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469098</v>
+        <v>121467022</v>
       </c>
       <c r="B67" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7381,21 +7371,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7405,13 +7395,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483445</v>
+        <v>483082</v>
       </c>
       <c r="R67" t="n">
-        <v>6833857</v>
+        <v>6834003</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7438,9 +7428,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7455,22 +7455,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469102</v>
+        <v>121469152</v>
       </c>
       <c r="B68" t="n">
-        <v>78341</v>
+        <v>78249</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483161</v>
+        <v>483169</v>
       </c>
       <c r="R68" t="n">
-        <v>6834377</v>
+        <v>6834491</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469125</v>
+        <v>121469069</v>
       </c>
       <c r="B69" t="n">
-        <v>78340</v>
+        <v>79193</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,21 +7585,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483307</v>
+        <v>483031</v>
       </c>
       <c r="R69" t="n">
-        <v>6833983</v>
+        <v>6834458</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121465603</v>
+        <v>121469095</v>
       </c>
       <c r="B70" t="n">
         <v>78341</v>
@@ -7707,17 +7707,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483561</v>
+        <v>482925</v>
       </c>
       <c r="R70" t="n">
-        <v>6833992</v>
+        <v>6833909</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7744,19 +7744,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7771,22 +7761,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469136</v>
+        <v>121469154</v>
       </c>
       <c r="B71" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7799,21 +7789,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7823,10 +7813,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483198</v>
+        <v>483081</v>
       </c>
       <c r="R71" t="n">
-        <v>6834484</v>
+        <v>6834496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469106</v>
+        <v>121469337</v>
       </c>
       <c r="B72" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7891,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482967</v>
+        <v>483413</v>
       </c>
       <c r="R72" t="n">
-        <v>6834340</v>
+        <v>6834033</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469149</v>
+        <v>121469114</v>
       </c>
       <c r="B73" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +7993,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8017,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483268</v>
+        <v>483434</v>
       </c>
       <c r="R73" t="n">
-        <v>6834459</v>
+        <v>6833855</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8079,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469150</v>
+        <v>121469131</v>
       </c>
       <c r="B74" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8105,21 +8095,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8129,10 +8119,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483294</v>
+        <v>483261</v>
       </c>
       <c r="R74" t="n">
-        <v>6834475</v>
+        <v>6834030</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,7 +8181,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469117</v>
+        <v>121469125</v>
       </c>
       <c r="B75" t="n">
         <v>78340</v>
@@ -8231,10 +8221,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483119</v>
+        <v>483307</v>
       </c>
       <c r="R75" t="n">
-        <v>6834405</v>
+        <v>6833983</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,10 +8283,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469148</v>
+        <v>121469139</v>
       </c>
       <c r="B76" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8299,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8323,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483160</v>
+        <v>483149</v>
       </c>
       <c r="R76" t="n">
-        <v>6834438</v>
+        <v>6834501</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,10 +8385,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469144</v>
+        <v>121469108</v>
       </c>
       <c r="B77" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8411,21 +8401,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8435,10 +8425,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483402</v>
+        <v>482925</v>
       </c>
       <c r="R77" t="n">
-        <v>6834000</v>
+        <v>6833910</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8487,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469070</v>
+        <v>121467080</v>
       </c>
       <c r="B78" t="n">
-        <v>79193</v>
+        <v>78341</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,37 +8503,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483031</v>
+        <v>483038</v>
       </c>
       <c r="R78" t="n">
-        <v>6834425</v>
+        <v>6834006</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8587,22 +8577,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121465160</v>
+        <v>121465603</v>
       </c>
       <c r="B79" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,37 +8605,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483115</v>
+        <v>483561</v>
       </c>
       <c r="R79" t="n">
-        <v>6833942</v>
+        <v>6833992</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8674,7 +8664,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8684,7 +8674,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8699,22 +8689,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121467022</v>
+        <v>121469340</v>
       </c>
       <c r="B80" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8727,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8751,13 +8741,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483082</v>
+        <v>483211</v>
       </c>
       <c r="R80" t="n">
-        <v>6834003</v>
+        <v>6834254</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8784,19 +8774,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8811,22 +8791,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469116</v>
+        <v>121469150</v>
       </c>
       <c r="B81" t="n">
-        <v>78340</v>
+        <v>78249</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8839,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8863,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483484</v>
+        <v>483294</v>
       </c>
       <c r="R81" t="n">
-        <v>6833901</v>
+        <v>6834475</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8925,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469348</v>
+        <v>121469126</v>
       </c>
       <c r="B82" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8941,21 +8921,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8965,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483153</v>
+        <v>483476</v>
       </c>
       <c r="R82" t="n">
-        <v>6834505</v>
+        <v>6834017</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9027,7 +9007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469340</v>
+        <v>121469344</v>
       </c>
       <c r="B83" t="n">
         <v>79222</v>
@@ -9067,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483211</v>
+        <v>483119</v>
       </c>
       <c r="R83" t="n">
-        <v>6834254</v>
+        <v>6834405</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,10 +9109,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121465202</v>
+        <v>121465159</v>
       </c>
       <c r="B84" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9145,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9169,13 +9149,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483084</v>
+        <v>483204</v>
       </c>
       <c r="R84" t="n">
-        <v>6833930</v>
+        <v>6833925</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9204,7 +9184,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9214,7 +9194,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9229,22 +9209,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121467080</v>
+        <v>121465246</v>
       </c>
       <c r="B85" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9257,21 +9237,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9281,13 +9261,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483038</v>
+        <v>483187</v>
       </c>
       <c r="R85" t="n">
-        <v>6834006</v>
+        <v>6833888</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9314,9 +9294,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9331,22 +9321,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469143</v>
+        <v>121465604</v>
       </c>
       <c r="B86" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9359,37 +9349,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483038</v>
+        <v>483179</v>
       </c>
       <c r="R86" t="n">
-        <v>6834461</v>
+        <v>6833973</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9416,9 +9406,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9433,19 +9433,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469131</v>
+        <v>121469132</v>
       </c>
       <c r="B87" t="n">
         <v>78604</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483261</v>
+        <v>483255</v>
       </c>
       <c r="R87" t="n">
-        <v>6834030</v>
+        <v>6834077</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,7 +9547,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469119</v>
+        <v>121469122</v>
       </c>
       <c r="B88" t="n">
         <v>78340</v>
@@ -9587,10 +9587,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483265</v>
+        <v>482967</v>
       </c>
       <c r="R88" t="n">
-        <v>6834572</v>
+        <v>6834340</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9649,10 +9649,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469133</v>
+        <v>121469148</v>
       </c>
       <c r="B89" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9665,21 +9665,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483241</v>
+        <v>483160</v>
       </c>
       <c r="R89" t="n">
-        <v>6834112</v>
+        <v>6834438</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9751,10 +9751,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469154</v>
+        <v>121469070</v>
       </c>
       <c r="B90" t="n">
-        <v>78249</v>
+        <v>79193</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483081</v>
+        <v>483031</v>
       </c>
       <c r="R90" t="n">
-        <v>6834496</v>
+        <v>6834425</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9853,10 +9853,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121465664</v>
+        <v>121469104</v>
       </c>
       <c r="B91" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9869,37 +9869,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483498</v>
+        <v>483265</v>
       </c>
       <c r="R91" t="n">
-        <v>6834031</v>
+        <v>6834572</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9943,22 +9943,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469147</v>
+        <v>121469120</v>
       </c>
       <c r="B92" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483181</v>
+        <v>483153</v>
       </c>
       <c r="R92" t="n">
-        <v>6834299</v>
+        <v>6834504</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10057,10 +10057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469337</v>
+        <v>121469142</v>
       </c>
       <c r="B93" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10073,21 +10073,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10097,10 +10097,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483413</v>
+        <v>483076</v>
       </c>
       <c r="R93" t="n">
-        <v>6834033</v>
+        <v>6834476</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10159,7 +10159,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469349</v>
+        <v>121469343</v>
       </c>
       <c r="B94" t="n">
         <v>79222</v>
@@ -10199,10 +10199,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483065</v>
+        <v>483155</v>
       </c>
       <c r="R94" t="n">
-        <v>6834469</v>
+        <v>6834382</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469110</v>
+        <v>121469099</v>
       </c>
       <c r="B95" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,21 +10277,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483144</v>
+        <v>483482</v>
       </c>
       <c r="R95" t="n">
-        <v>6833875</v>
+        <v>6833855</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10363,10 +10363,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469105</v>
+        <v>121469149</v>
       </c>
       <c r="B96" t="n">
-        <v>78341</v>
+        <v>78249</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483153</v>
+        <v>483268</v>
       </c>
       <c r="R96" t="n">
-        <v>6834504</v>
+        <v>6834459</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10465,10 +10465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469099</v>
+        <v>121469137</v>
       </c>
       <c r="B97" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,21 +10481,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483482</v>
+        <v>483198</v>
       </c>
       <c r="R97" t="n">
-        <v>6833855</v>
+        <v>6834476</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10567,10 +10567,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465024</v>
+        <v>121465017</v>
       </c>
       <c r="B98" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10791,7 +10791,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121465412</v>
+        <v>121466096</v>
       </c>
       <c r="B100" t="n">
         <v>78340</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483177</v>
+        <v>483350</v>
       </c>
       <c r="R100" t="n">
-        <v>6833971</v>
+        <v>6834071</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465017</v>
+        <v>121465052</v>
       </c>
       <c r="B101" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121466059</v>
+        <v>121465234</v>
       </c>
       <c r="B102" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483350</v>
+        <v>483201</v>
       </c>
       <c r="R102" t="n">
-        <v>6834071</v>
+        <v>6833961</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11120,17 +11120,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121464931</v>
+        <v>121465024</v>
       </c>
       <c r="B103" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>482985</v>
+        <v>482987</v>
       </c>
       <c r="R103" t="n">
-        <v>6833943</v>
+        <v>6833950</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121466096</v>
+        <v>121465426</v>
       </c>
       <c r="B104" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483350</v>
+        <v>483209</v>
       </c>
       <c r="R104" t="n">
-        <v>6834071</v>
+        <v>6833990</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11344,17 +11344,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465052</v>
+        <v>121465266</v>
       </c>
       <c r="B105" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>482987</v>
+        <v>483204</v>
       </c>
       <c r="R105" t="n">
-        <v>6833950</v>
+        <v>6833967</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465234</v>
+        <v>121465412</v>
       </c>
       <c r="B106" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483201</v>
+        <v>483177</v>
       </c>
       <c r="R106" t="n">
-        <v>6833961</v>
+        <v>6833971</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11568,17 +11568,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121465266</v>
+        <v>121466059</v>
       </c>
       <c r="B107" t="n">
-        <v>79193</v>
+        <v>79222</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483204</v>
+        <v>483350</v>
       </c>
       <c r="R107" t="n">
-        <v>6833967</v>
+        <v>6834071</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,7 +11687,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121465426</v>
+        <v>121464931</v>
       </c>
       <c r="B108" t="n">
         <v>78341</v>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483209</v>
+        <v>482985</v>
       </c>
       <c r="R108" t="n">
-        <v>6833990</v>
+        <v>6833943</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326438</v>
+        <v>121326433</v>
       </c>
       <c r="B2" t="n">
-        <v>78341</v>
+        <v>79196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483043</v>
+        <v>483040</v>
       </c>
       <c r="R2" t="n">
-        <v>6834195</v>
+        <v>6834198</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326737</v>
+        <v>121326438</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483242</v>
+        <v>483043</v>
       </c>
       <c r="R3" t="n">
-        <v>6834570</v>
+        <v>6834195</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>121326179</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326921</v>
+        <v>121326737</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483134</v>
+        <v>483242</v>
       </c>
       <c r="R5" t="n">
-        <v>6833995</v>
+        <v>6834570</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>121326404</v>
       </c>
       <c r="B6" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326433</v>
+        <v>121326800</v>
       </c>
       <c r="B7" t="n">
-        <v>79193</v>
+        <v>78343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483040</v>
+        <v>483205</v>
       </c>
       <c r="R7" t="n">
-        <v>6834198</v>
+        <v>6834165</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326800</v>
+        <v>121326921</v>
       </c>
       <c r="B8" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483205</v>
+        <v>483134</v>
       </c>
       <c r="R8" t="n">
-        <v>6834165</v>
+        <v>6833995</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469130</v>
+        <v>121469144</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>78252</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483307</v>
+        <v>483402</v>
       </c>
       <c r="R9" t="n">
-        <v>6833983</v>
+        <v>6834000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469124</v>
+        <v>121469140</v>
       </c>
       <c r="B10" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482865</v>
+        <v>483106</v>
       </c>
       <c r="R10" t="n">
-        <v>6834254</v>
+        <v>6834495</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469136</v>
+        <v>121469114</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483198</v>
+        <v>483434</v>
       </c>
       <c r="R11" t="n">
-        <v>6834484</v>
+        <v>6833855</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469145</v>
+        <v>121465604</v>
       </c>
       <c r="B12" t="n">
-        <v>78249</v>
+        <v>78343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483387</v>
+        <v>483179</v>
       </c>
       <c r="R12" t="n">
-        <v>6833994</v>
+        <v>6833973</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,9 +1768,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469098</v>
+        <v>121469334</v>
       </c>
       <c r="B13" t="n">
-        <v>78341</v>
+        <v>79225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483445</v>
+        <v>483084</v>
       </c>
       <c r="R13" t="n">
-        <v>6833857</v>
+        <v>6833901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469349</v>
+        <v>121469136</v>
       </c>
       <c r="B14" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483065</v>
+        <v>483198</v>
       </c>
       <c r="R14" t="n">
-        <v>6834469</v>
+        <v>6834484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2014,7 @@
         <v>121469146</v>
       </c>
       <c r="B15" t="n">
-        <v>78249</v>
+        <v>78252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469096</v>
+        <v>121465159</v>
       </c>
       <c r="B16" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,37 +2129,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483058</v>
+        <v>483204</v>
       </c>
       <c r="R16" t="n">
-        <v>6833926</v>
+        <v>6833925</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,9 +2186,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121466253</v>
+        <v>121469347</v>
       </c>
       <c r="B17" t="n">
-        <v>78341</v>
+        <v>79225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,37 +2241,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483464</v>
+        <v>483261</v>
       </c>
       <c r="R17" t="n">
-        <v>6833910</v>
+        <v>6834535</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,22 +2315,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469347</v>
+        <v>121469142</v>
       </c>
       <c r="B18" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483261</v>
+        <v>483076</v>
       </c>
       <c r="R18" t="n">
-        <v>6834535</v>
+        <v>6834476</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469342</v>
+        <v>121469147</v>
       </c>
       <c r="B19" t="n">
-        <v>79222</v>
+        <v>78252</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483160</v>
+        <v>483181</v>
       </c>
       <c r="R19" t="n">
-        <v>6834377</v>
+        <v>6834299</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469334</v>
+        <v>121469119</v>
       </c>
       <c r="B20" t="n">
-        <v>79222</v>
+        <v>78343</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483084</v>
+        <v>483265</v>
       </c>
       <c r="R20" t="n">
-        <v>6833901</v>
+        <v>6834572</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469110</v>
+        <v>121469122</v>
       </c>
       <c r="B21" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483144</v>
+        <v>482967</v>
       </c>
       <c r="R21" t="n">
-        <v>6833875</v>
+        <v>6834340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469118</v>
+        <v>121469106</v>
       </c>
       <c r="B22" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483210</v>
+        <v>482967</v>
       </c>
       <c r="R22" t="n">
-        <v>6834456</v>
+        <v>6834340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469155</v>
+        <v>121469098</v>
       </c>
       <c r="B23" t="n">
-        <v>78249</v>
+        <v>78344</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482892</v>
+        <v>483445</v>
       </c>
       <c r="R23" t="n">
-        <v>6834282</v>
+        <v>6833857</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469117</v>
+        <v>121469095</v>
       </c>
       <c r="B24" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483119</v>
+        <v>482925</v>
       </c>
       <c r="R24" t="n">
-        <v>6834405</v>
+        <v>6833909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121465664</v>
+        <v>121469150</v>
       </c>
       <c r="B25" t="n">
-        <v>78340</v>
+        <v>78252</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,37 +3057,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483498</v>
+        <v>483294</v>
       </c>
       <c r="R25" t="n">
-        <v>6834031</v>
+        <v>6834475</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3111,22 +3131,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469147</v>
+        <v>121469343</v>
       </c>
       <c r="B26" t="n">
-        <v>78249</v>
+        <v>79225</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483181</v>
+        <v>483155</v>
       </c>
       <c r="R26" t="n">
-        <v>6834299</v>
+        <v>6834382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469127</v>
+        <v>121469143</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483514</v>
+        <v>483038</v>
       </c>
       <c r="R27" t="n">
-        <v>6834064</v>
+        <v>6834461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121465615</v>
+        <v>121469118</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,34 +3363,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483179</v>
+        <v>483210</v>
       </c>
       <c r="R28" t="n">
-        <v>6833973</v>
+        <v>6834456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,19 +3420,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,22 +3437,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467007</v>
+        <v>121465615</v>
       </c>
       <c r="B29" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,37 +3465,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483082</v>
+        <v>483179</v>
       </c>
       <c r="R29" t="n">
-        <v>6834003</v>
+        <v>6833973</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3514,7 +3524,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3524,7 +3534,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3539,22 +3549,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469107</v>
+        <v>121469105</v>
       </c>
       <c r="B30" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3591,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>482865</v>
+        <v>483153</v>
       </c>
       <c r="R30" t="n">
-        <v>6834255</v>
+        <v>6834504</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469144</v>
+        <v>121465246</v>
       </c>
       <c r="B31" t="n">
-        <v>78249</v>
+        <v>78343</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,37 +3679,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483402</v>
+        <v>483187</v>
       </c>
       <c r="R31" t="n">
-        <v>6834000</v>
+        <v>6833888</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3726,9 +3736,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3743,22 +3763,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469115</v>
+        <v>121469135</v>
       </c>
       <c r="B32" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3791,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3815,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483445</v>
+        <v>483205</v>
       </c>
       <c r="R32" t="n">
-        <v>6833857</v>
+        <v>6834490</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469128</v>
+        <v>121469351</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483524</v>
+        <v>482864</v>
       </c>
       <c r="R33" t="n">
-        <v>6834071</v>
+        <v>6834255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469106</v>
+        <v>121469345</v>
       </c>
       <c r="B34" t="n">
-        <v>78341</v>
+        <v>79225</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>482967</v>
+        <v>483210</v>
       </c>
       <c r="R34" t="n">
-        <v>6834340</v>
+        <v>6834457</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469156</v>
+        <v>121469340</v>
       </c>
       <c r="B35" t="n">
-        <v>78249</v>
+        <v>79225</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>482876</v>
+        <v>483211</v>
       </c>
       <c r="R35" t="n">
-        <v>6834258</v>
+        <v>6834254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4183,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469336</v>
+        <v>121467080</v>
       </c>
       <c r="B36" t="n">
-        <v>79222</v>
+        <v>78344</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,37 +4199,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483492</v>
+        <v>483038</v>
       </c>
       <c r="R36" t="n">
-        <v>6834084</v>
+        <v>6834006</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4253,22 +4273,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469348</v>
+        <v>121469104</v>
       </c>
       <c r="B37" t="n">
-        <v>79222</v>
+        <v>78344</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4301,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483153</v>
+        <v>483265</v>
       </c>
       <c r="R37" t="n">
-        <v>6834505</v>
+        <v>6834572</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469097</v>
+        <v>121469107</v>
       </c>
       <c r="B38" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4407,10 +4427,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483408</v>
+        <v>482865</v>
       </c>
       <c r="R38" t="n">
-        <v>6833852</v>
+        <v>6834255</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4489,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121465160</v>
+        <v>121469099</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4505,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,13 +4529,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483115</v>
+        <v>483482</v>
       </c>
       <c r="R39" t="n">
-        <v>6833942</v>
+        <v>6833855</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4542,19 +4562,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4569,22 +4579,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469116</v>
+        <v>121469131</v>
       </c>
       <c r="B40" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4607,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4631,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483484</v>
+        <v>483261</v>
       </c>
       <c r="R40" t="n">
-        <v>6833901</v>
+        <v>6834030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469112</v>
+        <v>121469096</v>
       </c>
       <c r="B41" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,21 +4709,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483408</v>
+        <v>483058</v>
       </c>
       <c r="R41" t="n">
-        <v>6833852</v>
+        <v>6833926</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469339</v>
+        <v>121469103</v>
       </c>
       <c r="B42" t="n">
-        <v>79222</v>
+        <v>78344</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4811,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483213</v>
+        <v>483145</v>
       </c>
       <c r="R42" t="n">
-        <v>6834252</v>
+        <v>6834394</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469105</v>
+        <v>121469149</v>
       </c>
       <c r="B43" t="n">
-        <v>78341</v>
+        <v>78252</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4903,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4927,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483153</v>
+        <v>483268</v>
       </c>
       <c r="R43" t="n">
-        <v>6834504</v>
+        <v>6834459</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469157</v>
+        <v>121469156</v>
       </c>
       <c r="B44" t="n">
-        <v>77988</v>
+        <v>78252</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5005,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5029,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483143</v>
+        <v>482876</v>
       </c>
       <c r="R44" t="n">
-        <v>6833875</v>
+        <v>6834258</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121465189</v>
+        <v>121469069</v>
       </c>
       <c r="B45" t="n">
-        <v>78341</v>
+        <v>79196</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5107,37 +5117,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483204</v>
+        <v>483031</v>
       </c>
       <c r="R45" t="n">
-        <v>6833925</v>
+        <v>6834458</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5164,19 +5174,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5191,22 +5191,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469333</v>
+        <v>121469070</v>
       </c>
       <c r="B46" t="n">
-        <v>79222</v>
+        <v>79196</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483059</v>
+        <v>483031</v>
       </c>
       <c r="R46" t="n">
-        <v>6833927</v>
+        <v>6834425</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469345</v>
+        <v>121465556</v>
       </c>
       <c r="B47" t="n">
-        <v>79222</v>
+        <v>78344</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,37 +5321,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483210</v>
+        <v>483536</v>
       </c>
       <c r="R47" t="n">
-        <v>6834457</v>
+        <v>6833990</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5395,22 +5395,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469350</v>
+        <v>121465160</v>
       </c>
       <c r="B48" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5447,13 +5447,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483033</v>
+        <v>483115</v>
       </c>
       <c r="R48" t="n">
-        <v>6834458</v>
+        <v>6833942</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5480,9 +5480,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5497,22 +5507,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469119</v>
+        <v>121469139</v>
       </c>
       <c r="B49" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483265</v>
+        <v>483149</v>
       </c>
       <c r="R49" t="n">
-        <v>6834572</v>
+        <v>6834501</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469133</v>
+        <v>121469116</v>
       </c>
       <c r="B50" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5627,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5651,10 +5661,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483241</v>
+        <v>483484</v>
       </c>
       <c r="R50" t="n">
-        <v>6834112</v>
+        <v>6833901</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469071</v>
+        <v>121469120</v>
       </c>
       <c r="B51" t="n">
-        <v>57504</v>
+        <v>78343</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5729,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5753,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483265</v>
+        <v>483153</v>
       </c>
       <c r="R51" t="n">
-        <v>6834571</v>
+        <v>6834504</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5815,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469101</v>
+        <v>121469335</v>
       </c>
       <c r="B52" t="n">
-        <v>78341</v>
+        <v>79225</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5831,21 +5841,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5855,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483168</v>
+        <v>483483</v>
       </c>
       <c r="R52" t="n">
-        <v>6834333</v>
+        <v>6833854</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5917,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469103</v>
+        <v>121469137</v>
       </c>
       <c r="B53" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5933,21 +5943,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5957,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483145</v>
+        <v>483198</v>
       </c>
       <c r="R53" t="n">
-        <v>6834394</v>
+        <v>6834476</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6019,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469351</v>
+        <v>121469112</v>
       </c>
       <c r="B54" t="n">
-        <v>79222</v>
+        <v>78343</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6035,21 +6045,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6059,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>482864</v>
+        <v>483408</v>
       </c>
       <c r="R54" t="n">
-        <v>6834255</v>
+        <v>6833852</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6121,10 +6131,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469335</v>
+        <v>121469152</v>
       </c>
       <c r="B55" t="n">
-        <v>79222</v>
+        <v>78252</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6137,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6161,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483483</v>
+        <v>483169</v>
       </c>
       <c r="R55" t="n">
-        <v>6833854</v>
+        <v>6834491</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469158</v>
+        <v>121469115</v>
       </c>
       <c r="B56" t="n">
-        <v>77988</v>
+        <v>78343</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6239,21 +6249,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6263,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>482967</v>
+        <v>483445</v>
       </c>
       <c r="R56" t="n">
-        <v>6834339</v>
+        <v>6833857</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469135</v>
+        <v>121469158</v>
       </c>
       <c r="B57" t="n">
-        <v>78604</v>
+        <v>77991</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483205</v>
+        <v>482967</v>
       </c>
       <c r="R57" t="n">
-        <v>6834490</v>
+        <v>6834339</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469140</v>
+        <v>121469342</v>
       </c>
       <c r="B58" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6443,21 +6453,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6467,10 +6477,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483106</v>
+        <v>483160</v>
       </c>
       <c r="R58" t="n">
-        <v>6834495</v>
+        <v>6834377</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,10 +6539,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469134</v>
+        <v>121469349</v>
       </c>
       <c r="B59" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6545,21 +6555,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6569,10 +6579,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483277</v>
+        <v>483065</v>
       </c>
       <c r="R59" t="n">
-        <v>6834451</v>
+        <v>6834469</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,10 +6641,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469100</v>
+        <v>121467007</v>
       </c>
       <c r="B60" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6671,13 +6681,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483211</v>
+        <v>483082</v>
       </c>
       <c r="R60" t="n">
-        <v>6834254</v>
+        <v>6834003</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6704,9 +6714,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6721,22 +6741,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121465556</v>
+        <v>121469148</v>
       </c>
       <c r="B61" t="n">
-        <v>78341</v>
+        <v>78252</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6749,37 +6769,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483536</v>
+        <v>483160</v>
       </c>
       <c r="R61" t="n">
-        <v>6833990</v>
+        <v>6834438</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6823,22 +6843,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469102</v>
+        <v>121469125</v>
       </c>
       <c r="B62" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6851,21 +6871,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6875,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483161</v>
+        <v>483307</v>
       </c>
       <c r="R62" t="n">
-        <v>6834377</v>
+        <v>6833983</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469143</v>
+        <v>121469126</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6977,10 +6997,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483038</v>
+        <v>483476</v>
       </c>
       <c r="R63" t="n">
-        <v>6834461</v>
+        <v>6834017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,10 +7059,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121465202</v>
+        <v>121469154</v>
       </c>
       <c r="B64" t="n">
-        <v>78249</v>
+        <v>78252</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7075,17 +7095,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483084</v>
+        <v>483081</v>
       </c>
       <c r="R64" t="n">
-        <v>6833930</v>
+        <v>6834496</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7112,19 +7132,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7139,22 +7149,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469338</v>
+        <v>121469337</v>
       </c>
       <c r="B65" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483246</v>
+        <v>483413</v>
       </c>
       <c r="R65" t="n">
-        <v>6834122</v>
+        <v>6834033</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7253,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469341</v>
+        <v>121469348</v>
       </c>
       <c r="B66" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7293,10 +7303,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483181</v>
+        <v>483153</v>
       </c>
       <c r="R66" t="n">
-        <v>6834299</v>
+        <v>6834505</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7355,10 +7365,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121467022</v>
+        <v>121469101</v>
       </c>
       <c r="B67" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,21 +7381,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7395,13 +7405,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483082</v>
+        <v>483168</v>
       </c>
       <c r="R67" t="n">
-        <v>6834003</v>
+        <v>6834333</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7428,19 +7438,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7455,22 +7455,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469152</v>
+        <v>121465189</v>
       </c>
       <c r="B68" t="n">
-        <v>78249</v>
+        <v>78344</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,37 +7483,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483169</v>
+        <v>483204</v>
       </c>
       <c r="R68" t="n">
-        <v>6834491</v>
+        <v>6833925</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7540,9 +7540,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7557,22 +7567,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469069</v>
+        <v>121469333</v>
       </c>
       <c r="B69" t="n">
-        <v>79193</v>
+        <v>79225</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7609,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483031</v>
+        <v>483059</v>
       </c>
       <c r="R69" t="n">
-        <v>6834458</v>
+        <v>6833927</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7671,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469095</v>
+        <v>121469110</v>
       </c>
       <c r="B70" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7687,21 +7697,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7711,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>482925</v>
+        <v>483144</v>
       </c>
       <c r="R70" t="n">
-        <v>6833909</v>
+        <v>6833875</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7773,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469154</v>
+        <v>121467022</v>
       </c>
       <c r="B71" t="n">
-        <v>78249</v>
+        <v>78343</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7789,21 +7799,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7813,13 +7823,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483081</v>
+        <v>483082</v>
       </c>
       <c r="R71" t="n">
-        <v>6834496</v>
+        <v>6834003</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7846,9 +7856,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7863,22 +7883,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469337</v>
+        <v>121469128</v>
       </c>
       <c r="B72" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7891,21 +7911,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7915,10 +7935,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483413</v>
+        <v>483524</v>
       </c>
       <c r="R72" t="n">
-        <v>6834033</v>
+        <v>6834071</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,10 +7997,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469114</v>
+        <v>121469338</v>
       </c>
       <c r="B73" t="n">
-        <v>78340</v>
+        <v>79225</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7993,21 +8013,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8017,10 +8037,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483434</v>
+        <v>483246</v>
       </c>
       <c r="R73" t="n">
-        <v>6833855</v>
+        <v>6834122</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8079,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469131</v>
+        <v>121469117</v>
       </c>
       <c r="B74" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8095,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8119,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483261</v>
+        <v>483119</v>
       </c>
       <c r="R74" t="n">
-        <v>6834030</v>
+        <v>6834405</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469125</v>
+        <v>121469108</v>
       </c>
       <c r="B75" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8221,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483307</v>
+        <v>482925</v>
       </c>
       <c r="R75" t="n">
-        <v>6833983</v>
+        <v>6833910</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8283,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469139</v>
+        <v>121469157</v>
       </c>
       <c r="B76" t="n">
-        <v>78604</v>
+        <v>77991</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8299,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8323,10 +8343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483149</v>
+        <v>483143</v>
       </c>
       <c r="R76" t="n">
-        <v>6834501</v>
+        <v>6833875</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8385,10 +8405,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469108</v>
+        <v>121469133</v>
       </c>
       <c r="B77" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8401,21 +8421,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8425,10 +8445,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>482925</v>
+        <v>483241</v>
       </c>
       <c r="R77" t="n">
-        <v>6833910</v>
+        <v>6834112</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8487,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121467080</v>
+        <v>121469130</v>
       </c>
       <c r="B78" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8503,37 +8523,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483038</v>
+        <v>483307</v>
       </c>
       <c r="R78" t="n">
-        <v>6834006</v>
+        <v>6833983</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8577,22 +8597,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121465603</v>
+        <v>121465202</v>
       </c>
       <c r="B79" t="n">
-        <v>78341</v>
+        <v>78252</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8605,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8629,13 +8649,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483561</v>
+        <v>483084</v>
       </c>
       <c r="R79" t="n">
-        <v>6833992</v>
+        <v>6833930</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8664,7 +8684,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8674,7 +8694,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8689,22 +8709,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469340</v>
+        <v>121465664</v>
       </c>
       <c r="B80" t="n">
-        <v>79222</v>
+        <v>78343</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,37 +8737,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483211</v>
+        <v>483498</v>
       </c>
       <c r="R80" t="n">
-        <v>6834254</v>
+        <v>6834031</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8791,22 +8811,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469150</v>
+        <v>121469132</v>
       </c>
       <c r="B81" t="n">
-        <v>78249</v>
+        <v>78607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,21 +8839,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8843,10 +8863,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483294</v>
+        <v>483255</v>
       </c>
       <c r="R81" t="n">
-        <v>6834475</v>
+        <v>6834077</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8905,10 +8925,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469126</v>
+        <v>121469071</v>
       </c>
       <c r="B82" t="n">
-        <v>78604</v>
+        <v>57507</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8965,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483476</v>
+        <v>483265</v>
       </c>
       <c r="R82" t="n">
-        <v>6834017</v>
+        <v>6834571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469344</v>
+        <v>121469100</v>
       </c>
       <c r="B83" t="n">
-        <v>79222</v>
+        <v>78344</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9023,21 +9043,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9047,10 +9067,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483119</v>
+        <v>483211</v>
       </c>
       <c r="R83" t="n">
-        <v>6834405</v>
+        <v>6834254</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,10 +9129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121465159</v>
+        <v>121469134</v>
       </c>
       <c r="B84" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,37 +9145,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483204</v>
+        <v>483277</v>
       </c>
       <c r="R84" t="n">
-        <v>6833925</v>
+        <v>6834451</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9182,19 +9202,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9209,22 +9219,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121465246</v>
+        <v>121469350</v>
       </c>
       <c r="B85" t="n">
-        <v>78340</v>
+        <v>79225</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9237,37 +9247,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483187</v>
+        <v>483033</v>
       </c>
       <c r="R85" t="n">
-        <v>6833888</v>
+        <v>6834458</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9294,19 +9304,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9321,22 +9321,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121465604</v>
+        <v>121469339</v>
       </c>
       <c r="B86" t="n">
-        <v>78340</v>
+        <v>79225</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9349,37 +9349,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483179</v>
+        <v>483213</v>
       </c>
       <c r="R86" t="n">
-        <v>6833973</v>
+        <v>6834252</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9406,19 +9406,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9433,22 +9423,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469132</v>
+        <v>121469097</v>
       </c>
       <c r="B87" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9461,21 +9451,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9475,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483255</v>
+        <v>483408</v>
       </c>
       <c r="R87" t="n">
-        <v>6834077</v>
+        <v>6833852</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,10 +9537,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469122</v>
+        <v>121469155</v>
       </c>
       <c r="B88" t="n">
-        <v>78340</v>
+        <v>78252</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9563,21 +9553,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9587,10 +9577,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482967</v>
+        <v>482892</v>
       </c>
       <c r="R88" t="n">
-        <v>6834340</v>
+        <v>6834282</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9649,10 +9639,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469148</v>
+        <v>121469336</v>
       </c>
       <c r="B89" t="n">
-        <v>78249</v>
+        <v>79225</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9665,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9689,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483160</v>
+        <v>483492</v>
       </c>
       <c r="R89" t="n">
-        <v>6834438</v>
+        <v>6834084</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9751,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469070</v>
+        <v>121469124</v>
       </c>
       <c r="B90" t="n">
-        <v>79193</v>
+        <v>78343</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9767,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9791,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483031</v>
+        <v>482865</v>
       </c>
       <c r="R90" t="n">
-        <v>6834425</v>
+        <v>6834254</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9853,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469104</v>
+        <v>121469127</v>
       </c>
       <c r="B91" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9869,21 +9859,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9893,10 +9883,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483265</v>
+        <v>483514</v>
       </c>
       <c r="R91" t="n">
-        <v>6834572</v>
+        <v>6834064</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9955,10 +9945,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469120</v>
+        <v>121469341</v>
       </c>
       <c r="B92" t="n">
-        <v>78340</v>
+        <v>79225</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9961,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483153</v>
+        <v>483181</v>
       </c>
       <c r="R92" t="n">
-        <v>6834504</v>
+        <v>6834299</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10057,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469142</v>
+        <v>121469344</v>
       </c>
       <c r="B93" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10073,21 +10063,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10097,10 +10087,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483076</v>
+        <v>483119</v>
       </c>
       <c r="R93" t="n">
-        <v>6834476</v>
+        <v>6834405</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10159,10 +10149,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469343</v>
+        <v>121465603</v>
       </c>
       <c r="B94" t="n">
-        <v>79222</v>
+        <v>78344</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10175,37 +10165,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483155</v>
+        <v>483561</v>
       </c>
       <c r="R94" t="n">
-        <v>6834382</v>
+        <v>6833992</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10232,9 +10222,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10249,22 +10249,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469099</v>
+        <v>121469145</v>
       </c>
       <c r="B95" t="n">
-        <v>78341</v>
+        <v>78252</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,21 +10277,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483482</v>
+        <v>483387</v>
       </c>
       <c r="R95" t="n">
-        <v>6833855</v>
+        <v>6833994</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10363,10 +10363,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469149</v>
+        <v>121469102</v>
       </c>
       <c r="B96" t="n">
-        <v>78249</v>
+        <v>78344</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483268</v>
+        <v>483161</v>
       </c>
       <c r="R96" t="n">
-        <v>6834459</v>
+        <v>6834377</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10465,10 +10465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469137</v>
+        <v>121466253</v>
       </c>
       <c r="B97" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,37 +10481,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483198</v>
+        <v>483464</v>
       </c>
       <c r="R97" t="n">
-        <v>6834476</v>
+        <v>6833910</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465017</v>
+        <v>121465991</v>
       </c>
       <c r="B98" t="n">
-        <v>78340</v>
+        <v>79717</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,25 +10579,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>482987</v>
+        <v>483306</v>
       </c>
       <c r="R98" t="n">
-        <v>6833950</v>
+        <v>6834009</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465991</v>
+        <v>121465052</v>
       </c>
       <c r="B99" t="n">
-        <v>79714</v>
+        <v>78607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10691,25 +10691,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483306</v>
+        <v>482987</v>
       </c>
       <c r="R99" t="n">
-        <v>6834009</v>
+        <v>6833950</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121466096</v>
+        <v>121465426</v>
       </c>
       <c r="B100" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483350</v>
+        <v>483209</v>
       </c>
       <c r="R100" t="n">
-        <v>6834071</v>
+        <v>6833990</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465052</v>
+        <v>121465234</v>
       </c>
       <c r="B101" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>482987</v>
+        <v>483201</v>
       </c>
       <c r="R101" t="n">
-        <v>6833950</v>
+        <v>6833961</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465234</v>
+        <v>121466096</v>
       </c>
       <c r="B102" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483201</v>
+        <v>483350</v>
       </c>
       <c r="R102" t="n">
-        <v>6833961</v>
+        <v>6834071</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11120,17 +11120,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121465024</v>
+        <v>121466059</v>
       </c>
       <c r="B103" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>482987</v>
+        <v>483350</v>
       </c>
       <c r="R103" t="n">
-        <v>6833950</v>
+        <v>6834071</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465426</v>
+        <v>121465024</v>
       </c>
       <c r="B104" t="n">
-        <v>78341</v>
+        <v>79225</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483209</v>
+        <v>482987</v>
       </c>
       <c r="R104" t="n">
-        <v>6833990</v>
+        <v>6833950</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11344,17 +11344,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465266</v>
+        <v>121465017</v>
       </c>
       <c r="B105" t="n">
-        <v>79193</v>
+        <v>78343</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483204</v>
+        <v>482987</v>
       </c>
       <c r="R105" t="n">
-        <v>6833967</v>
+        <v>6833950</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465412</v>
+        <v>121465266</v>
       </c>
       <c r="B106" t="n">
-        <v>78340</v>
+        <v>79196</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483177</v>
+        <v>483204</v>
       </c>
       <c r="R106" t="n">
-        <v>6833971</v>
+        <v>6833967</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11568,17 +11568,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121466059</v>
+        <v>121465412</v>
       </c>
       <c r="B107" t="n">
-        <v>79222</v>
+        <v>78343</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483350</v>
+        <v>483177</v>
       </c>
       <c r="R107" t="n">
-        <v>6834071</v>
+        <v>6833971</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11690,7 +11690,7 @@
         <v>121464931</v>
       </c>
       <c r="B108" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326433</v>
+        <v>121326737</v>
       </c>
       <c r="B2" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483040</v>
+        <v>483242</v>
       </c>
       <c r="R2" t="n">
-        <v>6834198</v>
+        <v>6834570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326438</v>
+        <v>121326800</v>
       </c>
       <c r="B3" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483043</v>
+        <v>483205</v>
       </c>
       <c r="R3" t="n">
-        <v>6834195</v>
+        <v>6834165</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326179</v>
+        <v>121326433</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>79196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482925</v>
+        <v>483040</v>
       </c>
       <c r="R4" t="n">
-        <v>6834028</v>
+        <v>6834198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326737</v>
+        <v>121326921</v>
       </c>
       <c r="B5" t="n">
         <v>78607</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483242</v>
+        <v>483134</v>
       </c>
       <c r="R5" t="n">
-        <v>6834570</v>
+        <v>6833995</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326404</v>
+        <v>121326179</v>
       </c>
       <c r="B6" t="n">
         <v>78344</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483018</v>
+        <v>482925</v>
       </c>
       <c r="R6" t="n">
-        <v>6834214</v>
+        <v>6834028</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326800</v>
+        <v>121326438</v>
       </c>
       <c r="B7" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483205</v>
+        <v>483043</v>
       </c>
       <c r="R7" t="n">
-        <v>6834165</v>
+        <v>6834195</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326921</v>
+        <v>121326404</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483134</v>
+        <v>483018</v>
       </c>
       <c r="R8" t="n">
-        <v>6833995</v>
+        <v>6834214</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469144</v>
+        <v>121465160</v>
       </c>
       <c r="B9" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483402</v>
+        <v>483115</v>
       </c>
       <c r="R9" t="n">
-        <v>6834000</v>
+        <v>6833942</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,9 +1462,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,19 +1489,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469140</v>
+        <v>121469128</v>
       </c>
       <c r="B10" t="n">
         <v>78607</v>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483106</v>
+        <v>483524</v>
       </c>
       <c r="R10" t="n">
-        <v>6834495</v>
+        <v>6834071</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469114</v>
+        <v>121465202</v>
       </c>
       <c r="B11" t="n">
-        <v>78343</v>
+        <v>78252</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1619,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483434</v>
+        <v>483084</v>
       </c>
       <c r="R11" t="n">
-        <v>6833855</v>
+        <v>6833930</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1676,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121465604</v>
+        <v>121469144</v>
       </c>
       <c r="B12" t="n">
-        <v>78343</v>
+        <v>78252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483179</v>
+        <v>483402</v>
       </c>
       <c r="R12" t="n">
-        <v>6833973</v>
+        <v>6834000</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,19 +1788,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,19 +1805,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469334</v>
+        <v>121469342</v>
       </c>
       <c r="B13" t="n">
         <v>79225</v>
@@ -1847,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483084</v>
+        <v>483160</v>
       </c>
       <c r="R13" t="n">
-        <v>6833901</v>
+        <v>6834377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469136</v>
+        <v>121469098</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483198</v>
+        <v>483445</v>
       </c>
       <c r="R14" t="n">
-        <v>6834484</v>
+        <v>6833857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469146</v>
+        <v>121469133</v>
       </c>
       <c r="B15" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483260</v>
+        <v>483241</v>
       </c>
       <c r="R15" t="n">
-        <v>6834060</v>
+        <v>6834112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121465159</v>
+        <v>121469333</v>
       </c>
       <c r="B16" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,37 +2139,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483204</v>
+        <v>483059</v>
       </c>
       <c r="R16" t="n">
-        <v>6833925</v>
+        <v>6833927</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2186,19 +2196,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469347</v>
+        <v>121469117</v>
       </c>
       <c r="B17" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483261</v>
+        <v>483119</v>
       </c>
       <c r="R17" t="n">
-        <v>6834535</v>
+        <v>6834405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469142</v>
+        <v>121469334</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483076</v>
+        <v>483084</v>
       </c>
       <c r="R18" t="n">
-        <v>6834476</v>
+        <v>6833901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469147</v>
+        <v>121469108</v>
       </c>
       <c r="B19" t="n">
-        <v>78252</v>
+        <v>78343</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483181</v>
+        <v>482925</v>
       </c>
       <c r="R19" t="n">
-        <v>6834299</v>
+        <v>6833910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469119</v>
+        <v>121469350</v>
       </c>
       <c r="B20" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483265</v>
+        <v>483033</v>
       </c>
       <c r="R20" t="n">
-        <v>6834572</v>
+        <v>6834458</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469122</v>
+        <v>121469136</v>
       </c>
       <c r="B21" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482967</v>
+        <v>483198</v>
       </c>
       <c r="R21" t="n">
-        <v>6834340</v>
+        <v>6834484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469106</v>
+        <v>121465159</v>
       </c>
       <c r="B22" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482967</v>
+        <v>483204</v>
       </c>
       <c r="R22" t="n">
-        <v>6834340</v>
+        <v>6833925</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,9 +2808,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,22 +2835,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469098</v>
+        <v>121469349</v>
       </c>
       <c r="B23" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483445</v>
+        <v>483065</v>
       </c>
       <c r="R23" t="n">
-        <v>6833857</v>
+        <v>6834469</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469095</v>
+        <v>121469118</v>
       </c>
       <c r="B24" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482925</v>
+        <v>483210</v>
       </c>
       <c r="R24" t="n">
-        <v>6833909</v>
+        <v>6834456</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469150</v>
+        <v>121469127</v>
       </c>
       <c r="B25" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483294</v>
+        <v>483514</v>
       </c>
       <c r="R25" t="n">
-        <v>6834475</v>
+        <v>6834064</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469343</v>
+        <v>121469104</v>
       </c>
       <c r="B26" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483155</v>
+        <v>483265</v>
       </c>
       <c r="R26" t="n">
-        <v>6834382</v>
+        <v>6834572</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469143</v>
+        <v>121469107</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483038</v>
+        <v>482865</v>
       </c>
       <c r="R27" t="n">
-        <v>6834461</v>
+        <v>6834255</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469118</v>
+        <v>121469102</v>
       </c>
       <c r="B28" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483210</v>
+        <v>483161</v>
       </c>
       <c r="R28" t="n">
-        <v>6834456</v>
+        <v>6834377</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121465615</v>
+        <v>121469125</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,34 +3475,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483179</v>
+        <v>483307</v>
       </c>
       <c r="R29" t="n">
-        <v>6833973</v>
+        <v>6833983</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3522,19 +3532,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3549,22 +3549,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469105</v>
+        <v>121469115</v>
       </c>
       <c r="B30" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483153</v>
+        <v>483445</v>
       </c>
       <c r="R30" t="n">
-        <v>6834504</v>
+        <v>6833857</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469135</v>
+        <v>121469110</v>
       </c>
       <c r="B32" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3791,21 +3791,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483205</v>
+        <v>483144</v>
       </c>
       <c r="R32" t="n">
-        <v>6834490</v>
+        <v>6833875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469351</v>
+        <v>121469112</v>
       </c>
       <c r="B33" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482864</v>
+        <v>483408</v>
       </c>
       <c r="R33" t="n">
-        <v>6834255</v>
+        <v>6833852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469345</v>
+        <v>121469101</v>
       </c>
       <c r="B34" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483210</v>
+        <v>483168</v>
       </c>
       <c r="R34" t="n">
-        <v>6834457</v>
+        <v>6834333</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469340</v>
+        <v>121469145</v>
       </c>
       <c r="B35" t="n">
-        <v>79225</v>
+        <v>78252</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483211</v>
+        <v>483387</v>
       </c>
       <c r="R35" t="n">
-        <v>6834254</v>
+        <v>6833994</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,10 +4183,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121467080</v>
+        <v>121469336</v>
       </c>
       <c r="B36" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483038</v>
+        <v>483492</v>
       </c>
       <c r="R36" t="n">
-        <v>6834006</v>
+        <v>6834084</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4273,22 +4273,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469104</v>
+        <v>121469341</v>
       </c>
       <c r="B37" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483265</v>
+        <v>483181</v>
       </c>
       <c r="R37" t="n">
-        <v>6834572</v>
+        <v>6834299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469107</v>
+        <v>121469338</v>
       </c>
       <c r="B38" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4403,21 +4403,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>482865</v>
+        <v>483246</v>
       </c>
       <c r="R38" t="n">
-        <v>6834255</v>
+        <v>6834122</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469099</v>
+        <v>121469135</v>
       </c>
       <c r="B39" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483482</v>
+        <v>483205</v>
       </c>
       <c r="R39" t="n">
-        <v>6833855</v>
+        <v>6834490</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469131</v>
+        <v>121469130</v>
       </c>
       <c r="B40" t="n">
         <v>78607</v>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483261</v>
+        <v>483307</v>
       </c>
       <c r="R40" t="n">
-        <v>6834030</v>
+        <v>6833983</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469096</v>
+        <v>121469347</v>
       </c>
       <c r="B41" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4709,21 +4709,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483058</v>
+        <v>483261</v>
       </c>
       <c r="R41" t="n">
-        <v>6833926</v>
+        <v>6834535</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469103</v>
+        <v>121469124</v>
       </c>
       <c r="B42" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,21 +4811,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483145</v>
+        <v>482865</v>
       </c>
       <c r="R42" t="n">
-        <v>6834394</v>
+        <v>6834254</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469149</v>
+        <v>121469335</v>
       </c>
       <c r="B43" t="n">
-        <v>78252</v>
+        <v>79225</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483268</v>
+        <v>483483</v>
       </c>
       <c r="R43" t="n">
-        <v>6834459</v>
+        <v>6833854</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469156</v>
+        <v>121465189</v>
       </c>
       <c r="B44" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,37 +5015,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>482876</v>
+        <v>483204</v>
       </c>
       <c r="R44" t="n">
-        <v>6834258</v>
+        <v>6833925</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5072,9 +5072,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5089,22 +5099,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469069</v>
+        <v>121469095</v>
       </c>
       <c r="B45" t="n">
-        <v>79196</v>
+        <v>78344</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,21 +5127,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483031</v>
+        <v>482925</v>
       </c>
       <c r="R45" t="n">
-        <v>6834458</v>
+        <v>6833909</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469070</v>
+        <v>121469154</v>
       </c>
       <c r="B46" t="n">
-        <v>79196</v>
+        <v>78252</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5229,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483031</v>
+        <v>483081</v>
       </c>
       <c r="R46" t="n">
-        <v>6834425</v>
+        <v>6834496</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121465556</v>
+        <v>121469147</v>
       </c>
       <c r="B47" t="n">
-        <v>78344</v>
+        <v>78252</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,37 +5331,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483536</v>
+        <v>483181</v>
       </c>
       <c r="R47" t="n">
-        <v>6833990</v>
+        <v>6834299</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5395,22 +5405,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121465160</v>
+        <v>121469120</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,21 +5433,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5447,13 +5457,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483115</v>
+        <v>483153</v>
       </c>
       <c r="R48" t="n">
-        <v>6833942</v>
+        <v>6834504</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5480,19 +5490,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5507,22 +5507,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469139</v>
+        <v>121469119</v>
       </c>
       <c r="B49" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483149</v>
+        <v>483265</v>
       </c>
       <c r="R49" t="n">
-        <v>6834501</v>
+        <v>6834572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469116</v>
+        <v>121469070</v>
       </c>
       <c r="B50" t="n">
-        <v>78343</v>
+        <v>79196</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483484</v>
+        <v>483031</v>
       </c>
       <c r="R50" t="n">
-        <v>6833901</v>
+        <v>6834425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469120</v>
+        <v>121466253</v>
       </c>
       <c r="B51" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,37 +5739,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483153</v>
+        <v>483464</v>
       </c>
       <c r="R51" t="n">
-        <v>6834504</v>
+        <v>6833910</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5813,22 +5813,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469335</v>
+        <v>121469099</v>
       </c>
       <c r="B52" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483483</v>
+        <v>483482</v>
       </c>
       <c r="R52" t="n">
-        <v>6833854</v>
+        <v>6833855</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469137</v>
+        <v>121469150</v>
       </c>
       <c r="B53" t="n">
-        <v>78607</v>
+        <v>78252</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,21 +5943,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483198</v>
+        <v>483294</v>
       </c>
       <c r="R53" t="n">
-        <v>6834476</v>
+        <v>6834475</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469112</v>
+        <v>121469139</v>
       </c>
       <c r="B54" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483408</v>
+        <v>483149</v>
       </c>
       <c r="R54" t="n">
-        <v>6833852</v>
+        <v>6834501</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,7 +6131,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469152</v>
+        <v>121469149</v>
       </c>
       <c r="B55" t="n">
         <v>78252</v>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483169</v>
+        <v>483268</v>
       </c>
       <c r="R55" t="n">
-        <v>6834491</v>
+        <v>6834459</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469115</v>
+        <v>121469152</v>
       </c>
       <c r="B56" t="n">
-        <v>78343</v>
+        <v>78252</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6249,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483445</v>
+        <v>483169</v>
       </c>
       <c r="R56" t="n">
-        <v>6833857</v>
+        <v>6834491</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469158</v>
+        <v>121465615</v>
       </c>
       <c r="B57" t="n">
-        <v>77991</v>
+        <v>78607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,34 +6351,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>482967</v>
+        <v>483179</v>
       </c>
       <c r="R57" t="n">
-        <v>6834339</v>
+        <v>6833973</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,9 +6408,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,22 +6435,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469342</v>
+        <v>121465604</v>
       </c>
       <c r="B58" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,37 +6463,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483160</v>
+        <v>483179</v>
       </c>
       <c r="R58" t="n">
-        <v>6834377</v>
+        <v>6833973</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6510,9 +6520,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6527,22 +6547,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469349</v>
+        <v>121465664</v>
       </c>
       <c r="B59" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,37 +6575,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483065</v>
+        <v>483498</v>
       </c>
       <c r="R59" t="n">
-        <v>6834469</v>
+        <v>6834031</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6629,19 +6649,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121467007</v>
+        <v>121465603</v>
       </c>
       <c r="B60" t="n">
         <v>78344</v>
@@ -6677,17 +6697,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483082</v>
+        <v>483561</v>
       </c>
       <c r="R60" t="n">
-        <v>6834003</v>
+        <v>6833992</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6716,7 +6736,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6726,7 +6746,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6741,22 +6761,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469148</v>
+        <v>121469103</v>
       </c>
       <c r="B61" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6769,21 +6789,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6793,10 +6813,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483160</v>
+        <v>483145</v>
       </c>
       <c r="R61" t="n">
-        <v>6834438</v>
+        <v>6834394</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,10 +6875,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469125</v>
+        <v>121469069</v>
       </c>
       <c r="B62" t="n">
-        <v>78343</v>
+        <v>79196</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6871,21 +6891,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6895,10 +6915,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483307</v>
+        <v>483031</v>
       </c>
       <c r="R62" t="n">
-        <v>6833983</v>
+        <v>6834458</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,10 +6977,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469126</v>
+        <v>121469337</v>
       </c>
       <c r="B63" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6973,21 +6993,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6997,10 +7017,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483476</v>
+        <v>483413</v>
       </c>
       <c r="R63" t="n">
-        <v>6834017</v>
+        <v>6834033</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7059,10 +7079,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469154</v>
+        <v>121469340</v>
       </c>
       <c r="B64" t="n">
-        <v>78252</v>
+        <v>79225</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7075,21 +7095,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7099,10 +7119,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483081</v>
+        <v>483211</v>
       </c>
       <c r="R64" t="n">
-        <v>6834496</v>
+        <v>6834254</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,10 +7181,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469337</v>
+        <v>121469097</v>
       </c>
       <c r="B65" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7177,21 +7197,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7201,10 +7221,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483413</v>
+        <v>483408</v>
       </c>
       <c r="R65" t="n">
-        <v>6834033</v>
+        <v>6833852</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,10 +7283,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469348</v>
+        <v>121469143</v>
       </c>
       <c r="B66" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7279,21 +7299,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7303,10 +7323,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483153</v>
+        <v>483038</v>
       </c>
       <c r="R66" t="n">
-        <v>6834505</v>
+        <v>6834461</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7365,10 +7385,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469101</v>
+        <v>121469155</v>
       </c>
       <c r="B67" t="n">
-        <v>78344</v>
+        <v>78252</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7381,21 +7401,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7405,10 +7425,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483168</v>
+        <v>482892</v>
       </c>
       <c r="R67" t="n">
-        <v>6834333</v>
+        <v>6834282</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,10 +7487,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121465189</v>
+        <v>121469140</v>
       </c>
       <c r="B68" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,37 +7503,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483204</v>
+        <v>483106</v>
       </c>
       <c r="R68" t="n">
-        <v>6833925</v>
+        <v>6834495</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7540,19 +7560,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7567,19 +7577,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469333</v>
+        <v>121469348</v>
       </c>
       <c r="B69" t="n">
         <v>79225</v>
@@ -7619,10 +7629,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483059</v>
+        <v>483153</v>
       </c>
       <c r="R69" t="n">
-        <v>6833927</v>
+        <v>6834505</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7691,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469110</v>
+        <v>121469100</v>
       </c>
       <c r="B70" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7697,21 +7707,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7721,10 +7731,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483144</v>
+        <v>483211</v>
       </c>
       <c r="R70" t="n">
-        <v>6833875</v>
+        <v>6834254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,10 +7793,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121467022</v>
+        <v>121469351</v>
       </c>
       <c r="B71" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7799,21 +7809,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7823,13 +7833,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483082</v>
+        <v>482864</v>
       </c>
       <c r="R71" t="n">
-        <v>6834003</v>
+        <v>6834255</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7856,19 +7866,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7883,22 +7883,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469128</v>
+        <v>121467022</v>
       </c>
       <c r="B72" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7911,21 +7911,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483524</v>
+        <v>483082</v>
       </c>
       <c r="R72" t="n">
-        <v>6834071</v>
+        <v>6834003</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7968,9 +7968,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7985,22 +7995,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469338</v>
+        <v>121469116</v>
       </c>
       <c r="B73" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8013,21 +8023,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8037,10 +8047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483246</v>
+        <v>483484</v>
       </c>
       <c r="R73" t="n">
-        <v>6834122</v>
+        <v>6833901</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,10 +8109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469117</v>
+        <v>121469132</v>
       </c>
       <c r="B74" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,21 +8125,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8139,10 +8149,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483119</v>
+        <v>483255</v>
       </c>
       <c r="R74" t="n">
-        <v>6834405</v>
+        <v>6834077</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,10 +8211,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469108</v>
+        <v>121469343</v>
       </c>
       <c r="B75" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8227,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8251,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>482925</v>
+        <v>483155</v>
       </c>
       <c r="R75" t="n">
-        <v>6833910</v>
+        <v>6834382</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8313,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469157</v>
+        <v>121469339</v>
       </c>
       <c r="B76" t="n">
-        <v>77991</v>
+        <v>79225</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8329,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,10 +8353,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483143</v>
+        <v>483213</v>
       </c>
       <c r="R76" t="n">
-        <v>6833875</v>
+        <v>6834252</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,7 +8415,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469133</v>
+        <v>121469142</v>
       </c>
       <c r="B77" t="n">
         <v>78607</v>
@@ -8445,10 +8455,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483241</v>
+        <v>483076</v>
       </c>
       <c r="R77" t="n">
-        <v>6834112</v>
+        <v>6834476</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8517,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469130</v>
+        <v>121467080</v>
       </c>
       <c r="B78" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8523,37 +8533,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483307</v>
+        <v>483038</v>
       </c>
       <c r="R78" t="n">
-        <v>6833983</v>
+        <v>6834006</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8597,22 +8607,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121465202</v>
+        <v>121469131</v>
       </c>
       <c r="B79" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8625,37 +8635,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483084</v>
+        <v>483261</v>
       </c>
       <c r="R79" t="n">
-        <v>6833930</v>
+        <v>6834030</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8682,19 +8692,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8709,22 +8709,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121465664</v>
+        <v>121469134</v>
       </c>
       <c r="B80" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8737,37 +8737,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483498</v>
+        <v>483277</v>
       </c>
       <c r="R80" t="n">
-        <v>6834031</v>
+        <v>6834451</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8811,22 +8811,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469132</v>
+        <v>121469106</v>
       </c>
       <c r="B81" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8839,21 +8839,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483255</v>
+        <v>482967</v>
       </c>
       <c r="R81" t="n">
-        <v>6834077</v>
+        <v>6834340</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8925,10 +8925,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469071</v>
+        <v>121469096</v>
       </c>
       <c r="B82" t="n">
-        <v>57507</v>
+        <v>78344</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8941,21 +8941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483265</v>
+        <v>483058</v>
       </c>
       <c r="R82" t="n">
-        <v>6834571</v>
+        <v>6833926</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9027,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469100</v>
+        <v>121469114</v>
       </c>
       <c r="B83" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9043,21 +9043,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483211</v>
+        <v>483434</v>
       </c>
       <c r="R83" t="n">
-        <v>6834254</v>
+        <v>6833855</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,7 +9129,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469134</v>
+        <v>121469126</v>
       </c>
       <c r="B84" t="n">
         <v>78607</v>
@@ -9169,10 +9169,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483277</v>
+        <v>483476</v>
       </c>
       <c r="R84" t="n">
-        <v>6834451</v>
+        <v>6834017</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9231,10 +9231,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469350</v>
+        <v>121469105</v>
       </c>
       <c r="B85" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,21 +9247,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483033</v>
+        <v>483153</v>
       </c>
       <c r="R85" t="n">
-        <v>6834458</v>
+        <v>6834504</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9333,10 +9333,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469339</v>
+        <v>121469156</v>
       </c>
       <c r="B86" t="n">
-        <v>79225</v>
+        <v>78252</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9349,21 +9349,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483213</v>
+        <v>482876</v>
       </c>
       <c r="R86" t="n">
-        <v>6834252</v>
+        <v>6834258</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469097</v>
+        <v>121469148</v>
       </c>
       <c r="B87" t="n">
-        <v>78344</v>
+        <v>78252</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9451,21 +9451,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483408</v>
+        <v>483160</v>
       </c>
       <c r="R87" t="n">
-        <v>6833852</v>
+        <v>6834438</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9537,10 +9537,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469155</v>
+        <v>121469157</v>
       </c>
       <c r="B88" t="n">
-        <v>78252</v>
+        <v>77991</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9553,21 +9553,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482892</v>
+        <v>483143</v>
       </c>
       <c r="R88" t="n">
-        <v>6834282</v>
+        <v>6833875</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9639,7 +9639,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469336</v>
+        <v>121469344</v>
       </c>
       <c r="B89" t="n">
         <v>79225</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483492</v>
+        <v>483119</v>
       </c>
       <c r="R89" t="n">
-        <v>6834084</v>
+        <v>6834405</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469124</v>
+        <v>121467007</v>
       </c>
       <c r="B90" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9757,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,13 +9781,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482865</v>
+        <v>483082</v>
       </c>
       <c r="R90" t="n">
-        <v>6834254</v>
+        <v>6834003</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9814,9 +9814,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9831,22 +9841,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469127</v>
+        <v>121469146</v>
       </c>
       <c r="B91" t="n">
-        <v>78607</v>
+        <v>78252</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9859,21 +9869,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9883,10 +9893,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483514</v>
+        <v>483260</v>
       </c>
       <c r="R91" t="n">
-        <v>6834064</v>
+        <v>6834060</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9945,7 +9955,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469341</v>
+        <v>121469345</v>
       </c>
       <c r="B92" t="n">
         <v>79225</v>
@@ -9985,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483181</v>
+        <v>483210</v>
       </c>
       <c r="R92" t="n">
-        <v>6834299</v>
+        <v>6834457</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,10 +10057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469344</v>
+        <v>121469137</v>
       </c>
       <c r="B93" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10063,21 +10073,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10087,10 +10097,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483119</v>
+        <v>483198</v>
       </c>
       <c r="R93" t="n">
-        <v>6834405</v>
+        <v>6834476</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10149,10 +10159,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121465603</v>
+        <v>121469158</v>
       </c>
       <c r="B94" t="n">
-        <v>78344</v>
+        <v>77991</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,37 +10175,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483561</v>
+        <v>482967</v>
       </c>
       <c r="R94" t="n">
-        <v>6833992</v>
+        <v>6834339</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10222,19 +10232,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10249,22 +10249,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469145</v>
+        <v>121469122</v>
       </c>
       <c r="B95" t="n">
-        <v>78252</v>
+        <v>78343</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,21 +10277,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483387</v>
+        <v>482967</v>
       </c>
       <c r="R95" t="n">
-        <v>6833994</v>
+        <v>6834340</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10363,7 +10363,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469102</v>
+        <v>121465556</v>
       </c>
       <c r="B96" t="n">
         <v>78344</v>
@@ -10399,17 +10399,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483161</v>
+        <v>483536</v>
       </c>
       <c r="R96" t="n">
-        <v>6834377</v>
+        <v>6833990</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10453,22 +10453,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121466253</v>
+        <v>121469071</v>
       </c>
       <c r="B97" t="n">
-        <v>78344</v>
+        <v>57507</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,37 +10481,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483464</v>
+        <v>483265</v>
       </c>
       <c r="R97" t="n">
-        <v>6833910</v>
+        <v>6834571</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465991</v>
+        <v>121465426</v>
       </c>
       <c r="B98" t="n">
-        <v>79717</v>
+        <v>78344</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,25 +10579,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483306</v>
+        <v>483209</v>
       </c>
       <c r="R98" t="n">
-        <v>6834009</v>
+        <v>6833990</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465052</v>
+        <v>121465412</v>
       </c>
       <c r="B99" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>482987</v>
+        <v>483177</v>
       </c>
       <c r="R99" t="n">
-        <v>6833950</v>
+        <v>6833971</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,7 +10791,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121465426</v>
+        <v>121464931</v>
       </c>
       <c r="B100" t="n">
         <v>78344</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483209</v>
+        <v>482985</v>
       </c>
       <c r="R100" t="n">
-        <v>6833990</v>
+        <v>6833943</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465234</v>
+        <v>121466096</v>
       </c>
       <c r="B101" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483201</v>
+        <v>483350</v>
       </c>
       <c r="R101" t="n">
-        <v>6833961</v>
+        <v>6834071</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121466096</v>
+        <v>121465234</v>
       </c>
       <c r="B102" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483350</v>
+        <v>483201</v>
       </c>
       <c r="R102" t="n">
-        <v>6834071</v>
+        <v>6833961</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121466059</v>
+        <v>121465017</v>
       </c>
       <c r="B103" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483350</v>
+        <v>482987</v>
       </c>
       <c r="R103" t="n">
-        <v>6834071</v>
+        <v>6833950</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465024</v>
+        <v>121465052</v>
       </c>
       <c r="B104" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465017</v>
+        <v>121465266</v>
       </c>
       <c r="B105" t="n">
-        <v>78343</v>
+        <v>79196</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>482987</v>
+        <v>483204</v>
       </c>
       <c r="R105" t="n">
-        <v>6833950</v>
+        <v>6833967</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11463,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465266</v>
+        <v>121465991</v>
       </c>
       <c r="B106" t="n">
-        <v>79196</v>
+        <v>79717</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11475,25 +11475,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483204</v>
+        <v>483306</v>
       </c>
       <c r="R106" t="n">
-        <v>6833967</v>
+        <v>6834009</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121465412</v>
+        <v>121465024</v>
       </c>
       <c r="B107" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483177</v>
+        <v>482987</v>
       </c>
       <c r="R107" t="n">
-        <v>6833971</v>
+        <v>6833950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121464931</v>
+        <v>121466059</v>
       </c>
       <c r="B108" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>482985</v>
+        <v>483350</v>
       </c>
       <c r="R108" t="n">
-        <v>6833943</v>
+        <v>6834071</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469136</v>
+        <v>121469104</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483198</v>
+        <v>483265</v>
       </c>
       <c r="R21" t="n">
-        <v>6834484</v>
+        <v>6834572</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121465159</v>
+        <v>121469107</v>
       </c>
       <c r="B22" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483204</v>
+        <v>482865</v>
       </c>
       <c r="R22" t="n">
-        <v>6833925</v>
+        <v>6834255</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,19 +2808,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,22 +2825,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469349</v>
+        <v>121469102</v>
       </c>
       <c r="B23" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483065</v>
+        <v>483161</v>
       </c>
       <c r="R23" t="n">
-        <v>6834469</v>
+        <v>6834377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469118</v>
+        <v>121469136</v>
       </c>
       <c r="B24" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483210</v>
+        <v>483198</v>
       </c>
       <c r="R24" t="n">
-        <v>6834456</v>
+        <v>6834484</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469127</v>
+        <v>121465159</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,37 +3057,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483514</v>
+        <v>483204</v>
       </c>
       <c r="R25" t="n">
-        <v>6834064</v>
+        <v>6833925</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3124,9 +3114,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3141,22 +3141,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469104</v>
+        <v>121469349</v>
       </c>
       <c r="B26" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483265</v>
+        <v>483065</v>
       </c>
       <c r="R26" t="n">
-        <v>6834572</v>
+        <v>6834469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469107</v>
+        <v>121469118</v>
       </c>
       <c r="B27" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482865</v>
+        <v>483210</v>
       </c>
       <c r="R27" t="n">
-        <v>6834255</v>
+        <v>6834456</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469102</v>
+        <v>121469127</v>
       </c>
       <c r="B28" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483161</v>
+        <v>483514</v>
       </c>
       <c r="R28" t="n">
-        <v>6834377</v>
+        <v>6834064</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469125</v>
+        <v>121469145</v>
       </c>
       <c r="B29" t="n">
-        <v>78343</v>
+        <v>78252</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483307</v>
+        <v>483387</v>
       </c>
       <c r="R29" t="n">
-        <v>6833983</v>
+        <v>6833994</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469115</v>
+        <v>121469125</v>
       </c>
       <c r="B30" t="n">
         <v>78343</v>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483445</v>
+        <v>483307</v>
       </c>
       <c r="R30" t="n">
-        <v>6833857</v>
+        <v>6833983</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121465246</v>
+        <v>121469115</v>
       </c>
       <c r="B31" t="n">
         <v>78343</v>
@@ -3699,17 +3699,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483187</v>
+        <v>483445</v>
       </c>
       <c r="R31" t="n">
-        <v>6833888</v>
+        <v>6833857</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3736,19 +3736,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,19 +3753,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469110</v>
+        <v>121465246</v>
       </c>
       <c r="B32" t="n">
         <v>78343</v>
@@ -3811,17 +3801,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483144</v>
+        <v>483187</v>
       </c>
       <c r="R32" t="n">
-        <v>6833875</v>
+        <v>6833888</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3848,9 +3838,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,19 +3865,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469112</v>
+        <v>121469110</v>
       </c>
       <c r="B33" t="n">
         <v>78343</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483408</v>
+        <v>483144</v>
       </c>
       <c r="R33" t="n">
-        <v>6833852</v>
+        <v>6833875</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469101</v>
+        <v>121469112</v>
       </c>
       <c r="B34" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483168</v>
+        <v>483408</v>
       </c>
       <c r="R34" t="n">
-        <v>6834333</v>
+        <v>6833852</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469145</v>
+        <v>121469101</v>
       </c>
       <c r="B35" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483387</v>
+        <v>483168</v>
       </c>
       <c r="R35" t="n">
-        <v>6833994</v>
+        <v>6834333</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121465615</v>
+        <v>121465603</v>
       </c>
       <c r="B57" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483179</v>
+        <v>483561</v>
       </c>
       <c r="R57" t="n">
-        <v>6833973</v>
+        <v>6833992</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6435,22 +6435,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121465604</v>
+        <v>121469103</v>
       </c>
       <c r="B58" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6463,37 +6463,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483179</v>
+        <v>483145</v>
       </c>
       <c r="R58" t="n">
-        <v>6833973</v>
+        <v>6834394</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6520,19 +6520,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6547,22 +6537,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121465664</v>
+        <v>121469069</v>
       </c>
       <c r="B59" t="n">
-        <v>78343</v>
+        <v>79196</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,37 +6565,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483498</v>
+        <v>483031</v>
       </c>
       <c r="R59" t="n">
-        <v>6834031</v>
+        <v>6834458</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6649,22 +6639,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121465603</v>
+        <v>121465615</v>
       </c>
       <c r="B60" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6667,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,13 +6691,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483561</v>
+        <v>483179</v>
       </c>
       <c r="R60" t="n">
-        <v>6833992</v>
+        <v>6833973</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6736,7 +6726,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6746,7 +6736,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6761,22 +6751,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469103</v>
+        <v>121465604</v>
       </c>
       <c r="B61" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6789,37 +6779,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483145</v>
+        <v>483179</v>
       </c>
       <c r="R61" t="n">
-        <v>6834394</v>
+        <v>6833973</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6846,9 +6836,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6863,22 +6863,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469069</v>
+        <v>121465664</v>
       </c>
       <c r="B62" t="n">
-        <v>79196</v>
+        <v>78343</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483031</v>
+        <v>483498</v>
       </c>
       <c r="R62" t="n">
-        <v>6834458</v>
+        <v>6834031</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6965,12 +6965,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469155</v>
+        <v>121469140</v>
       </c>
       <c r="B67" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7401,21 +7401,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>482892</v>
+        <v>483106</v>
       </c>
       <c r="R67" t="n">
-        <v>6834282</v>
+        <v>6834495</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7487,10 +7487,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469140</v>
+        <v>121469348</v>
       </c>
       <c r="B68" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483106</v>
+        <v>483153</v>
       </c>
       <c r="R68" t="n">
-        <v>6834495</v>
+        <v>6834505</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7589,10 +7589,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469348</v>
+        <v>121469155</v>
       </c>
       <c r="B69" t="n">
-        <v>79225</v>
+        <v>78252</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483153</v>
+        <v>482892</v>
       </c>
       <c r="R69" t="n">
-        <v>6834505</v>
+        <v>6834282</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469100</v>
+        <v>121469132</v>
       </c>
       <c r="B70" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483211</v>
+        <v>483255</v>
       </c>
       <c r="R70" t="n">
-        <v>6834254</v>
+        <v>6834077</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469132</v>
+        <v>121469100</v>
       </c>
       <c r="B74" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483255</v>
+        <v>483211</v>
       </c>
       <c r="R74" t="n">
-        <v>6834077</v>
+        <v>6834254</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8211,10 +8211,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469343</v>
+        <v>121467080</v>
       </c>
       <c r="B75" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8227,37 +8227,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483155</v>
+        <v>483038</v>
       </c>
       <c r="R75" t="n">
-        <v>6834382</v>
+        <v>6834006</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8301,19 +8301,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469339</v>
+        <v>121469343</v>
       </c>
       <c r="B76" t="n">
         <v>79225</v>
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483213</v>
+        <v>483155</v>
       </c>
       <c r="R76" t="n">
-        <v>6834252</v>
+        <v>6834382</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8415,10 +8415,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469142</v>
+        <v>121469339</v>
       </c>
       <c r="B77" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8431,21 +8431,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483076</v>
+        <v>483213</v>
       </c>
       <c r="R77" t="n">
-        <v>6834476</v>
+        <v>6834252</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121467080</v>
+        <v>121469142</v>
       </c>
       <c r="B78" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8533,37 +8533,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483038</v>
+        <v>483076</v>
       </c>
       <c r="R78" t="n">
-        <v>6834006</v>
+        <v>6834476</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8607,12 +8607,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9853,10 +9853,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469146</v>
+        <v>121469345</v>
       </c>
       <c r="B91" t="n">
-        <v>78252</v>
+        <v>79225</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9869,21 +9869,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483260</v>
+        <v>483210</v>
       </c>
       <c r="R91" t="n">
-        <v>6834060</v>
+        <v>6834457</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9955,10 +9955,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469345</v>
+        <v>121469146</v>
       </c>
       <c r="B92" t="n">
-        <v>79225</v>
+        <v>78252</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483210</v>
+        <v>483260</v>
       </c>
       <c r="R92" t="n">
-        <v>6834457</v>
+        <v>6834060</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -9027,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469114</v>
+        <v>121469156</v>
       </c>
       <c r="B83" t="n">
-        <v>78343</v>
+        <v>78252</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9043,21 +9043,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483434</v>
+        <v>482876</v>
       </c>
       <c r="R83" t="n">
-        <v>6833855</v>
+        <v>6834258</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,10 +9129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469126</v>
+        <v>121469114</v>
       </c>
       <c r="B84" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9145,21 +9145,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9169,10 +9169,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483476</v>
+        <v>483434</v>
       </c>
       <c r="R84" t="n">
-        <v>6834017</v>
+        <v>6833855</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9231,10 +9231,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469105</v>
+        <v>121469126</v>
       </c>
       <c r="B85" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,21 +9247,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483153</v>
+        <v>483476</v>
       </c>
       <c r="R85" t="n">
-        <v>6834504</v>
+        <v>6834017</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9333,10 +9333,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469156</v>
+        <v>121469105</v>
       </c>
       <c r="B86" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9349,21 +9349,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482876</v>
+        <v>483153</v>
       </c>
       <c r="R86" t="n">
-        <v>6834258</v>
+        <v>6834504</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326737</v>
+        <v>121326179</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483242</v>
+        <v>482925</v>
       </c>
       <c r="R2" t="n">
-        <v>6834570</v>
+        <v>6834028</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326800</v>
+        <v>121326921</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483205</v>
+        <v>483134</v>
       </c>
       <c r="R3" t="n">
-        <v>6834165</v>
+        <v>6833995</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326433</v>
+        <v>121326800</v>
       </c>
       <c r="B4" t="n">
-        <v>79196</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483040</v>
+        <v>483205</v>
       </c>
       <c r="R4" t="n">
-        <v>6834198</v>
+        <v>6834165</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326921</v>
+        <v>121326433</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483134</v>
+        <v>483040</v>
       </c>
       <c r="R5" t="n">
-        <v>6833995</v>
+        <v>6834198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326179</v>
+        <v>121326737</v>
       </c>
       <c r="B6" t="n">
-        <v>78344</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482925</v>
+        <v>483242</v>
       </c>
       <c r="R6" t="n">
-        <v>6834028</v>
+        <v>6834570</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
         <v>121326438</v>
       </c>
       <c r="B7" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>121326404</v>
       </c>
       <c r="B8" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121465160</v>
+        <v>121469127</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483115</v>
+        <v>483514</v>
       </c>
       <c r="R9" t="n">
-        <v>6833942</v>
+        <v>6834064</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,19 +1462,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469128</v>
+        <v>121469119</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483524</v>
+        <v>483265</v>
       </c>
       <c r="R10" t="n">
-        <v>6834071</v>
+        <v>6834572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121465202</v>
+        <v>121465604</v>
       </c>
       <c r="B11" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483084</v>
+        <v>483179</v>
       </c>
       <c r="R11" t="n">
-        <v>6833930</v>
+        <v>6833973</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1678,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469144</v>
+        <v>121469351</v>
       </c>
       <c r="B12" t="n">
-        <v>78252</v>
+        <v>79226</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483402</v>
+        <v>482864</v>
       </c>
       <c r="R12" t="n">
-        <v>6834000</v>
+        <v>6834255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469342</v>
+        <v>121467080</v>
       </c>
       <c r="B13" t="n">
-        <v>79225</v>
+        <v>78345</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,37 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483160</v>
+        <v>483038</v>
       </c>
       <c r="R13" t="n">
-        <v>6834377</v>
+        <v>6834006</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,22 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469098</v>
+        <v>121465603</v>
       </c>
       <c r="B14" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,17 +1945,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483445</v>
+        <v>483561</v>
       </c>
       <c r="R14" t="n">
-        <v>6833857</v>
+        <v>6833992</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1982,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469133</v>
+        <v>121469130</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483241</v>
+        <v>483307</v>
       </c>
       <c r="R15" t="n">
-        <v>6834112</v>
+        <v>6833983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469333</v>
+        <v>121469128</v>
       </c>
       <c r="B16" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483059</v>
+        <v>483524</v>
       </c>
       <c r="R16" t="n">
-        <v>6833927</v>
+        <v>6834071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469117</v>
+        <v>121469142</v>
       </c>
       <c r="B17" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483119</v>
+        <v>483076</v>
       </c>
       <c r="R17" t="n">
-        <v>6834405</v>
+        <v>6834476</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469334</v>
+        <v>121465615</v>
       </c>
       <c r="B18" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,34 +2343,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483084</v>
+        <v>483179</v>
       </c>
       <c r="R18" t="n">
-        <v>6833901</v>
+        <v>6833973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,9 +2400,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469108</v>
+        <v>121469125</v>
       </c>
       <c r="B19" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482925</v>
+        <v>483307</v>
       </c>
       <c r="R19" t="n">
-        <v>6833910</v>
+        <v>6833983</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469350</v>
+        <v>121469114</v>
       </c>
       <c r="B20" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483033</v>
+        <v>483434</v>
       </c>
       <c r="R20" t="n">
-        <v>6834458</v>
+        <v>6833855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469104</v>
+        <v>121469345</v>
       </c>
       <c r="B21" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483265</v>
+        <v>483210</v>
       </c>
       <c r="R21" t="n">
-        <v>6834572</v>
+        <v>6834457</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469107</v>
+        <v>121469101</v>
       </c>
       <c r="B22" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482865</v>
+        <v>483168</v>
       </c>
       <c r="R22" t="n">
-        <v>6834255</v>
+        <v>6834333</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469102</v>
+        <v>121469115</v>
       </c>
       <c r="B23" t="n">
         <v>78344</v>
@@ -2853,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483161</v>
+        <v>483445</v>
       </c>
       <c r="R23" t="n">
-        <v>6834377</v>
+        <v>6833857</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469136</v>
+        <v>121469110</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483198</v>
+        <v>483144</v>
       </c>
       <c r="R24" t="n">
-        <v>6834484</v>
+        <v>6833875</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121465159</v>
+        <v>121469116</v>
       </c>
       <c r="B25" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,17 +3087,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483204</v>
+        <v>483484</v>
       </c>
       <c r="R25" t="n">
-        <v>6833925</v>
+        <v>6833901</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3114,19 +3124,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3141,22 +3141,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469349</v>
+        <v>121469155</v>
       </c>
       <c r="B26" t="n">
-        <v>79225</v>
+        <v>78253</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483065</v>
+        <v>482892</v>
       </c>
       <c r="R26" t="n">
-        <v>6834469</v>
+        <v>6834282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469118</v>
+        <v>121469144</v>
       </c>
       <c r="B27" t="n">
-        <v>78343</v>
+        <v>78253</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483210</v>
+        <v>483402</v>
       </c>
       <c r="R27" t="n">
-        <v>6834456</v>
+        <v>6834000</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469127</v>
+        <v>121469097</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>78345</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483514</v>
+        <v>483408</v>
       </c>
       <c r="R28" t="n">
-        <v>6834064</v>
+        <v>6833852</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469145</v>
+        <v>121465189</v>
       </c>
       <c r="B29" t="n">
-        <v>78252</v>
+        <v>78345</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,37 +3475,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483387</v>
+        <v>483204</v>
       </c>
       <c r="R29" t="n">
-        <v>6833994</v>
+        <v>6833925</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3532,9 +3532,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3549,22 +3559,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469125</v>
+        <v>121469339</v>
       </c>
       <c r="B30" t="n">
-        <v>78343</v>
+        <v>79226</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3601,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483307</v>
+        <v>483213</v>
       </c>
       <c r="R30" t="n">
-        <v>6833983</v>
+        <v>6834252</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,10 +3673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469115</v>
+        <v>121469157</v>
       </c>
       <c r="B31" t="n">
-        <v>78343</v>
+        <v>77992</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3689,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3713,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483445</v>
+        <v>483143</v>
       </c>
       <c r="R31" t="n">
-        <v>6833857</v>
+        <v>6833875</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121465246</v>
+        <v>121469071</v>
       </c>
       <c r="B32" t="n">
-        <v>78343</v>
+        <v>57508</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,37 +3791,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483187</v>
+        <v>483265</v>
       </c>
       <c r="R32" t="n">
-        <v>6833888</v>
+        <v>6834571</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3838,19 +3848,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469110</v>
+        <v>121469139</v>
       </c>
       <c r="B33" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483144</v>
+        <v>483149</v>
       </c>
       <c r="R33" t="n">
-        <v>6833875</v>
+        <v>6834501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469112</v>
+        <v>121469134</v>
       </c>
       <c r="B34" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483408</v>
+        <v>483277</v>
       </c>
       <c r="R34" t="n">
-        <v>6833852</v>
+        <v>6834451</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469101</v>
+        <v>121465159</v>
       </c>
       <c r="B35" t="n">
         <v>78344</v>
@@ -4097,37 +4097,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483168</v>
+        <v>483204</v>
       </c>
       <c r="R35" t="n">
-        <v>6834333</v>
+        <v>6833925</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4154,9 +4154,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,22 +4181,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469336</v>
+        <v>121469343</v>
       </c>
       <c r="B36" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4223,10 +4233,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483492</v>
+        <v>483155</v>
       </c>
       <c r="R36" t="n">
-        <v>6834084</v>
+        <v>6834382</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4295,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469341</v>
+        <v>121469117</v>
       </c>
       <c r="B37" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4301,21 +4311,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4325,10 +4335,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483181</v>
+        <v>483119</v>
       </c>
       <c r="R37" t="n">
-        <v>6834299</v>
+        <v>6834405</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,10 +4397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469338</v>
+        <v>121465664</v>
       </c>
       <c r="B38" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4403,37 +4413,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483246</v>
+        <v>483498</v>
       </c>
       <c r="R38" t="n">
-        <v>6834122</v>
+        <v>6834031</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4477,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469135</v>
+        <v>121469344</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4505,21 +4515,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4539,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483205</v>
+        <v>483119</v>
       </c>
       <c r="R39" t="n">
-        <v>6834490</v>
+        <v>6834405</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,10 +4601,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469130</v>
+        <v>121469070</v>
       </c>
       <c r="B40" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,21 +4617,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483307</v>
+        <v>483031</v>
       </c>
       <c r="R40" t="n">
-        <v>6833983</v>
+        <v>6834425</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469347</v>
+        <v>121469102</v>
       </c>
       <c r="B41" t="n">
-        <v>79225</v>
+        <v>78345</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4709,21 +4719,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483261</v>
+        <v>483161</v>
       </c>
       <c r="R41" t="n">
-        <v>6834535</v>
+        <v>6834377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469124</v>
+        <v>121466253</v>
       </c>
       <c r="B42" t="n">
-        <v>78343</v>
+        <v>78345</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,37 +4821,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>482865</v>
+        <v>483464</v>
       </c>
       <c r="R42" t="n">
-        <v>6834254</v>
+        <v>6833910</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4885,22 +4895,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469335</v>
+        <v>121469108</v>
       </c>
       <c r="B43" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4923,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4947,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483483</v>
+        <v>482925</v>
       </c>
       <c r="R43" t="n">
-        <v>6833854</v>
+        <v>6833910</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +5009,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121465189</v>
+        <v>121469338</v>
       </c>
       <c r="B44" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,37 +5025,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483204</v>
+        <v>483246</v>
       </c>
       <c r="R44" t="n">
-        <v>6833925</v>
+        <v>6834122</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5072,19 +5082,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5099,22 +5099,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469095</v>
+        <v>121469347</v>
       </c>
       <c r="B45" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482925</v>
+        <v>483261</v>
       </c>
       <c r="R45" t="n">
-        <v>6833909</v>
+        <v>6834535</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469154</v>
+        <v>121469126</v>
       </c>
       <c r="B46" t="n">
-        <v>78252</v>
+        <v>78608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5229,21 +5229,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483081</v>
+        <v>483476</v>
       </c>
       <c r="R46" t="n">
-        <v>6834496</v>
+        <v>6834017</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469147</v>
+        <v>121469103</v>
       </c>
       <c r="B47" t="n">
-        <v>78252</v>
+        <v>78345</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,21 +5331,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483181</v>
+        <v>483145</v>
       </c>
       <c r="R47" t="n">
-        <v>6834299</v>
+        <v>6834394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469120</v>
+        <v>121469342</v>
       </c>
       <c r="B48" t="n">
-        <v>78343</v>
+        <v>79226</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,21 +5433,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483153</v>
+        <v>483160</v>
       </c>
       <c r="R48" t="n">
-        <v>6834504</v>
+        <v>6834377</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469119</v>
+        <v>121469335</v>
       </c>
       <c r="B49" t="n">
-        <v>78343</v>
+        <v>79226</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483265</v>
+        <v>483483</v>
       </c>
       <c r="R49" t="n">
-        <v>6834572</v>
+        <v>6833854</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469070</v>
+        <v>121467007</v>
       </c>
       <c r="B50" t="n">
-        <v>79196</v>
+        <v>78345</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,13 +5661,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483031</v>
+        <v>483082</v>
       </c>
       <c r="R50" t="n">
-        <v>6834425</v>
+        <v>6834003</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5694,9 +5694,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5711,22 +5721,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121466253</v>
+        <v>121469104</v>
       </c>
       <c r="B51" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5759,17 +5769,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483464</v>
+        <v>483265</v>
       </c>
       <c r="R51" t="n">
-        <v>6833910</v>
+        <v>6834572</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5813,22 +5823,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469099</v>
+        <v>121469095</v>
       </c>
       <c r="B52" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,10 +5875,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483482</v>
+        <v>482925</v>
       </c>
       <c r="R52" t="n">
-        <v>6833855</v>
+        <v>6833909</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5930,7 +5940,7 @@
         <v>121469150</v>
       </c>
       <c r="B53" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6029,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469139</v>
+        <v>121469154</v>
       </c>
       <c r="B54" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483149</v>
+        <v>483081</v>
       </c>
       <c r="R54" t="n">
-        <v>6834501</v>
+        <v>6834496</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469149</v>
+        <v>121469146</v>
       </c>
       <c r="B55" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6171,10 +6181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483268</v>
+        <v>483260</v>
       </c>
       <c r="R55" t="n">
-        <v>6834459</v>
+        <v>6834060</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469152</v>
+        <v>121469122</v>
       </c>
       <c r="B56" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6259,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6283,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483169</v>
+        <v>482967</v>
       </c>
       <c r="R56" t="n">
-        <v>6834491</v>
+        <v>6834340</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,7 +6345,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121465603</v>
+        <v>121465246</v>
       </c>
       <c r="B57" t="n">
         <v>78344</v>
@@ -6351,21 +6361,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6385,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483561</v>
+        <v>483187</v>
       </c>
       <c r="R57" t="n">
-        <v>6833992</v>
+        <v>6833888</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -6410,7 +6420,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6420,7 +6430,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6447,10 +6457,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469103</v>
+        <v>121469341</v>
       </c>
       <c r="B58" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6463,21 +6473,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6487,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483145</v>
+        <v>483181</v>
       </c>
       <c r="R58" t="n">
-        <v>6834394</v>
+        <v>6834299</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6549,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469069</v>
+        <v>121469112</v>
       </c>
       <c r="B59" t="n">
-        <v>79196</v>
+        <v>78344</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6565,21 +6575,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6589,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483031</v>
+        <v>483408</v>
       </c>
       <c r="R59" t="n">
-        <v>6834458</v>
+        <v>6833852</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121465615</v>
+        <v>121469069</v>
       </c>
       <c r="B60" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6667,34 +6677,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483179</v>
+        <v>483031</v>
       </c>
       <c r="R60" t="n">
-        <v>6833973</v>
+        <v>6834458</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6724,19 +6734,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6751,22 +6751,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121465604</v>
+        <v>121469100</v>
       </c>
       <c r="B61" t="n">
-        <v>78343</v>
+        <v>78345</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,37 +6779,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483179</v>
+        <v>483211</v>
       </c>
       <c r="R61" t="n">
-        <v>6833973</v>
+        <v>6834254</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6836,19 +6836,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6863,22 +6853,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121465664</v>
+        <v>121469096</v>
       </c>
       <c r="B62" t="n">
-        <v>78343</v>
+        <v>78345</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6891,37 +6881,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483498</v>
+        <v>483058</v>
       </c>
       <c r="R62" t="n">
-        <v>6834031</v>
+        <v>6833926</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6965,22 +6955,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469337</v>
+        <v>121469107</v>
       </c>
       <c r="B63" t="n">
-        <v>79225</v>
+        <v>78345</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6993,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7017,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483413</v>
+        <v>482865</v>
       </c>
       <c r="R63" t="n">
-        <v>6834033</v>
+        <v>6834255</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7079,10 +7069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469340</v>
+        <v>121465202</v>
       </c>
       <c r="B64" t="n">
-        <v>79225</v>
+        <v>78253</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7095,37 +7085,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483211</v>
+        <v>483084</v>
       </c>
       <c r="R64" t="n">
-        <v>6834254</v>
+        <v>6833930</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7152,9 +7142,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7169,22 +7169,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469097</v>
+        <v>121469336</v>
       </c>
       <c r="B65" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7197,21 +7197,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483408</v>
+        <v>483492</v>
       </c>
       <c r="R65" t="n">
-        <v>6833852</v>
+        <v>6834084</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7283,10 +7283,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469143</v>
+        <v>121469120</v>
       </c>
       <c r="B66" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7299,21 +7299,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483038</v>
+        <v>483153</v>
       </c>
       <c r="R66" t="n">
-        <v>6834461</v>
+        <v>6834504</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7388,7 +7388,7 @@
         <v>121469140</v>
       </c>
       <c r="B67" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7487,10 +7487,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469348</v>
+        <v>121469132</v>
       </c>
       <c r="B68" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483153</v>
+        <v>483255</v>
       </c>
       <c r="R68" t="n">
-        <v>6834505</v>
+        <v>6834077</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7589,10 +7589,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469155</v>
+        <v>121469145</v>
       </c>
       <c r="B69" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>482892</v>
+        <v>483387</v>
       </c>
       <c r="R69" t="n">
-        <v>6834282</v>
+        <v>6833994</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469132</v>
+        <v>121469149</v>
       </c>
       <c r="B70" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483255</v>
+        <v>483268</v>
       </c>
       <c r="R70" t="n">
-        <v>6834077</v>
+        <v>6834459</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469351</v>
+        <v>121469106</v>
       </c>
       <c r="B71" t="n">
-        <v>79225</v>
+        <v>78345</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7809,21 +7809,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>482864</v>
+        <v>482967</v>
       </c>
       <c r="R71" t="n">
-        <v>6834255</v>
+        <v>6834340</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7895,10 +7895,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121467022</v>
+        <v>121469147</v>
       </c>
       <c r="B72" t="n">
-        <v>78343</v>
+        <v>78253</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7911,21 +7911,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483082</v>
+        <v>483181</v>
       </c>
       <c r="R72" t="n">
-        <v>6834003</v>
+        <v>6834299</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7968,19 +7968,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7995,22 +7985,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469116</v>
+        <v>121469133</v>
       </c>
       <c r="B73" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8023,21 +8013,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8047,10 +8037,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483484</v>
+        <v>483241</v>
       </c>
       <c r="R73" t="n">
-        <v>6833901</v>
+        <v>6834112</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8109,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469100</v>
+        <v>121469131</v>
       </c>
       <c r="B74" t="n">
-        <v>78344</v>
+        <v>78608</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8125,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8149,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483211</v>
+        <v>483261</v>
       </c>
       <c r="R74" t="n">
-        <v>6834254</v>
+        <v>6834030</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8211,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121467080</v>
+        <v>121469348</v>
       </c>
       <c r="B75" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8227,37 +8217,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483038</v>
+        <v>483153</v>
       </c>
       <c r="R75" t="n">
-        <v>6834006</v>
+        <v>6834505</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8301,22 +8291,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469343</v>
+        <v>121467022</v>
       </c>
       <c r="B76" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8329,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8353,13 +8343,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483155</v>
+        <v>483082</v>
       </c>
       <c r="R76" t="n">
-        <v>6834382</v>
+        <v>6834003</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8386,9 +8376,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8403,22 +8403,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469339</v>
+        <v>121469105</v>
       </c>
       <c r="B77" t="n">
-        <v>79225</v>
+        <v>78345</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8431,21 +8431,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483213</v>
+        <v>483153</v>
       </c>
       <c r="R77" t="n">
-        <v>6834252</v>
+        <v>6834504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469142</v>
+        <v>121465556</v>
       </c>
       <c r="B78" t="n">
-        <v>78607</v>
+        <v>78345</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8533,37 +8533,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483076</v>
+        <v>483536</v>
       </c>
       <c r="R78" t="n">
-        <v>6834476</v>
+        <v>6833990</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8607,22 +8607,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469131</v>
+        <v>121469349</v>
       </c>
       <c r="B79" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483261</v>
+        <v>483065</v>
       </c>
       <c r="R79" t="n">
-        <v>6834030</v>
+        <v>6834469</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8721,10 +8721,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469134</v>
+        <v>121469148</v>
       </c>
       <c r="B80" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483277</v>
+        <v>483160</v>
       </c>
       <c r="R80" t="n">
-        <v>6834451</v>
+        <v>6834438</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8823,10 +8823,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469106</v>
+        <v>121469152</v>
       </c>
       <c r="B81" t="n">
-        <v>78344</v>
+        <v>78253</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8839,21 +8839,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>482967</v>
+        <v>483169</v>
       </c>
       <c r="R81" t="n">
-        <v>6834340</v>
+        <v>6834491</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469096</v>
+        <v>121469124</v>
       </c>
       <c r="B82" t="n">
         <v>78344</v>
@@ -8941,21 +8941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483058</v>
+        <v>482865</v>
       </c>
       <c r="R82" t="n">
-        <v>6833926</v>
+        <v>6834254</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9027,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469156</v>
+        <v>121469350</v>
       </c>
       <c r="B83" t="n">
-        <v>78252</v>
+        <v>79226</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9043,21 +9043,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>482876</v>
+        <v>483033</v>
       </c>
       <c r="R83" t="n">
-        <v>6834258</v>
+        <v>6834458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,10 +9129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469114</v>
+        <v>121469099</v>
       </c>
       <c r="B84" t="n">
-        <v>78343</v>
+        <v>78345</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9145,21 +9145,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483434</v>
+        <v>483482</v>
       </c>
       <c r="R84" t="n">
         <v>6833855</v>
@@ -9231,10 +9231,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469126</v>
+        <v>121469337</v>
       </c>
       <c r="B85" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,21 +9247,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483476</v>
+        <v>483413</v>
       </c>
       <c r="R85" t="n">
-        <v>6834017</v>
+        <v>6834033</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9333,7 +9333,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469105</v>
+        <v>121469118</v>
       </c>
       <c r="B86" t="n">
         <v>78344</v>
@@ -9349,21 +9349,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483153</v>
+        <v>483210</v>
       </c>
       <c r="R86" t="n">
-        <v>6834504</v>
+        <v>6834456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469148</v>
+        <v>121469334</v>
       </c>
       <c r="B87" t="n">
-        <v>78252</v>
+        <v>79226</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9451,21 +9451,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483160</v>
+        <v>483084</v>
       </c>
       <c r="R87" t="n">
-        <v>6834438</v>
+        <v>6833901</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9537,10 +9537,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469157</v>
+        <v>121469098</v>
       </c>
       <c r="B88" t="n">
-        <v>77991</v>
+        <v>78345</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9553,21 +9553,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483143</v>
+        <v>483445</v>
       </c>
       <c r="R88" t="n">
-        <v>6833875</v>
+        <v>6833857</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9639,10 +9639,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469344</v>
+        <v>121465160</v>
       </c>
       <c r="B89" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,13 +9679,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483119</v>
+        <v>483115</v>
       </c>
       <c r="R89" t="n">
-        <v>6834405</v>
+        <v>6833942</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9712,9 +9712,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9729,22 +9739,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121467007</v>
+        <v>121469135</v>
       </c>
       <c r="B90" t="n">
-        <v>78344</v>
+        <v>78608</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9757,21 +9767,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,13 +9791,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483082</v>
+        <v>483205</v>
       </c>
       <c r="R90" t="n">
-        <v>6834003</v>
+        <v>6834490</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9814,19 +9824,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9841,22 +9841,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469345</v>
+        <v>121469143</v>
       </c>
       <c r="B91" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9869,21 +9869,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483210</v>
+        <v>483038</v>
       </c>
       <c r="R91" t="n">
-        <v>6834457</v>
+        <v>6834461</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9955,10 +9955,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469146</v>
+        <v>121469137</v>
       </c>
       <c r="B92" t="n">
-        <v>78252</v>
+        <v>78608</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483260</v>
+        <v>483198</v>
       </c>
       <c r="R92" t="n">
-        <v>6834060</v>
+        <v>6834476</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10057,10 +10057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469137</v>
+        <v>121469136</v>
       </c>
       <c r="B93" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>483198</v>
       </c>
       <c r="R93" t="n">
-        <v>6834476</v>
+        <v>6834484</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10159,10 +10159,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469158</v>
+        <v>121469156</v>
       </c>
       <c r="B94" t="n">
-        <v>77991</v>
+        <v>78253</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10175,21 +10175,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10199,10 +10199,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>482967</v>
+        <v>482876</v>
       </c>
       <c r="R94" t="n">
-        <v>6834339</v>
+        <v>6834258</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469122</v>
+        <v>121469333</v>
       </c>
       <c r="B95" t="n">
-        <v>78343</v>
+        <v>79226</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,21 +10277,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>482967</v>
+        <v>483059</v>
       </c>
       <c r="R95" t="n">
-        <v>6834340</v>
+        <v>6833927</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10363,10 +10363,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121465556</v>
+        <v>121469158</v>
       </c>
       <c r="B96" t="n">
-        <v>78344</v>
+        <v>77992</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,37 +10379,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483536</v>
+        <v>482967</v>
       </c>
       <c r="R96" t="n">
-        <v>6833990</v>
+        <v>6834339</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10453,22 +10453,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469071</v>
+        <v>121469340</v>
       </c>
       <c r="B97" t="n">
-        <v>57507</v>
+        <v>79226</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,21 +10481,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483265</v>
+        <v>483211</v>
       </c>
       <c r="R97" t="n">
-        <v>6834571</v>
+        <v>6834254</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10567,7 +10567,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465426</v>
+        <v>121465017</v>
       </c>
       <c r="B98" t="n">
         <v>78344</v>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483209</v>
+        <v>482987</v>
       </c>
       <c r="R98" t="n">
-        <v>6833990</v>
+        <v>6833950</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465412</v>
+        <v>121466059</v>
       </c>
       <c r="B99" t="n">
-        <v>78343</v>
+        <v>79226</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483177</v>
+        <v>483350</v>
       </c>
       <c r="R99" t="n">
-        <v>6833971</v>
+        <v>6834071</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121464931</v>
+        <v>121465052</v>
       </c>
       <c r="B100" t="n">
-        <v>78344</v>
+        <v>78608</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>482985</v>
+        <v>482987</v>
       </c>
       <c r="R100" t="n">
-        <v>6833943</v>
+        <v>6833950</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121466096</v>
+        <v>121465234</v>
       </c>
       <c r="B101" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483350</v>
+        <v>483201</v>
       </c>
       <c r="R101" t="n">
-        <v>6834071</v>
+        <v>6833961</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465234</v>
+        <v>121465024</v>
       </c>
       <c r="B102" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483201</v>
+        <v>482987</v>
       </c>
       <c r="R102" t="n">
-        <v>6833961</v>
+        <v>6833950</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121465017</v>
+        <v>121465266</v>
       </c>
       <c r="B103" t="n">
-        <v>78343</v>
+        <v>79197</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>482987</v>
+        <v>483204</v>
       </c>
       <c r="R103" t="n">
-        <v>6833950</v>
+        <v>6833967</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465052</v>
+        <v>121465426</v>
       </c>
       <c r="B104" t="n">
-        <v>78607</v>
+        <v>78345</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>482987</v>
+        <v>483209</v>
       </c>
       <c r="R104" t="n">
-        <v>6833950</v>
+        <v>6833990</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465266</v>
+        <v>121464931</v>
       </c>
       <c r="B105" t="n">
-        <v>79196</v>
+        <v>78345</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483204</v>
+        <v>482985</v>
       </c>
       <c r="R105" t="n">
-        <v>6833967</v>
+        <v>6833943</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11466,7 +11466,7 @@
         <v>121465991</v>
       </c>
       <c r="B106" t="n">
-        <v>79717</v>
+        <v>79718</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11575,10 +11575,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121465024</v>
+        <v>121466096</v>
       </c>
       <c r="B107" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>482987</v>
+        <v>483350</v>
       </c>
       <c r="R107" t="n">
-        <v>6833950</v>
+        <v>6834071</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121466059</v>
+        <v>121465412</v>
       </c>
       <c r="B108" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483350</v>
+        <v>483177</v>
       </c>
       <c r="R108" t="n">
-        <v>6834071</v>
+        <v>6833971</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -5111,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469347</v>
+        <v>121469126</v>
       </c>
       <c r="B45" t="n">
-        <v>79226</v>
+        <v>78608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483261</v>
+        <v>483476</v>
       </c>
       <c r="R45" t="n">
-        <v>6834535</v>
+        <v>6834017</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469126</v>
+        <v>121469347</v>
       </c>
       <c r="B46" t="n">
-        <v>78608</v>
+        <v>79226</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5229,21 +5229,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483476</v>
+        <v>483261</v>
       </c>
       <c r="R46" t="n">
-        <v>6834017</v>
+        <v>6834535</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469069</v>
+        <v>121469100</v>
       </c>
       <c r="B60" t="n">
-        <v>79197</v>
+        <v>78345</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483031</v>
+        <v>483211</v>
       </c>
       <c r="R60" t="n">
-        <v>6834458</v>
+        <v>6834254</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,7 +6763,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469100</v>
+        <v>121469096</v>
       </c>
       <c r="B61" t="n">
         <v>78345</v>
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483211</v>
+        <v>483058</v>
       </c>
       <c r="R61" t="n">
-        <v>6834254</v>
+        <v>6833926</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469096</v>
+        <v>121469107</v>
       </c>
       <c r="B62" t="n">
         <v>78345</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483058</v>
+        <v>482865</v>
       </c>
       <c r="R62" t="n">
-        <v>6833926</v>
+        <v>6834255</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469107</v>
+        <v>121469069</v>
       </c>
       <c r="B63" t="n">
-        <v>78345</v>
+        <v>79197</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>482865</v>
+        <v>483031</v>
       </c>
       <c r="R63" t="n">
-        <v>6834255</v>
+        <v>6834458</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326179</v>
+        <v>121326800</v>
       </c>
       <c r="B2" t="n">
         <v>78345</v>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482925</v>
+        <v>483205</v>
       </c>
       <c r="R2" t="n">
-        <v>6834028</v>
+        <v>6834165</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121326921</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326800</v>
+        <v>121326438</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483205</v>
+        <v>483043</v>
       </c>
       <c r="R4" t="n">
-        <v>6834165</v>
+        <v>6834195</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,7 +984,7 @@
         <v>121326433</v>
       </c>
       <c r="B5" t="n">
-        <v>79197</v>
+        <v>79198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326737</v>
+        <v>121326404</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483242</v>
+        <v>483018</v>
       </c>
       <c r="R6" t="n">
-        <v>6834570</v>
+        <v>6834214</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326438</v>
+        <v>121326179</v>
       </c>
       <c r="B7" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483043</v>
+        <v>482925</v>
       </c>
       <c r="R7" t="n">
-        <v>6834195</v>
+        <v>6834028</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326404</v>
+        <v>121326737</v>
       </c>
       <c r="B8" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483018</v>
+        <v>483242</v>
       </c>
       <c r="R8" t="n">
-        <v>6834214</v>
+        <v>6834570</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469127</v>
+        <v>121469130</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483514</v>
+        <v>483307</v>
       </c>
       <c r="R9" t="n">
-        <v>6834064</v>
+        <v>6833983</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469119</v>
+        <v>121469131</v>
       </c>
       <c r="B10" t="n">
-        <v>78344</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483265</v>
+        <v>483261</v>
       </c>
       <c r="R10" t="n">
-        <v>6834572</v>
+        <v>6834030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121465604</v>
+        <v>121469343</v>
       </c>
       <c r="B11" t="n">
-        <v>78344</v>
+        <v>79227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483179</v>
+        <v>483155</v>
       </c>
       <c r="R11" t="n">
-        <v>6833973</v>
+        <v>6834382</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,19 +1666,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469351</v>
+        <v>121469336</v>
       </c>
       <c r="B12" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482864</v>
+        <v>483492</v>
       </c>
       <c r="R12" t="n">
-        <v>6834255</v>
+        <v>6834084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467080</v>
+        <v>121469155</v>
       </c>
       <c r="B13" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483038</v>
+        <v>482892</v>
       </c>
       <c r="R13" t="n">
-        <v>6834006</v>
+        <v>6834282</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121465603</v>
+        <v>121469147</v>
       </c>
       <c r="B14" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,37 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483561</v>
+        <v>483181</v>
       </c>
       <c r="R14" t="n">
-        <v>6833992</v>
+        <v>6834299</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,19 +1972,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469130</v>
+        <v>121465159</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483307</v>
+        <v>483204</v>
       </c>
       <c r="R15" t="n">
-        <v>6833983</v>
+        <v>6833925</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2094,9 +2074,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469128</v>
+        <v>121469139</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483524</v>
+        <v>483149</v>
       </c>
       <c r="R16" t="n">
-        <v>6834071</v>
+        <v>6834501</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469142</v>
+        <v>121469114</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483076</v>
+        <v>483434</v>
       </c>
       <c r="R17" t="n">
-        <v>6834476</v>
+        <v>6833855</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121465615</v>
+        <v>121469070</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>79198</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483179</v>
+        <v>483031</v>
       </c>
       <c r="R18" t="n">
-        <v>6833973</v>
+        <v>6834425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,19 +2390,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469125</v>
+        <v>121469105</v>
       </c>
       <c r="B19" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483307</v>
+        <v>483153</v>
       </c>
       <c r="R19" t="n">
-        <v>6833983</v>
+        <v>6834504</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469114</v>
+        <v>121469098</v>
       </c>
       <c r="B20" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483434</v>
+        <v>483445</v>
       </c>
       <c r="R20" t="n">
-        <v>6833855</v>
+        <v>6833857</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469345</v>
+        <v>121465556</v>
       </c>
       <c r="B21" t="n">
-        <v>79226</v>
+        <v>78346</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,37 +2639,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483210</v>
+        <v>483536</v>
       </c>
       <c r="R21" t="n">
-        <v>6834457</v>
+        <v>6833990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2733,22 +2713,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469101</v>
+        <v>121469154</v>
       </c>
       <c r="B22" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483168</v>
+        <v>483081</v>
       </c>
       <c r="R22" t="n">
-        <v>6834333</v>
+        <v>6834496</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469115</v>
+        <v>121469116</v>
       </c>
       <c r="B23" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483445</v>
+        <v>483484</v>
       </c>
       <c r="R23" t="n">
-        <v>6833857</v>
+        <v>6833901</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469110</v>
+        <v>121469124</v>
       </c>
       <c r="B24" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483144</v>
+        <v>482865</v>
       </c>
       <c r="R24" t="n">
-        <v>6833875</v>
+        <v>6834254</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469116</v>
+        <v>121469351</v>
       </c>
       <c r="B25" t="n">
-        <v>78344</v>
+        <v>79227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483484</v>
+        <v>482864</v>
       </c>
       <c r="R25" t="n">
-        <v>6833901</v>
+        <v>6834255</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3153,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469155</v>
+        <v>121469136</v>
       </c>
       <c r="B26" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482892</v>
+        <v>483198</v>
       </c>
       <c r="R26" t="n">
-        <v>6834282</v>
+        <v>6834484</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469144</v>
+        <v>121469134</v>
       </c>
       <c r="B27" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483402</v>
+        <v>483277</v>
       </c>
       <c r="R27" t="n">
-        <v>6834000</v>
+        <v>6834451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469097</v>
+        <v>121469112</v>
       </c>
       <c r="B28" t="n">
         <v>78345</v>
@@ -3373,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3459,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121465189</v>
+        <v>121469149</v>
       </c>
       <c r="B29" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,37 +3455,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483204</v>
+        <v>483268</v>
       </c>
       <c r="R29" t="n">
-        <v>6833925</v>
+        <v>6834459</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3532,19 +3512,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3559,22 +3529,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469339</v>
+        <v>121469146</v>
       </c>
       <c r="B30" t="n">
-        <v>79226</v>
+        <v>78254</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483213</v>
+        <v>483260</v>
       </c>
       <c r="R30" t="n">
-        <v>6834252</v>
+        <v>6834060</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469157</v>
+        <v>121469104</v>
       </c>
       <c r="B31" t="n">
-        <v>77992</v>
+        <v>78346</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3689,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3713,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483143</v>
+        <v>483265</v>
       </c>
       <c r="R31" t="n">
-        <v>6833875</v>
+        <v>6834572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469071</v>
+        <v>121469107</v>
       </c>
       <c r="B32" t="n">
-        <v>57508</v>
+        <v>78346</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3791,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3815,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483265</v>
+        <v>482865</v>
       </c>
       <c r="R32" t="n">
-        <v>6834571</v>
+        <v>6834255</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469139</v>
+        <v>121467007</v>
       </c>
       <c r="B33" t="n">
-        <v>78608</v>
+        <v>78346</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,13 +3887,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483149</v>
+        <v>483082</v>
       </c>
       <c r="R33" t="n">
-        <v>6834501</v>
+        <v>6834003</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3950,9 +3920,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,22 +3947,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469134</v>
+        <v>121469144</v>
       </c>
       <c r="B34" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483277</v>
+        <v>483402</v>
       </c>
       <c r="R34" t="n">
-        <v>6834451</v>
+        <v>6834000</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121465159</v>
+        <v>121465202</v>
       </c>
       <c r="B35" t="n">
-        <v>78344</v>
+        <v>78254</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4097,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,13 +4101,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483204</v>
+        <v>483084</v>
       </c>
       <c r="R35" t="n">
-        <v>6833925</v>
+        <v>6833930</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4156,7 +4136,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4166,7 +4146,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4181,22 +4161,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469343</v>
+        <v>121469339</v>
       </c>
       <c r="B36" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4233,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483155</v>
+        <v>483213</v>
       </c>
       <c r="R36" t="n">
-        <v>6834382</v>
+        <v>6834252</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469117</v>
+        <v>121469137</v>
       </c>
       <c r="B37" t="n">
-        <v>78344</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4311,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4335,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483119</v>
+        <v>483198</v>
       </c>
       <c r="R37" t="n">
-        <v>6834405</v>
+        <v>6834476</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4397,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121465664</v>
+        <v>121469340</v>
       </c>
       <c r="B38" t="n">
-        <v>78344</v>
+        <v>79227</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,37 +4393,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483498</v>
+        <v>483211</v>
       </c>
       <c r="R38" t="n">
-        <v>6834031</v>
+        <v>6834254</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4487,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469344</v>
+        <v>121469126</v>
       </c>
       <c r="B39" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4515,21 +4495,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4539,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483119</v>
+        <v>483476</v>
       </c>
       <c r="R39" t="n">
-        <v>6834405</v>
+        <v>6834017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4601,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469070</v>
+        <v>121469119</v>
       </c>
       <c r="B40" t="n">
-        <v>79197</v>
+        <v>78345</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4617,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4641,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483031</v>
+        <v>483265</v>
       </c>
       <c r="R40" t="n">
-        <v>6834425</v>
+        <v>6834572</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469102</v>
+        <v>121469348</v>
       </c>
       <c r="B41" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,21 +4699,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4743,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483161</v>
+        <v>483153</v>
       </c>
       <c r="R41" t="n">
-        <v>6834377</v>
+        <v>6834505</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121466253</v>
+        <v>121465615</v>
       </c>
       <c r="B42" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4845,13 +4825,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483464</v>
+        <v>483179</v>
       </c>
       <c r="R42" t="n">
-        <v>6833910</v>
+        <v>6833973</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4878,9 +4858,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4895,22 +4885,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469108</v>
+        <v>121469115</v>
       </c>
       <c r="B43" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4947,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>482925</v>
+        <v>483445</v>
       </c>
       <c r="R43" t="n">
-        <v>6833910</v>
+        <v>6833857</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469338</v>
+        <v>121469337</v>
       </c>
       <c r="B44" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5049,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483246</v>
+        <v>483413</v>
       </c>
       <c r="R44" t="n">
-        <v>6834122</v>
+        <v>6834033</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469126</v>
+        <v>121469158</v>
       </c>
       <c r="B45" t="n">
-        <v>78608</v>
+        <v>77993</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5127,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5151,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483476</v>
+        <v>482967</v>
       </c>
       <c r="R45" t="n">
-        <v>6834017</v>
+        <v>6834339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469347</v>
+        <v>121469128</v>
       </c>
       <c r="B46" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5229,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5253,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483261</v>
+        <v>483524</v>
       </c>
       <c r="R46" t="n">
-        <v>6834535</v>
+        <v>6834071</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469103</v>
+        <v>121469097</v>
       </c>
       <c r="B47" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5355,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483145</v>
+        <v>483408</v>
       </c>
       <c r="R47" t="n">
-        <v>6834394</v>
+        <v>6833852</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469342</v>
+        <v>121469069</v>
       </c>
       <c r="B48" t="n">
-        <v>79226</v>
+        <v>79198</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5457,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483160</v>
+        <v>483031</v>
       </c>
       <c r="R48" t="n">
-        <v>6834377</v>
+        <v>6834458</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469335</v>
+        <v>121465246</v>
       </c>
       <c r="B49" t="n">
-        <v>79226</v>
+        <v>78345</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,37 +5525,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483483</v>
+        <v>483187</v>
       </c>
       <c r="R49" t="n">
-        <v>6833854</v>
+        <v>6833888</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5592,9 +5582,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5609,22 +5609,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121467007</v>
+        <v>121469350</v>
       </c>
       <c r="B50" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,13 +5661,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483082</v>
+        <v>483033</v>
       </c>
       <c r="R50" t="n">
-        <v>6834003</v>
+        <v>6834458</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5694,19 +5694,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5721,22 +5711,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469104</v>
+        <v>121469099</v>
       </c>
       <c r="B51" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5773,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483265</v>
+        <v>483482</v>
       </c>
       <c r="R51" t="n">
-        <v>6834572</v>
+        <v>6833855</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5835,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469095</v>
+        <v>121465603</v>
       </c>
       <c r="B52" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5871,17 +5861,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>482925</v>
+        <v>483561</v>
       </c>
       <c r="R52" t="n">
-        <v>6833909</v>
+        <v>6833992</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5908,9 +5898,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5925,22 +5925,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469150</v>
+        <v>121469132</v>
       </c>
       <c r="B53" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5953,21 +5953,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483294</v>
+        <v>483255</v>
       </c>
       <c r="R53" t="n">
-        <v>6834475</v>
+        <v>6834077</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469154</v>
+        <v>121467022</v>
       </c>
       <c r="B54" t="n">
-        <v>78253</v>
+        <v>78345</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6055,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6079,13 +6079,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483081</v>
+        <v>483082</v>
       </c>
       <c r="R54" t="n">
-        <v>6834496</v>
+        <v>6834003</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6112,9 +6112,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6129,22 +6139,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469146</v>
+        <v>121469103</v>
       </c>
       <c r="B55" t="n">
-        <v>78253</v>
+        <v>78346</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,21 +6167,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6181,10 +6191,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483260</v>
+        <v>483145</v>
       </c>
       <c r="R55" t="n">
-        <v>6834060</v>
+        <v>6834394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6253,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469122</v>
+        <v>121469101</v>
       </c>
       <c r="B56" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6259,21 +6269,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6283,10 +6293,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>482967</v>
+        <v>483168</v>
       </c>
       <c r="R56" t="n">
-        <v>6834340</v>
+        <v>6834333</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,10 +6355,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121465246</v>
+        <v>121469095</v>
       </c>
       <c r="B57" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6361,37 +6371,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483187</v>
+        <v>482925</v>
       </c>
       <c r="R57" t="n">
-        <v>6833888</v>
+        <v>6833909</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6418,19 +6428,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6445,22 +6445,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469341</v>
+        <v>121469142</v>
       </c>
       <c r="B58" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483181</v>
+        <v>483076</v>
       </c>
       <c r="R58" t="n">
-        <v>6834299</v>
+        <v>6834476</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469112</v>
+        <v>121469071</v>
       </c>
       <c r="B59" t="n">
-        <v>78344</v>
+        <v>57509</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483408</v>
+        <v>483265</v>
       </c>
       <c r="R59" t="n">
-        <v>6833852</v>
+        <v>6834571</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469100</v>
+        <v>121469152</v>
       </c>
       <c r="B60" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483211</v>
+        <v>483169</v>
       </c>
       <c r="R60" t="n">
-        <v>6834254</v>
+        <v>6834491</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469096</v>
+        <v>121469148</v>
       </c>
       <c r="B61" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,21 +6779,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483058</v>
+        <v>483160</v>
       </c>
       <c r="R61" t="n">
-        <v>6833926</v>
+        <v>6834438</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469107</v>
+        <v>121469125</v>
       </c>
       <c r="B62" t="n">
         <v>78345</v>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>482865</v>
+        <v>483307</v>
       </c>
       <c r="R62" t="n">
-        <v>6834255</v>
+        <v>6833983</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469069</v>
+        <v>121465160</v>
       </c>
       <c r="B63" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483031</v>
+        <v>483115</v>
       </c>
       <c r="R63" t="n">
-        <v>6834458</v>
+        <v>6833942</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7040,9 +7040,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7057,22 +7067,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121465202</v>
+        <v>121469135</v>
       </c>
       <c r="B64" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,37 +7095,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483084</v>
+        <v>483205</v>
       </c>
       <c r="R64" t="n">
-        <v>6833930</v>
+        <v>6834490</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7142,19 +7152,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7169,22 +7169,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469336</v>
+        <v>121469108</v>
       </c>
       <c r="B65" t="n">
-        <v>79226</v>
+        <v>78345</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7197,21 +7197,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483492</v>
+        <v>482925</v>
       </c>
       <c r="R65" t="n">
-        <v>6834084</v>
+        <v>6833910</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7283,10 +7283,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469120</v>
+        <v>121469345</v>
       </c>
       <c r="B66" t="n">
-        <v>78344</v>
+        <v>79227</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7299,21 +7299,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483153</v>
+        <v>483210</v>
       </c>
       <c r="R66" t="n">
-        <v>6834504</v>
+        <v>6834457</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7385,10 +7385,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469140</v>
+        <v>121469334</v>
       </c>
       <c r="B67" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7401,21 +7401,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483106</v>
+        <v>483084</v>
       </c>
       <c r="R67" t="n">
-        <v>6834495</v>
+        <v>6833901</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7487,10 +7487,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469132</v>
+        <v>121465664</v>
       </c>
       <c r="B68" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7503,37 +7503,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483255</v>
+        <v>483498</v>
       </c>
       <c r="R68" t="n">
-        <v>6834077</v>
+        <v>6834031</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7577,22 +7577,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469145</v>
+        <v>121469102</v>
       </c>
       <c r="B69" t="n">
-        <v>78253</v>
+        <v>78346</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483387</v>
+        <v>483161</v>
       </c>
       <c r="R69" t="n">
-        <v>6833994</v>
+        <v>6834377</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469149</v>
+        <v>121469110</v>
       </c>
       <c r="B70" t="n">
-        <v>78253</v>
+        <v>78345</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483268</v>
+        <v>483144</v>
       </c>
       <c r="R70" t="n">
-        <v>6834459</v>
+        <v>6833875</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469106</v>
+        <v>121469335</v>
       </c>
       <c r="B71" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7809,21 +7809,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>482967</v>
+        <v>483483</v>
       </c>
       <c r="R71" t="n">
-        <v>6834340</v>
+        <v>6833854</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7895,10 +7895,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469147</v>
+        <v>121469106</v>
       </c>
       <c r="B72" t="n">
-        <v>78253</v>
+        <v>78346</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7911,21 +7911,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483181</v>
+        <v>482967</v>
       </c>
       <c r="R72" t="n">
-        <v>6834299</v>
+        <v>6834340</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>121469133</v>
       </c>
       <c r="B73" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469131</v>
+        <v>121469349</v>
       </c>
       <c r="B74" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483261</v>
+        <v>483065</v>
       </c>
       <c r="R74" t="n">
-        <v>6834030</v>
+        <v>6834469</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469348</v>
+        <v>121469127</v>
       </c>
       <c r="B75" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483153</v>
+        <v>483514</v>
       </c>
       <c r="R75" t="n">
-        <v>6834505</v>
+        <v>6834064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121467022</v>
+        <v>121469157</v>
       </c>
       <c r="B76" t="n">
-        <v>78344</v>
+        <v>77993</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,13 +8343,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483082</v>
+        <v>483143</v>
       </c>
       <c r="R76" t="n">
-        <v>6834003</v>
+        <v>6833875</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8376,19 +8376,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8403,22 +8393,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469105</v>
+        <v>121465189</v>
       </c>
       <c r="B77" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8451,17 +8441,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483153</v>
+        <v>483204</v>
       </c>
       <c r="R77" t="n">
-        <v>6834504</v>
+        <v>6833925</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8488,9 +8478,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8505,22 +8505,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121465556</v>
+        <v>121469140</v>
       </c>
       <c r="B78" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8533,37 +8533,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483536</v>
+        <v>483106</v>
       </c>
       <c r="R78" t="n">
-        <v>6833990</v>
+        <v>6834495</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8607,22 +8607,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469349</v>
+        <v>121469333</v>
       </c>
       <c r="B79" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483065</v>
+        <v>483059</v>
       </c>
       <c r="R79" t="n">
-        <v>6834469</v>
+        <v>6833927</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8721,10 +8721,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469148</v>
+        <v>121469342</v>
       </c>
       <c r="B80" t="n">
-        <v>78253</v>
+        <v>79227</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8764,7 +8764,7 @@
         <v>483160</v>
       </c>
       <c r="R80" t="n">
-        <v>6834438</v>
+        <v>6834377</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8823,10 +8823,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469152</v>
+        <v>121469118</v>
       </c>
       <c r="B81" t="n">
-        <v>78253</v>
+        <v>78345</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8839,21 +8839,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483169</v>
+        <v>483210</v>
       </c>
       <c r="R81" t="n">
-        <v>6834491</v>
+        <v>6834456</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8925,10 +8925,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469124</v>
+        <v>121469100</v>
       </c>
       <c r="B82" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8941,21 +8941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>482865</v>
+        <v>483211</v>
       </c>
       <c r="R82" t="n">
         <v>6834254</v>
@@ -9027,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469350</v>
+        <v>121469096</v>
       </c>
       <c r="B83" t="n">
-        <v>79226</v>
+        <v>78346</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9043,21 +9043,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483033</v>
+        <v>483058</v>
       </c>
       <c r="R83" t="n">
-        <v>6834458</v>
+        <v>6833926</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,10 +9129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469099</v>
+        <v>121466253</v>
       </c>
       <c r="B84" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9165,17 +9165,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483482</v>
+        <v>483464</v>
       </c>
       <c r="R84" t="n">
-        <v>6833855</v>
+        <v>6833910</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9219,22 +9219,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469337</v>
+        <v>121469143</v>
       </c>
       <c r="B85" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,21 +9247,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483413</v>
+        <v>483038</v>
       </c>
       <c r="R85" t="n">
-        <v>6834033</v>
+        <v>6834461</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9333,10 +9333,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469118</v>
+        <v>121469122</v>
       </c>
       <c r="B86" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483210</v>
+        <v>482967</v>
       </c>
       <c r="R86" t="n">
-        <v>6834456</v>
+        <v>6834340</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469334</v>
+        <v>121469150</v>
       </c>
       <c r="B87" t="n">
-        <v>79226</v>
+        <v>78254</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9451,21 +9451,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483084</v>
+        <v>483294</v>
       </c>
       <c r="R87" t="n">
-        <v>6833901</v>
+        <v>6834475</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9537,10 +9537,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469098</v>
+        <v>121469145</v>
       </c>
       <c r="B88" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9553,21 +9553,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483445</v>
+        <v>483387</v>
       </c>
       <c r="R88" t="n">
-        <v>6833857</v>
+        <v>6833994</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9639,10 +9639,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121465160</v>
+        <v>121469120</v>
       </c>
       <c r="B89" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,13 +9679,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483115</v>
+        <v>483153</v>
       </c>
       <c r="R89" t="n">
-        <v>6833942</v>
+        <v>6834504</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9712,19 +9712,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9739,22 +9729,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469135</v>
+        <v>121469117</v>
       </c>
       <c r="B90" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9767,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9791,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483205</v>
+        <v>483119</v>
       </c>
       <c r="R90" t="n">
-        <v>6834490</v>
+        <v>6834405</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9853,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469143</v>
+        <v>121469338</v>
       </c>
       <c r="B91" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9869,21 +9859,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9893,10 +9883,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483038</v>
+        <v>483246</v>
       </c>
       <c r="R91" t="n">
-        <v>6834461</v>
+        <v>6834122</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9955,10 +9945,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469137</v>
+        <v>121469344</v>
       </c>
       <c r="B92" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9961,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483198</v>
+        <v>483119</v>
       </c>
       <c r="R92" t="n">
-        <v>6834476</v>
+        <v>6834405</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10057,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469136</v>
+        <v>121469156</v>
       </c>
       <c r="B93" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10073,21 +10063,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10097,10 +10087,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483198</v>
+        <v>482876</v>
       </c>
       <c r="R93" t="n">
-        <v>6834484</v>
+        <v>6834258</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10159,10 +10149,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469156</v>
+        <v>121469347</v>
       </c>
       <c r="B94" t="n">
-        <v>78253</v>
+        <v>79227</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10175,21 +10165,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10199,10 +10189,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>482876</v>
+        <v>483261</v>
       </c>
       <c r="R94" t="n">
-        <v>6834258</v>
+        <v>6834535</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10261,10 +10251,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469333</v>
+        <v>121465604</v>
       </c>
       <c r="B95" t="n">
-        <v>79226</v>
+        <v>78345</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,37 +10267,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483059</v>
+        <v>483179</v>
       </c>
       <c r="R95" t="n">
-        <v>6833927</v>
+        <v>6833973</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10334,9 +10324,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10351,22 +10351,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469158</v>
+        <v>121469341</v>
       </c>
       <c r="B96" t="n">
-        <v>77992</v>
+        <v>79227</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482967</v>
+        <v>483181</v>
       </c>
       <c r="R96" t="n">
-        <v>6834339</v>
+        <v>6834299</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10465,10 +10465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469340</v>
+        <v>121467080</v>
       </c>
       <c r="B97" t="n">
-        <v>79226</v>
+        <v>78346</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,37 +10481,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483211</v>
+        <v>483038</v>
       </c>
       <c r="R97" t="n">
-        <v>6834254</v>
+        <v>6834006</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465017</v>
+        <v>121465234</v>
       </c>
       <c r="B98" t="n">
-        <v>78344</v>
+        <v>78609</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>482987</v>
+        <v>483201</v>
       </c>
       <c r="R98" t="n">
-        <v>6833950</v>
+        <v>6833961</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121466059</v>
+        <v>121465426</v>
       </c>
       <c r="B99" t="n">
-        <v>79226</v>
+        <v>78346</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483350</v>
+        <v>483209</v>
       </c>
       <c r="R99" t="n">
-        <v>6834071</v>
+        <v>6833990</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121465052</v>
+        <v>121465024</v>
       </c>
       <c r="B100" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465234</v>
+        <v>121465052</v>
       </c>
       <c r="B101" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483201</v>
+        <v>482987</v>
       </c>
       <c r="R101" t="n">
-        <v>6833961</v>
+        <v>6833950</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465024</v>
+        <v>121465412</v>
       </c>
       <c r="B102" t="n">
-        <v>79226</v>
+        <v>78345</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>482987</v>
+        <v>483177</v>
       </c>
       <c r="R102" t="n">
-        <v>6833950</v>
+        <v>6833971</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121465266</v>
+        <v>121466096</v>
       </c>
       <c r="B103" t="n">
-        <v>79197</v>
+        <v>78345</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483204</v>
+        <v>483350</v>
       </c>
       <c r="R103" t="n">
-        <v>6833967</v>
+        <v>6834071</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11232,17 +11232,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465426</v>
+        <v>121465991</v>
       </c>
       <c r="B104" t="n">
-        <v>78345</v>
+        <v>79719</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11251,25 +11251,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483209</v>
+        <v>483306</v>
       </c>
       <c r="R104" t="n">
-        <v>6833990</v>
+        <v>6834009</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11344,17 +11344,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121464931</v>
+        <v>121466059</v>
       </c>
       <c r="B105" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>482985</v>
+        <v>483350</v>
       </c>
       <c r="R105" t="n">
-        <v>6833943</v>
+        <v>6834071</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465991</v>
+        <v>121464931</v>
       </c>
       <c r="B106" t="n">
-        <v>79718</v>
+        <v>78346</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11475,25 +11475,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483306</v>
+        <v>482985</v>
       </c>
       <c r="R106" t="n">
-        <v>6834009</v>
+        <v>6833943</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121466096</v>
+        <v>121465017</v>
       </c>
       <c r="B107" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483350</v>
+        <v>482987</v>
       </c>
       <c r="R107" t="n">
-        <v>6834071</v>
+        <v>6833950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121465412</v>
+        <v>121465266</v>
       </c>
       <c r="B108" t="n">
-        <v>78344</v>
+        <v>79198</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483177</v>
+        <v>483204</v>
       </c>
       <c r="R108" t="n">
-        <v>6833971</v>
+        <v>6833967</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326800</v>
+        <v>121326438</v>
       </c>
       <c r="B2" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483205</v>
+        <v>483043</v>
       </c>
       <c r="R2" t="n">
-        <v>6834165</v>
+        <v>6834195</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326921</v>
+        <v>121326800</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483134</v>
+        <v>483205</v>
       </c>
       <c r="R3" t="n">
-        <v>6833995</v>
+        <v>6834165</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326438</v>
+        <v>121326179</v>
       </c>
       <c r="B4" t="n">
         <v>78346</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483043</v>
+        <v>482925</v>
       </c>
       <c r="R4" t="n">
-        <v>6834195</v>
+        <v>6834028</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326433</v>
+        <v>121326921</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483040</v>
+        <v>483134</v>
       </c>
       <c r="R5" t="n">
-        <v>6834198</v>
+        <v>6833995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326179</v>
+        <v>121326433</v>
       </c>
       <c r="B7" t="n">
-        <v>78346</v>
+        <v>79198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482925</v>
+        <v>483040</v>
       </c>
       <c r="R7" t="n">
-        <v>6834028</v>
+        <v>6834198</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469130</v>
+        <v>121469351</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483307</v>
+        <v>482864</v>
       </c>
       <c r="R9" t="n">
-        <v>6833983</v>
+        <v>6834255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469131</v>
+        <v>121469133</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483261</v>
+        <v>483241</v>
       </c>
       <c r="R10" t="n">
-        <v>6834030</v>
+        <v>6834112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469343</v>
+        <v>121469152</v>
       </c>
       <c r="B11" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483155</v>
+        <v>483169</v>
       </c>
       <c r="R11" t="n">
-        <v>6834382</v>
+        <v>6834491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469336</v>
+        <v>121469144</v>
       </c>
       <c r="B12" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483492</v>
+        <v>483402</v>
       </c>
       <c r="R12" t="n">
-        <v>6834084</v>
+        <v>6834000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469155</v>
+        <v>121469115</v>
       </c>
       <c r="B13" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482892</v>
+        <v>483445</v>
       </c>
       <c r="R13" t="n">
-        <v>6834282</v>
+        <v>6833857</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469147</v>
+        <v>121469122</v>
       </c>
       <c r="B14" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483181</v>
+        <v>482967</v>
       </c>
       <c r="R14" t="n">
-        <v>6834299</v>
+        <v>6834340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121465159</v>
+        <v>121469341</v>
       </c>
       <c r="B15" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483204</v>
+        <v>483181</v>
       </c>
       <c r="R15" t="n">
-        <v>6833925</v>
+        <v>6834299</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2074,19 +2074,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469139</v>
+        <v>121469098</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483149</v>
+        <v>483445</v>
       </c>
       <c r="R16" t="n">
-        <v>6834501</v>
+        <v>6833857</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469114</v>
+        <v>121469131</v>
       </c>
       <c r="B17" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483434</v>
+        <v>483261</v>
       </c>
       <c r="R17" t="n">
-        <v>6833855</v>
+        <v>6834030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469070</v>
+        <v>121469142</v>
       </c>
       <c r="B18" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483031</v>
+        <v>483076</v>
       </c>
       <c r="R18" t="n">
-        <v>6834425</v>
+        <v>6834476</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469105</v>
+        <v>121469136</v>
       </c>
       <c r="B19" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483153</v>
+        <v>483198</v>
       </c>
       <c r="R19" t="n">
-        <v>6834504</v>
+        <v>6834484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469098</v>
+        <v>121469335</v>
       </c>
       <c r="B20" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483445</v>
+        <v>483483</v>
       </c>
       <c r="R20" t="n">
-        <v>6833857</v>
+        <v>6833854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121465556</v>
+        <v>121469139</v>
       </c>
       <c r="B21" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,37 +2629,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483536</v>
+        <v>483149</v>
       </c>
       <c r="R21" t="n">
-        <v>6833990</v>
+        <v>6834501</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2713,19 +2703,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469154</v>
+        <v>121469148</v>
       </c>
       <c r="B22" t="n">
         <v>78254</v>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483081</v>
+        <v>483160</v>
       </c>
       <c r="R22" t="n">
-        <v>6834496</v>
+        <v>6834438</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469116</v>
+        <v>121469130</v>
       </c>
       <c r="B23" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483484</v>
+        <v>483307</v>
       </c>
       <c r="R23" t="n">
-        <v>6833901</v>
+        <v>6833983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469124</v>
+        <v>121469135</v>
       </c>
       <c r="B24" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482865</v>
+        <v>483205</v>
       </c>
       <c r="R24" t="n">
-        <v>6834254</v>
+        <v>6834490</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469351</v>
+        <v>121469126</v>
       </c>
       <c r="B25" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482864</v>
+        <v>483476</v>
       </c>
       <c r="R25" t="n">
-        <v>6834255</v>
+        <v>6834017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469136</v>
+        <v>121469137</v>
       </c>
       <c r="B26" t="n">
         <v>78609</v>
@@ -3176,7 +3166,7 @@
         <v>483198</v>
       </c>
       <c r="R26" t="n">
-        <v>6834484</v>
+        <v>6834476</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469134</v>
+        <v>121465556</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,37 +3241,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483277</v>
+        <v>483536</v>
       </c>
       <c r="R27" t="n">
-        <v>6834451</v>
+        <v>6833990</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3325,12 +3315,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3439,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469149</v>
+        <v>121469106</v>
       </c>
       <c r="B29" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483268</v>
+        <v>482967</v>
       </c>
       <c r="R29" t="n">
-        <v>6834459</v>
+        <v>6834340</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469146</v>
+        <v>121469097</v>
       </c>
       <c r="B30" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483260</v>
+        <v>483408</v>
       </c>
       <c r="R30" t="n">
-        <v>6834060</v>
+        <v>6833852</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469104</v>
+        <v>121469340</v>
       </c>
       <c r="B31" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483265</v>
+        <v>483211</v>
       </c>
       <c r="R31" t="n">
-        <v>6834572</v>
+        <v>6834254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469107</v>
+        <v>121469345</v>
       </c>
       <c r="B32" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482865</v>
+        <v>483210</v>
       </c>
       <c r="R32" t="n">
-        <v>6834255</v>
+        <v>6834457</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121467007</v>
+        <v>121469127</v>
       </c>
       <c r="B33" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,13 +3877,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483082</v>
+        <v>483514</v>
       </c>
       <c r="R33" t="n">
-        <v>6834003</v>
+        <v>6834064</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3920,19 +3910,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,22 +3927,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469144</v>
+        <v>121469339</v>
       </c>
       <c r="B34" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483402</v>
+        <v>483213</v>
       </c>
       <c r="R34" t="n">
-        <v>6834000</v>
+        <v>6834252</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121465202</v>
+        <v>121469101</v>
       </c>
       <c r="B35" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,37 +4057,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483084</v>
+        <v>483168</v>
       </c>
       <c r="R35" t="n">
-        <v>6833930</v>
+        <v>6834333</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4134,19 +4114,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4161,22 +4131,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469339</v>
+        <v>121469132</v>
       </c>
       <c r="B36" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483213</v>
+        <v>483255</v>
       </c>
       <c r="R36" t="n">
-        <v>6834252</v>
+        <v>6834077</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469137</v>
+        <v>121469134</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4315,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483198</v>
+        <v>483277</v>
       </c>
       <c r="R37" t="n">
-        <v>6834476</v>
+        <v>6834451</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,7 +4347,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469340</v>
+        <v>121469338</v>
       </c>
       <c r="B38" t="n">
         <v>79227</v>
@@ -4417,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483211</v>
+        <v>483246</v>
       </c>
       <c r="R38" t="n">
-        <v>6834254</v>
+        <v>6834122</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469126</v>
+        <v>121467007</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4519,13 +4489,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483476</v>
+        <v>483082</v>
       </c>
       <c r="R39" t="n">
-        <v>6834017</v>
+        <v>6834003</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4552,9 +4522,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4569,22 +4549,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469119</v>
+        <v>121469154</v>
       </c>
       <c r="B40" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483265</v>
+        <v>483081</v>
       </c>
       <c r="R40" t="n">
-        <v>6834572</v>
+        <v>6834496</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469348</v>
+        <v>121465189</v>
       </c>
       <c r="B41" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,37 +4679,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483153</v>
+        <v>483204</v>
       </c>
       <c r="R41" t="n">
-        <v>6834505</v>
+        <v>6833925</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4756,9 +4736,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,19 +4763,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121465615</v>
+        <v>121469143</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -4821,14 +4811,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483179</v>
+        <v>483038</v>
       </c>
       <c r="R42" t="n">
-        <v>6833973</v>
+        <v>6834461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,19 +4848,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4885,22 +4865,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469115</v>
+        <v>121469107</v>
       </c>
       <c r="B43" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4893,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483445</v>
+        <v>482865</v>
       </c>
       <c r="R43" t="n">
-        <v>6833857</v>
+        <v>6834255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469337</v>
+        <v>121465160</v>
       </c>
       <c r="B44" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,13 +5019,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483413</v>
+        <v>483115</v>
       </c>
       <c r="R44" t="n">
-        <v>6834033</v>
+        <v>6833942</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5072,9 +5052,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5089,19 +5079,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469158</v>
+        <v>121469157</v>
       </c>
       <c r="B45" t="n">
         <v>77993</v>
@@ -5141,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482967</v>
+        <v>483143</v>
       </c>
       <c r="R45" t="n">
-        <v>6834339</v>
+        <v>6833875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,10 +5193,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469128</v>
+        <v>121469070</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5209,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5233,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483524</v>
+        <v>483031</v>
       </c>
       <c r="R46" t="n">
-        <v>6834071</v>
+        <v>6834425</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,7 +5295,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469097</v>
+        <v>121469102</v>
       </c>
       <c r="B47" t="n">
         <v>78346</v>
@@ -5345,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483408</v>
+        <v>483161</v>
       </c>
       <c r="R47" t="n">
-        <v>6833852</v>
+        <v>6834377</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5509,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121465246</v>
+        <v>121469140</v>
       </c>
       <c r="B49" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,37 +5515,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483187</v>
+        <v>483106</v>
       </c>
       <c r="R49" t="n">
-        <v>6833888</v>
+        <v>6834495</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5582,19 +5572,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5609,22 +5589,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469350</v>
+        <v>121469124</v>
       </c>
       <c r="B50" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5617,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483033</v>
+        <v>482865</v>
       </c>
       <c r="R50" t="n">
-        <v>6834458</v>
+        <v>6834254</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469099</v>
+        <v>121469158</v>
       </c>
       <c r="B51" t="n">
-        <v>78346</v>
+        <v>77993</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,21 +5719,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5743,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483482</v>
+        <v>482967</v>
       </c>
       <c r="R51" t="n">
-        <v>6833855</v>
+        <v>6834339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121465603</v>
+        <v>121469349</v>
       </c>
       <c r="B52" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,37 +5821,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483561</v>
+        <v>483065</v>
       </c>
       <c r="R52" t="n">
-        <v>6833992</v>
+        <v>6834469</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5898,19 +5878,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5925,22 +5895,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469132</v>
+        <v>121469350</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5953,21 +5923,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483255</v>
+        <v>483033</v>
       </c>
       <c r="R53" t="n">
-        <v>6834077</v>
+        <v>6834458</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,7 +6009,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121467022</v>
+        <v>121465159</v>
       </c>
       <c r="B54" t="n">
         <v>78345</v>
@@ -6075,17 +6045,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483082</v>
+        <v>483204</v>
       </c>
       <c r="R54" t="n">
-        <v>6834003</v>
+        <v>6833925</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6114,7 +6084,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6124,7 +6094,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6139,19 +6109,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469103</v>
+        <v>121469105</v>
       </c>
       <c r="B55" t="n">
         <v>78346</v>
@@ -6191,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483145</v>
+        <v>483153</v>
       </c>
       <c r="R55" t="n">
-        <v>6834394</v>
+        <v>6834504</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6253,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469101</v>
+        <v>121469119</v>
       </c>
       <c r="B56" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6269,21 +6239,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6293,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483168</v>
+        <v>483265</v>
       </c>
       <c r="R56" t="n">
-        <v>6834333</v>
+        <v>6834572</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6355,7 +6325,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469095</v>
+        <v>121469099</v>
       </c>
       <c r="B57" t="n">
         <v>78346</v>
@@ -6395,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>482925</v>
+        <v>483482</v>
       </c>
       <c r="R57" t="n">
-        <v>6833909</v>
+        <v>6833855</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6457,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469142</v>
+        <v>121469095</v>
       </c>
       <c r="B58" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6473,21 +6443,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6497,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483076</v>
+        <v>482925</v>
       </c>
       <c r="R58" t="n">
-        <v>6834476</v>
+        <v>6833909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469071</v>
+        <v>121465603</v>
       </c>
       <c r="B59" t="n">
-        <v>57509</v>
+        <v>78346</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,37 +6545,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483265</v>
+        <v>483561</v>
       </c>
       <c r="R59" t="n">
-        <v>6834571</v>
+        <v>6833992</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6632,9 +6602,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6649,22 +6629,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469152</v>
+        <v>121469342</v>
       </c>
       <c r="B60" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6657,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483169</v>
+        <v>483160</v>
       </c>
       <c r="R60" t="n">
-        <v>6834491</v>
+        <v>6834377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6743,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469148</v>
+        <v>121469343</v>
       </c>
       <c r="B61" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,21 +6759,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6803,10 +6783,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483160</v>
+        <v>483155</v>
       </c>
       <c r="R61" t="n">
-        <v>6834438</v>
+        <v>6834382</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,10 +6845,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469125</v>
+        <v>121469344</v>
       </c>
       <c r="B62" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,21 +6861,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,10 +6885,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483307</v>
+        <v>483119</v>
       </c>
       <c r="R62" t="n">
-        <v>6833983</v>
+        <v>6834405</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6947,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121465160</v>
+        <v>121469125</v>
       </c>
       <c r="B63" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6963,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,13 +6987,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483115</v>
+        <v>483307</v>
       </c>
       <c r="R63" t="n">
-        <v>6833942</v>
+        <v>6833983</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7040,19 +7020,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7067,22 +7037,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469135</v>
+        <v>121469145</v>
       </c>
       <c r="B64" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7095,21 +7065,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7119,10 +7089,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483205</v>
+        <v>483387</v>
       </c>
       <c r="R64" t="n">
-        <v>6834490</v>
+        <v>6833994</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7181,10 +7151,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469108</v>
+        <v>121469146</v>
       </c>
       <c r="B65" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7197,21 +7167,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7221,10 +7191,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>482925</v>
+        <v>483260</v>
       </c>
       <c r="R65" t="n">
-        <v>6833910</v>
+        <v>6834060</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7283,7 +7253,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469345</v>
+        <v>121469336</v>
       </c>
       <c r="B66" t="n">
         <v>79227</v>
@@ -7323,10 +7293,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483210</v>
+        <v>483492</v>
       </c>
       <c r="R66" t="n">
-        <v>6834457</v>
+        <v>6834084</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7385,10 +7355,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469334</v>
+        <v>121469110</v>
       </c>
       <c r="B67" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7401,21 +7371,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7425,10 +7395,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483084</v>
+        <v>483144</v>
       </c>
       <c r="R67" t="n">
-        <v>6833901</v>
+        <v>6833875</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7487,7 +7457,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121465664</v>
+        <v>121465604</v>
       </c>
       <c r="B68" t="n">
         <v>78345</v>
@@ -7527,13 +7497,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483498</v>
+        <v>483179</v>
       </c>
       <c r="R68" t="n">
-        <v>6834031</v>
+        <v>6833973</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7560,9 +7530,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7577,22 +7557,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469102</v>
+        <v>121469347</v>
       </c>
       <c r="B69" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7605,21 +7585,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7629,10 +7609,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483161</v>
+        <v>483261</v>
       </c>
       <c r="R69" t="n">
-        <v>6834377</v>
+        <v>6834535</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7691,10 +7671,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469110</v>
+        <v>121469104</v>
       </c>
       <c r="B70" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7707,21 +7687,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7731,10 +7711,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483144</v>
+        <v>483265</v>
       </c>
       <c r="R70" t="n">
-        <v>6833875</v>
+        <v>6834572</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7793,10 +7773,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469335</v>
+        <v>121466253</v>
       </c>
       <c r="B71" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7809,37 +7789,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483483</v>
+        <v>483464</v>
       </c>
       <c r="R71" t="n">
-        <v>6833854</v>
+        <v>6833910</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7883,22 +7863,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469106</v>
+        <v>121465202</v>
       </c>
       <c r="B72" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7911,37 +7891,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482967</v>
+        <v>483084</v>
       </c>
       <c r="R72" t="n">
-        <v>6834340</v>
+        <v>6833930</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7968,9 +7948,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7985,22 +7975,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469133</v>
+        <v>121467022</v>
       </c>
       <c r="B73" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8013,21 +8003,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8037,13 +8027,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483241</v>
+        <v>483082</v>
       </c>
       <c r="R73" t="n">
-        <v>6834112</v>
+        <v>6834003</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8070,9 +8060,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8087,22 +8087,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469349</v>
+        <v>121469120</v>
       </c>
       <c r="B74" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483065</v>
+        <v>483153</v>
       </c>
       <c r="R74" t="n">
-        <v>6834469</v>
+        <v>6834504</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469127</v>
+        <v>121469150</v>
       </c>
       <c r="B75" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483514</v>
+        <v>483294</v>
       </c>
       <c r="R75" t="n">
-        <v>6834064</v>
+        <v>6834475</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469157</v>
+        <v>121469117</v>
       </c>
       <c r="B76" t="n">
-        <v>77993</v>
+        <v>78345</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483143</v>
+        <v>483119</v>
       </c>
       <c r="R76" t="n">
-        <v>6833875</v>
+        <v>6834405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,7 +8405,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121465189</v>
+        <v>121469100</v>
       </c>
       <c r="B77" t="n">
         <v>78346</v>
@@ -8441,17 +8441,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483204</v>
+        <v>483211</v>
       </c>
       <c r="R77" t="n">
-        <v>6833925</v>
+        <v>6834254</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8478,19 +8478,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8505,22 +8495,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469140</v>
+        <v>121469155</v>
       </c>
       <c r="B78" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8533,21 +8523,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8557,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483106</v>
+        <v>482892</v>
       </c>
       <c r="R78" t="n">
-        <v>6834495</v>
+        <v>6834282</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8619,7 +8609,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469333</v>
+        <v>121469348</v>
       </c>
       <c r="B79" t="n">
         <v>79227</v>
@@ -8659,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483059</v>
+        <v>483153</v>
       </c>
       <c r="R79" t="n">
-        <v>6833927</v>
+        <v>6834505</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8721,10 +8711,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469342</v>
+        <v>121467080</v>
       </c>
       <c r="B80" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8737,37 +8727,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483160</v>
+        <v>483038</v>
       </c>
       <c r="R80" t="n">
-        <v>6834377</v>
+        <v>6834006</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8811,22 +8801,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469118</v>
+        <v>121469334</v>
       </c>
       <c r="B81" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8839,21 +8829,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8863,10 +8853,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483210</v>
+        <v>483084</v>
       </c>
       <c r="R81" t="n">
-        <v>6834456</v>
+        <v>6833901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8925,10 +8915,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469100</v>
+        <v>121469149</v>
       </c>
       <c r="B82" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8941,21 +8931,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8965,10 +8955,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483211</v>
+        <v>483268</v>
       </c>
       <c r="R82" t="n">
-        <v>6834254</v>
+        <v>6834459</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9027,10 +9017,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469096</v>
+        <v>121469108</v>
       </c>
       <c r="B83" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9043,21 +9033,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9067,10 +9057,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483058</v>
+        <v>482925</v>
       </c>
       <c r="R83" t="n">
-        <v>6833926</v>
+        <v>6833910</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,10 +9119,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121466253</v>
+        <v>121469333</v>
       </c>
       <c r="B84" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9145,37 +9135,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483464</v>
+        <v>483059</v>
       </c>
       <c r="R84" t="n">
-        <v>6833910</v>
+        <v>6833927</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9219,22 +9209,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469143</v>
+        <v>121465664</v>
       </c>
       <c r="B85" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,37 +9237,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483038</v>
+        <v>483498</v>
       </c>
       <c r="R85" t="n">
-        <v>6834461</v>
+        <v>6834031</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9321,19 +9311,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469122</v>
+        <v>121469118</v>
       </c>
       <c r="B86" t="n">
         <v>78345</v>
@@ -9373,10 +9363,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482967</v>
+        <v>483210</v>
       </c>
       <c r="R86" t="n">
-        <v>6834340</v>
+        <v>6834456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9435,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469150</v>
+        <v>121469114</v>
       </c>
       <c r="B87" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9451,21 +9441,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9475,10 +9465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483294</v>
+        <v>483434</v>
       </c>
       <c r="R87" t="n">
-        <v>6834475</v>
+        <v>6833855</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9537,10 +9527,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469145</v>
+        <v>121469116</v>
       </c>
       <c r="B88" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9553,21 +9543,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9577,10 +9567,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483387</v>
+        <v>483484</v>
       </c>
       <c r="R88" t="n">
-        <v>6833994</v>
+        <v>6833901</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9639,10 +9629,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469120</v>
+        <v>121469147</v>
       </c>
       <c r="B89" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9655,21 +9645,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,10 +9669,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483153</v>
+        <v>483181</v>
       </c>
       <c r="R89" t="n">
-        <v>6834504</v>
+        <v>6834299</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9731,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469117</v>
+        <v>121469128</v>
       </c>
       <c r="B90" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9757,21 +9747,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,10 +9771,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483119</v>
+        <v>483524</v>
       </c>
       <c r="R90" t="n">
-        <v>6834405</v>
+        <v>6834071</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,10 +9833,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469338</v>
+        <v>121469096</v>
       </c>
       <c r="B91" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9859,21 +9849,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9883,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483246</v>
+        <v>483058</v>
       </c>
       <c r="R91" t="n">
-        <v>6834122</v>
+        <v>6833926</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9945,10 +9935,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469344</v>
+        <v>121469156</v>
       </c>
       <c r="B92" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9961,21 +9951,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9985,10 +9975,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483119</v>
+        <v>482876</v>
       </c>
       <c r="R92" t="n">
-        <v>6834405</v>
+        <v>6834258</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,10 +10037,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469156</v>
+        <v>121469337</v>
       </c>
       <c r="B93" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10063,21 +10053,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10087,10 +10077,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>482876</v>
+        <v>483413</v>
       </c>
       <c r="R93" t="n">
-        <v>6834258</v>
+        <v>6834033</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10149,10 +10139,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469347</v>
+        <v>121465246</v>
       </c>
       <c r="B94" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,37 +10155,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483261</v>
+        <v>483187</v>
       </c>
       <c r="R94" t="n">
-        <v>6834535</v>
+        <v>6833888</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10222,9 +10212,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10239,22 +10239,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121465604</v>
+        <v>121465615</v>
       </c>
       <c r="B95" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10297,7 +10297,7 @@
         <v>6833973</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10363,10 +10363,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469341</v>
+        <v>121469071</v>
       </c>
       <c r="B96" t="n">
-        <v>79227</v>
+        <v>57509</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483181</v>
+        <v>483265</v>
       </c>
       <c r="R96" t="n">
-        <v>6834299</v>
+        <v>6834571</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10465,7 +10465,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121467080</v>
+        <v>121469103</v>
       </c>
       <c r="B97" t="n">
         <v>78346</v>
@@ -10501,17 +10501,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483038</v>
+        <v>483145</v>
       </c>
       <c r="R97" t="n">
-        <v>6834006</v>
+        <v>6834394</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465234</v>
+        <v>121466096</v>
       </c>
       <c r="B98" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483201</v>
+        <v>483350</v>
       </c>
       <c r="R98" t="n">
-        <v>6833961</v>
+        <v>6834071</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465426</v>
+        <v>121466059</v>
       </c>
       <c r="B99" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483209</v>
+        <v>483350</v>
       </c>
       <c r="R99" t="n">
-        <v>6833990</v>
+        <v>6834071</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121465024</v>
+        <v>121464931</v>
       </c>
       <c r="B100" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>482987</v>
+        <v>482985</v>
       </c>
       <c r="R100" t="n">
-        <v>6833950</v>
+        <v>6833943</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465052</v>
+        <v>121465266</v>
       </c>
       <c r="B101" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>482987</v>
+        <v>483204</v>
       </c>
       <c r="R101" t="n">
-        <v>6833950</v>
+        <v>6833967</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465412</v>
+        <v>121465234</v>
       </c>
       <c r="B102" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483177</v>
+        <v>483201</v>
       </c>
       <c r="R102" t="n">
-        <v>6833971</v>
+        <v>6833961</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,7 +11127,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121466096</v>
+        <v>121465412</v>
       </c>
       <c r="B103" t="n">
         <v>78345</v>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483350</v>
+        <v>483177</v>
       </c>
       <c r="R103" t="n">
-        <v>6834071</v>
+        <v>6833971</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11232,17 +11232,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465991</v>
+        <v>121465426</v>
       </c>
       <c r="B104" t="n">
-        <v>79719</v>
+        <v>78346</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11251,25 +11251,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483306</v>
+        <v>483209</v>
       </c>
       <c r="R104" t="n">
-        <v>6834009</v>
+        <v>6833990</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11344,14 +11344,14 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121466059</v>
+        <v>121465024</v>
       </c>
       <c r="B105" t="n">
         <v>79227</v>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483350</v>
+        <v>482987</v>
       </c>
       <c r="R105" t="n">
-        <v>6834071</v>
+        <v>6833950</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn, Anders Heggestad, Philipp Weiss, Lars-Erik Nilsson, Bo karlstens, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121464931</v>
+        <v>121465052</v>
       </c>
       <c r="B106" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>482985</v>
+        <v>482987</v>
       </c>
       <c r="R106" t="n">
-        <v>6833943</v>
+        <v>6833950</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121465266</v>
+        <v>121465991</v>
       </c>
       <c r="B108" t="n">
-        <v>79198</v>
+        <v>79719</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11699,25 +11699,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483204</v>
+        <v>483306</v>
       </c>
       <c r="R108" t="n">
-        <v>6833967</v>
+        <v>6834009</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326438</v>
+        <v>121326404</v>
       </c>
       <c r="B2" t="n">
         <v>78346</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483043</v>
+        <v>483018</v>
       </c>
       <c r="R2" t="n">
-        <v>6834195</v>
+        <v>6834214</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326800</v>
+        <v>121326921</v>
       </c>
       <c r="B3" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483205</v>
+        <v>483134</v>
       </c>
       <c r="R3" t="n">
-        <v>6834165</v>
+        <v>6833995</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326179</v>
+        <v>121326737</v>
       </c>
       <c r="B4" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482925</v>
+        <v>483242</v>
       </c>
       <c r="R4" t="n">
-        <v>6834028</v>
+        <v>6834570</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326921</v>
+        <v>121326438</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483134</v>
+        <v>483043</v>
       </c>
       <c r="R5" t="n">
-        <v>6833995</v>
+        <v>6834195</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326404</v>
+        <v>121326800</v>
       </c>
       <c r="B6" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483018</v>
+        <v>483205</v>
       </c>
       <c r="R6" t="n">
-        <v>6834214</v>
+        <v>6834165</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326433</v>
+        <v>121326179</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>78346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483040</v>
+        <v>482925</v>
       </c>
       <c r="R7" t="n">
-        <v>6834198</v>
+        <v>6834028</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326737</v>
+        <v>121326433</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483242</v>
+        <v>483040</v>
       </c>
       <c r="R8" t="n">
-        <v>6834570</v>
+        <v>6834198</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469351</v>
+        <v>121469098</v>
       </c>
       <c r="B9" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482864</v>
+        <v>483445</v>
       </c>
       <c r="R9" t="n">
-        <v>6834255</v>
+        <v>6833857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469133</v>
+        <v>121469110</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483241</v>
+        <v>483144</v>
       </c>
       <c r="R10" t="n">
-        <v>6834112</v>
+        <v>6833875</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469152</v>
+        <v>121469341</v>
       </c>
       <c r="B11" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483169</v>
+        <v>483181</v>
       </c>
       <c r="R11" t="n">
-        <v>6834491</v>
+        <v>6834299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469144</v>
+        <v>121469124</v>
       </c>
       <c r="B12" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483402</v>
+        <v>482865</v>
       </c>
       <c r="R12" t="n">
-        <v>6834000</v>
+        <v>6834254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469115</v>
+        <v>121469112</v>
       </c>
       <c r="B13" t="n">
         <v>78345</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483445</v>
+        <v>483408</v>
       </c>
       <c r="R13" t="n">
-        <v>6833857</v>
+        <v>6833852</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469122</v>
+        <v>121469142</v>
       </c>
       <c r="B14" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482967</v>
+        <v>483076</v>
       </c>
       <c r="R14" t="n">
-        <v>6834340</v>
+        <v>6834476</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469341</v>
+        <v>121465664</v>
       </c>
       <c r="B15" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483181</v>
+        <v>483498</v>
       </c>
       <c r="R15" t="n">
-        <v>6834299</v>
+        <v>6834031</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469098</v>
+        <v>121469125</v>
       </c>
       <c r="B16" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483445</v>
+        <v>483307</v>
       </c>
       <c r="R16" t="n">
-        <v>6833857</v>
+        <v>6833983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469131</v>
+        <v>121469102</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483261</v>
+        <v>483161</v>
       </c>
       <c r="R17" t="n">
-        <v>6834030</v>
+        <v>6834377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469142</v>
+        <v>121469095</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483076</v>
+        <v>482925</v>
       </c>
       <c r="R18" t="n">
-        <v>6834476</v>
+        <v>6833909</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469136</v>
+        <v>121469155</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483198</v>
+        <v>482892</v>
       </c>
       <c r="R19" t="n">
-        <v>6834484</v>
+        <v>6834282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469335</v>
+        <v>121469145</v>
       </c>
       <c r="B20" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483483</v>
+        <v>483387</v>
       </c>
       <c r="R20" t="n">
-        <v>6833854</v>
+        <v>6833994</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469139</v>
+        <v>121469136</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483149</v>
+        <v>483198</v>
       </c>
       <c r="R21" t="n">
-        <v>6834501</v>
+        <v>6834484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469148</v>
+        <v>121469342</v>
       </c>
       <c r="B22" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
         <v>483160</v>
       </c>
       <c r="R22" t="n">
-        <v>6834438</v>
+        <v>6834377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469130</v>
+        <v>121469334</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483307</v>
+        <v>483084</v>
       </c>
       <c r="R23" t="n">
-        <v>6833983</v>
+        <v>6833901</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469126</v>
+        <v>121469101</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483476</v>
+        <v>483168</v>
       </c>
       <c r="R25" t="n">
-        <v>6834017</v>
+        <v>6834333</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469137</v>
+        <v>121467007</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,13 +3163,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483198</v>
+        <v>483082</v>
       </c>
       <c r="R26" t="n">
-        <v>6834476</v>
+        <v>6834003</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3196,9 +3196,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,22 +3223,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121465556</v>
+        <v>121467022</v>
       </c>
       <c r="B27" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,37 +3251,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483536</v>
+        <v>483082</v>
       </c>
       <c r="R27" t="n">
-        <v>6833990</v>
+        <v>6834003</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3298,9 +3308,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3315,22 +3335,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469112</v>
+        <v>121469337</v>
       </c>
       <c r="B28" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3363,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483408</v>
+        <v>483413</v>
       </c>
       <c r="R28" t="n">
-        <v>6833852</v>
+        <v>6834033</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469106</v>
+        <v>121469146</v>
       </c>
       <c r="B29" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482967</v>
+        <v>483260</v>
       </c>
       <c r="R29" t="n">
-        <v>6834340</v>
+        <v>6834060</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469097</v>
+        <v>121469336</v>
       </c>
       <c r="B30" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483408</v>
+        <v>483492</v>
       </c>
       <c r="R30" t="n">
-        <v>6833852</v>
+        <v>6834084</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469340</v>
+        <v>121469345</v>
       </c>
       <c r="B31" t="n">
         <v>79227</v>
@@ -3673,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483211</v>
+        <v>483210</v>
       </c>
       <c r="R31" t="n">
-        <v>6834254</v>
+        <v>6834457</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469345</v>
+        <v>121469349</v>
       </c>
       <c r="B32" t="n">
         <v>79227</v>
@@ -3775,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483210</v>
+        <v>483065</v>
       </c>
       <c r="R32" t="n">
-        <v>6834457</v>
+        <v>6834469</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469127</v>
+        <v>121469117</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483514</v>
+        <v>483119</v>
       </c>
       <c r="R33" t="n">
-        <v>6834064</v>
+        <v>6834405</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469339</v>
+        <v>121469100</v>
       </c>
       <c r="B34" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483213</v>
+        <v>483211</v>
       </c>
       <c r="R34" t="n">
-        <v>6834252</v>
+        <v>6834254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469101</v>
+        <v>121469339</v>
       </c>
       <c r="B35" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483168</v>
+        <v>483213</v>
       </c>
       <c r="R35" t="n">
-        <v>6834333</v>
+        <v>6834252</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4163,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469132</v>
+        <v>121469134</v>
       </c>
       <c r="B36" t="n">
         <v>78609</v>
@@ -4183,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483255</v>
+        <v>483277</v>
       </c>
       <c r="R36" t="n">
-        <v>6834077</v>
+        <v>6834451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469134</v>
+        <v>121469126</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4285,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483277</v>
+        <v>483476</v>
       </c>
       <c r="R37" t="n">
-        <v>6834451</v>
+        <v>6834017</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469338</v>
+        <v>121469103</v>
       </c>
       <c r="B38" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483246</v>
+        <v>483145</v>
       </c>
       <c r="R38" t="n">
-        <v>6834122</v>
+        <v>6834394</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121467007</v>
+        <v>121469347</v>
       </c>
       <c r="B39" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,13 +4509,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483082</v>
+        <v>483261</v>
       </c>
       <c r="R39" t="n">
-        <v>6834003</v>
+        <v>6834535</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4522,19 +4542,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,22 +4559,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469154</v>
+        <v>121469333</v>
       </c>
       <c r="B40" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483081</v>
+        <v>483059</v>
       </c>
       <c r="R40" t="n">
-        <v>6834496</v>
+        <v>6833927</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121465189</v>
+        <v>121469351</v>
       </c>
       <c r="B41" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,37 +4689,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483204</v>
+        <v>482864</v>
       </c>
       <c r="R41" t="n">
-        <v>6833925</v>
+        <v>6834255</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4736,19 +4746,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,22 +4763,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469143</v>
+        <v>121465603</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,37 +4791,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483038</v>
+        <v>483561</v>
       </c>
       <c r="R42" t="n">
-        <v>6834461</v>
+        <v>6833992</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4848,9 +4848,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,19 +4875,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469107</v>
+        <v>121465189</v>
       </c>
       <c r="B43" t="n">
         <v>78346</v>
@@ -4913,17 +4923,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>482865</v>
+        <v>483204</v>
       </c>
       <c r="R43" t="n">
-        <v>6834255</v>
+        <v>6833925</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4950,9 +4960,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4967,19 +4987,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121465160</v>
+        <v>121469132</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5019,13 +5039,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483115</v>
+        <v>483255</v>
       </c>
       <c r="R44" t="n">
-        <v>6833942</v>
+        <v>6834077</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5052,19 +5072,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5079,19 +5089,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469157</v>
+        <v>121469158</v>
       </c>
       <c r="B45" t="n">
         <v>77993</v>
@@ -5131,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483143</v>
+        <v>482967</v>
       </c>
       <c r="R45" t="n">
-        <v>6833875</v>
+        <v>6834339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469070</v>
+        <v>121469120</v>
       </c>
       <c r="B46" t="n">
-        <v>79198</v>
+        <v>78345</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5209,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5233,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483031</v>
+        <v>483153</v>
       </c>
       <c r="R46" t="n">
-        <v>6834425</v>
+        <v>6834504</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469102</v>
+        <v>121465604</v>
       </c>
       <c r="B47" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5311,37 +5321,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483161</v>
+        <v>483179</v>
       </c>
       <c r="R47" t="n">
-        <v>6834377</v>
+        <v>6833973</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5368,9 +5378,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,22 +5405,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469069</v>
+        <v>121469150</v>
       </c>
       <c r="B48" t="n">
-        <v>79198</v>
+        <v>78254</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5413,21 +5433,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5437,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483031</v>
+        <v>483294</v>
       </c>
       <c r="R48" t="n">
-        <v>6834458</v>
+        <v>6834475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5499,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469140</v>
+        <v>121469154</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5539,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483106</v>
+        <v>483081</v>
       </c>
       <c r="R49" t="n">
-        <v>6834495</v>
+        <v>6834496</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469124</v>
+        <v>121469143</v>
       </c>
       <c r="B50" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5617,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5641,10 +5661,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>482865</v>
+        <v>483038</v>
       </c>
       <c r="R50" t="n">
-        <v>6834254</v>
+        <v>6834461</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5703,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469158</v>
+        <v>121469335</v>
       </c>
       <c r="B51" t="n">
-        <v>77993</v>
+        <v>79227</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5719,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5743,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>482967</v>
+        <v>483483</v>
       </c>
       <c r="R51" t="n">
-        <v>6834339</v>
+        <v>6833854</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5805,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469349</v>
+        <v>121467080</v>
       </c>
       <c r="B52" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,37 +5841,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483065</v>
+        <v>483038</v>
       </c>
       <c r="R52" t="n">
-        <v>6834469</v>
+        <v>6834006</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5895,22 +5915,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469350</v>
+        <v>121469140</v>
       </c>
       <c r="B53" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5923,21 +5943,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5947,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483033</v>
+        <v>483106</v>
       </c>
       <c r="R53" t="n">
-        <v>6834458</v>
+        <v>6834495</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121465159</v>
+        <v>121469104</v>
       </c>
       <c r="B54" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6025,37 +6045,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483204</v>
+        <v>483265</v>
       </c>
       <c r="R54" t="n">
-        <v>6833925</v>
+        <v>6834572</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6082,19 +6102,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6109,19 +6119,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469105</v>
+        <v>121469099</v>
       </c>
       <c r="B55" t="n">
         <v>78346</v>
@@ -6161,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483153</v>
+        <v>483482</v>
       </c>
       <c r="R55" t="n">
-        <v>6834504</v>
+        <v>6833855</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6325,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469099</v>
+        <v>121469340</v>
       </c>
       <c r="B57" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483482</v>
+        <v>483211</v>
       </c>
       <c r="R57" t="n">
-        <v>6833855</v>
+        <v>6834254</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469095</v>
+        <v>121469116</v>
       </c>
       <c r="B58" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6443,21 +6453,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6467,10 +6477,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>482925</v>
+        <v>483484</v>
       </c>
       <c r="R58" t="n">
-        <v>6833909</v>
+        <v>6833901</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,10 +6539,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121465603</v>
+        <v>121469343</v>
       </c>
       <c r="B59" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6545,37 +6555,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483561</v>
+        <v>483155</v>
       </c>
       <c r="R59" t="n">
-        <v>6833992</v>
+        <v>6834382</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6602,19 +6612,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6629,22 +6629,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469342</v>
+        <v>121469144</v>
       </c>
       <c r="B60" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6657,21 +6657,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483160</v>
+        <v>483402</v>
       </c>
       <c r="R60" t="n">
-        <v>6834377</v>
+        <v>6834000</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469343</v>
+        <v>121469131</v>
       </c>
       <c r="B61" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,21 +6759,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6783,10 +6783,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483155</v>
+        <v>483261</v>
       </c>
       <c r="R61" t="n">
-        <v>6834382</v>
+        <v>6834030</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469344</v>
+        <v>121469127</v>
       </c>
       <c r="B62" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6861,21 +6861,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483119</v>
+        <v>483514</v>
       </c>
       <c r="R62" t="n">
-        <v>6834405</v>
+        <v>6834064</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,10 +6947,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469125</v>
+        <v>121469128</v>
       </c>
       <c r="B63" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6963,21 +6963,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483307</v>
+        <v>483524</v>
       </c>
       <c r="R63" t="n">
-        <v>6833983</v>
+        <v>6834071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469145</v>
+        <v>121469108</v>
       </c>
       <c r="B64" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7065,21 +7065,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483387</v>
+        <v>482925</v>
       </c>
       <c r="R64" t="n">
-        <v>6833994</v>
+        <v>6833910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7151,10 +7151,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469146</v>
+        <v>121469139</v>
       </c>
       <c r="B65" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7167,21 +7167,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483260</v>
+        <v>483149</v>
       </c>
       <c r="R65" t="n">
-        <v>6834060</v>
+        <v>6834501</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469336</v>
+        <v>121469115</v>
       </c>
       <c r="B66" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7269,21 +7269,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483492</v>
+        <v>483445</v>
       </c>
       <c r="R66" t="n">
-        <v>6834084</v>
+        <v>6833857</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469110</v>
+        <v>121469069</v>
       </c>
       <c r="B67" t="n">
-        <v>78345</v>
+        <v>79198</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,21 +7371,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483144</v>
+        <v>483031</v>
       </c>
       <c r="R67" t="n">
-        <v>6833875</v>
+        <v>6834458</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121465604</v>
+        <v>121469097</v>
       </c>
       <c r="B68" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7473,37 +7473,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483179</v>
+        <v>483408</v>
       </c>
       <c r="R68" t="n">
-        <v>6833973</v>
+        <v>6833852</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7530,19 +7530,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7557,22 +7547,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469347</v>
+        <v>121465556</v>
       </c>
       <c r="B69" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,37 +7575,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483261</v>
+        <v>483536</v>
       </c>
       <c r="R69" t="n">
-        <v>6834535</v>
+        <v>6833990</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7659,22 +7649,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469104</v>
+        <v>121469148</v>
       </c>
       <c r="B70" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7687,21 +7677,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7711,10 +7701,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483265</v>
+        <v>483160</v>
       </c>
       <c r="R70" t="n">
-        <v>6834572</v>
+        <v>6834438</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7773,10 +7763,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121466253</v>
+        <v>121469157</v>
       </c>
       <c r="B71" t="n">
-        <v>78346</v>
+        <v>77993</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7789,37 +7779,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483464</v>
+        <v>483143</v>
       </c>
       <c r="R71" t="n">
-        <v>6833910</v>
+        <v>6833875</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7863,22 +7853,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121465202</v>
+        <v>121469107</v>
       </c>
       <c r="B72" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7891,37 +7881,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483084</v>
+        <v>482865</v>
       </c>
       <c r="R72" t="n">
-        <v>6833930</v>
+        <v>6834255</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7948,19 +7938,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7975,22 +7955,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121467022</v>
+        <v>121469156</v>
       </c>
       <c r="B73" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +7983,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,13 +8007,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483082</v>
+        <v>482876</v>
       </c>
       <c r="R73" t="n">
-        <v>6834003</v>
+        <v>6834258</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8060,19 +8040,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8087,22 +8057,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469120</v>
+        <v>121465202</v>
       </c>
       <c r="B74" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,37 +8085,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483153</v>
+        <v>483084</v>
       </c>
       <c r="R74" t="n">
-        <v>6834504</v>
+        <v>6833930</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8172,9 +8142,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8189,22 +8169,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469150</v>
+        <v>121469350</v>
       </c>
       <c r="B75" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8197,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8221,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483294</v>
+        <v>483033</v>
       </c>
       <c r="R75" t="n">
-        <v>6834475</v>
+        <v>6834458</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8283,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469117</v>
+        <v>121465160</v>
       </c>
       <c r="B76" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8299,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,13 +8323,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483119</v>
+        <v>483115</v>
       </c>
       <c r="R76" t="n">
-        <v>6834405</v>
+        <v>6833942</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8376,9 +8356,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8393,19 +8383,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469100</v>
+        <v>121469105</v>
       </c>
       <c r="B77" t="n">
         <v>78346</v>
@@ -8445,10 +8435,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483211</v>
+        <v>483153</v>
       </c>
       <c r="R77" t="n">
-        <v>6834254</v>
+        <v>6834504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8497,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469155</v>
+        <v>121469096</v>
       </c>
       <c r="B78" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8523,21 +8513,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8547,10 +8537,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>482892</v>
+        <v>483058</v>
       </c>
       <c r="R78" t="n">
-        <v>6834282</v>
+        <v>6833926</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8609,10 +8599,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469348</v>
+        <v>121469137</v>
       </c>
       <c r="B79" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8625,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8639,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483153</v>
+        <v>483198</v>
       </c>
       <c r="R79" t="n">
-        <v>6834505</v>
+        <v>6834476</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8711,10 +8701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121467080</v>
+        <v>121469114</v>
       </c>
       <c r="B80" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8727,37 +8717,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483038</v>
+        <v>483434</v>
       </c>
       <c r="R80" t="n">
-        <v>6834006</v>
+        <v>6833855</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8801,22 +8791,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469334</v>
+        <v>121469122</v>
       </c>
       <c r="B81" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8829,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8853,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483084</v>
+        <v>482967</v>
       </c>
       <c r="R81" t="n">
-        <v>6833901</v>
+        <v>6834340</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8915,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469149</v>
+        <v>121465246</v>
       </c>
       <c r="B82" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8931,37 +8921,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483268</v>
+        <v>483187</v>
       </c>
       <c r="R82" t="n">
-        <v>6834459</v>
+        <v>6833888</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8988,9 +8978,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9005,22 +9005,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469108</v>
+        <v>121465615</v>
       </c>
       <c r="B83" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9033,34 +9033,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>482925</v>
+        <v>483179</v>
       </c>
       <c r="R83" t="n">
-        <v>6833910</v>
+        <v>6833973</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9090,9 +9090,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9107,19 +9117,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469333</v>
+        <v>121469338</v>
       </c>
       <c r="B84" t="n">
         <v>79227</v>
@@ -9159,10 +9169,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483059</v>
+        <v>483246</v>
       </c>
       <c r="R84" t="n">
-        <v>6833927</v>
+        <v>6834122</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9221,10 +9231,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121465664</v>
+        <v>121469106</v>
       </c>
       <c r="B85" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9237,37 +9247,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483498</v>
+        <v>482967</v>
       </c>
       <c r="R85" t="n">
-        <v>6834031</v>
+        <v>6834340</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9311,22 +9321,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469118</v>
+        <v>121469071</v>
       </c>
       <c r="B86" t="n">
-        <v>78345</v>
+        <v>57509</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9339,21 +9349,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9363,10 +9373,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483210</v>
+        <v>483265</v>
       </c>
       <c r="R86" t="n">
-        <v>6834456</v>
+        <v>6834571</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9425,10 +9435,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469114</v>
+        <v>121469070</v>
       </c>
       <c r="B87" t="n">
-        <v>78345</v>
+        <v>79198</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9441,21 +9451,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9465,10 +9475,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483434</v>
+        <v>483031</v>
       </c>
       <c r="R87" t="n">
-        <v>6833855</v>
+        <v>6834425</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9527,10 +9537,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469116</v>
+        <v>121469344</v>
       </c>
       <c r="B88" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9543,21 +9553,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9567,10 +9577,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483484</v>
+        <v>483119</v>
       </c>
       <c r="R88" t="n">
-        <v>6833901</v>
+        <v>6834405</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9629,10 +9639,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469147</v>
+        <v>121469133</v>
       </c>
       <c r="B89" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9645,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9669,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483181</v>
+        <v>483241</v>
       </c>
       <c r="R89" t="n">
-        <v>6834299</v>
+        <v>6834112</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9731,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469128</v>
+        <v>121469149</v>
       </c>
       <c r="B90" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9747,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9771,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483524</v>
+        <v>483268</v>
       </c>
       <c r="R90" t="n">
-        <v>6834071</v>
+        <v>6834459</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9833,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469096</v>
+        <v>121469147</v>
       </c>
       <c r="B91" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9849,21 +9859,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9883,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483058</v>
+        <v>483181</v>
       </c>
       <c r="R91" t="n">
-        <v>6833926</v>
+        <v>6834299</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9935,10 +9945,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469156</v>
+        <v>121469348</v>
       </c>
       <c r="B92" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9951,21 +9961,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9975,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>482876</v>
+        <v>483153</v>
       </c>
       <c r="R92" t="n">
-        <v>6834258</v>
+        <v>6834505</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10037,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469337</v>
+        <v>121469130</v>
       </c>
       <c r="B93" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10053,21 +10063,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10077,10 +10087,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483413</v>
+        <v>483307</v>
       </c>
       <c r="R93" t="n">
-        <v>6834033</v>
+        <v>6833983</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10139,10 +10149,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121465246</v>
+        <v>121469152</v>
       </c>
       <c r="B94" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10155,37 +10165,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483187</v>
+        <v>483169</v>
       </c>
       <c r="R94" t="n">
-        <v>6833888</v>
+        <v>6834491</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10212,19 +10222,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10239,22 +10239,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121465615</v>
+        <v>121466253</v>
       </c>
       <c r="B95" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10291,13 +10291,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483179</v>
+        <v>483464</v>
       </c>
       <c r="R95" t="n">
-        <v>6833973</v>
+        <v>6833910</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10324,19 +10324,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10351,22 +10341,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469071</v>
+        <v>121469118</v>
       </c>
       <c r="B96" t="n">
-        <v>57509</v>
+        <v>78345</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,21 +10369,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10403,10 +10393,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483265</v>
+        <v>483210</v>
       </c>
       <c r="R96" t="n">
-        <v>6834571</v>
+        <v>6834456</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10465,10 +10455,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469103</v>
+        <v>121465159</v>
       </c>
       <c r="B97" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,37 +10471,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483145</v>
+        <v>483204</v>
       </c>
       <c r="R97" t="n">
-        <v>6834394</v>
+        <v>6833925</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10538,9 +10528,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121466096</v>
+        <v>121465991</v>
       </c>
       <c r="B98" t="n">
-        <v>78345</v>
+        <v>79719</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,25 +10579,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483350</v>
+        <v>483306</v>
       </c>
       <c r="R98" t="n">
-        <v>6834071</v>
+        <v>6834009</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121466059</v>
+        <v>121465426</v>
       </c>
       <c r="B99" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483350</v>
+        <v>483209</v>
       </c>
       <c r="R99" t="n">
-        <v>6834071</v>
+        <v>6833990</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121464931</v>
+        <v>121466096</v>
       </c>
       <c r="B100" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>482985</v>
+        <v>483350</v>
       </c>
       <c r="R100" t="n">
-        <v>6833943</v>
+        <v>6834071</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465266</v>
+        <v>121465024</v>
       </c>
       <c r="B101" t="n">
-        <v>79198</v>
+        <v>79227</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483204</v>
+        <v>482987</v>
       </c>
       <c r="R101" t="n">
-        <v>6833967</v>
+        <v>6833950</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,7 +11015,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465234</v>
+        <v>121465052</v>
       </c>
       <c r="B102" t="n">
         <v>78609</v>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483201</v>
+        <v>482987</v>
       </c>
       <c r="R102" t="n">
-        <v>6833961</v>
+        <v>6833950</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121465412</v>
+        <v>121465266</v>
       </c>
       <c r="B103" t="n">
-        <v>78345</v>
+        <v>79198</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483177</v>
+        <v>483204</v>
       </c>
       <c r="R103" t="n">
-        <v>6833971</v>
+        <v>6833967</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465426</v>
+        <v>121465234</v>
       </c>
       <c r="B104" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483209</v>
+        <v>483201</v>
       </c>
       <c r="R104" t="n">
-        <v>6833990</v>
+        <v>6833961</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,7 +11351,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465024</v>
+        <v>121466059</v>
       </c>
       <c r="B105" t="n">
         <v>79227</v>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>482987</v>
+        <v>483350</v>
       </c>
       <c r="R105" t="n">
-        <v>6833950</v>
+        <v>6834071</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11463,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465052</v>
+        <v>121465412</v>
       </c>
       <c r="B106" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>482987</v>
+        <v>483177</v>
       </c>
       <c r="R106" t="n">
-        <v>6833950</v>
+        <v>6833971</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121465991</v>
+        <v>121464931</v>
       </c>
       <c r="B108" t="n">
-        <v>79719</v>
+        <v>78346</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11699,25 +11699,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483306</v>
+        <v>482985</v>
       </c>
       <c r="R108" t="n">
-        <v>6834009</v>
+        <v>6833943</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326404</v>
+        <v>121326921</v>
       </c>
       <c r="B2" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483018</v>
+        <v>483134</v>
       </c>
       <c r="R2" t="n">
-        <v>6834214</v>
+        <v>6833995</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326921</v>
+        <v>121326800</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483134</v>
+        <v>483205</v>
       </c>
       <c r="R3" t="n">
-        <v>6833995</v>
+        <v>6834165</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326737</v>
+        <v>121326179</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483242</v>
+        <v>482925</v>
       </c>
       <c r="R4" t="n">
-        <v>6834570</v>
+        <v>6834028</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326438</v>
+        <v>121326737</v>
       </c>
       <c r="B5" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483043</v>
+        <v>483242</v>
       </c>
       <c r="R5" t="n">
-        <v>6834195</v>
+        <v>6834570</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326800</v>
+        <v>121326438</v>
       </c>
       <c r="B6" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483205</v>
+        <v>483043</v>
       </c>
       <c r="R6" t="n">
-        <v>6834165</v>
+        <v>6834195</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326179</v>
+        <v>121326404</v>
       </c>
       <c r="B7" t="n">
         <v>78346</v>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482925</v>
+        <v>483018</v>
       </c>
       <c r="R7" t="n">
-        <v>6834028</v>
+        <v>6834214</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469098</v>
+        <v>121465160</v>
       </c>
       <c r="B9" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483445</v>
+        <v>483115</v>
       </c>
       <c r="R9" t="n">
-        <v>6833857</v>
+        <v>6833942</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,9 +1462,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,19 +1489,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469110</v>
+        <v>121469120</v>
       </c>
       <c r="B10" t="n">
         <v>78345</v>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483144</v>
+        <v>483153</v>
       </c>
       <c r="R10" t="n">
-        <v>6833875</v>
+        <v>6834504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469341</v>
+        <v>121469070</v>
       </c>
       <c r="B11" t="n">
-        <v>79227</v>
+        <v>79198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483181</v>
+        <v>483031</v>
       </c>
       <c r="R11" t="n">
-        <v>6834299</v>
+        <v>6834425</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469124</v>
+        <v>121469104</v>
       </c>
       <c r="B12" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482865</v>
+        <v>483265</v>
       </c>
       <c r="R12" t="n">
-        <v>6834254</v>
+        <v>6834572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469112</v>
+        <v>121469150</v>
       </c>
       <c r="B13" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483408</v>
+        <v>483294</v>
       </c>
       <c r="R13" t="n">
-        <v>6833852</v>
+        <v>6834475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469142</v>
+        <v>121469155</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483076</v>
+        <v>482892</v>
       </c>
       <c r="R14" t="n">
-        <v>6834476</v>
+        <v>6834282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121465664</v>
+        <v>121469106</v>
       </c>
       <c r="B15" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2027,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483498</v>
+        <v>482967</v>
       </c>
       <c r="R15" t="n">
-        <v>6834031</v>
+        <v>6834340</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469125</v>
+        <v>121469130</v>
       </c>
       <c r="B16" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469102</v>
+        <v>121469110</v>
       </c>
       <c r="B17" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483161</v>
+        <v>483144</v>
       </c>
       <c r="R17" t="n">
-        <v>6834377</v>
+        <v>6833875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469095</v>
+        <v>121469119</v>
       </c>
       <c r="B18" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482925</v>
+        <v>483265</v>
       </c>
       <c r="R18" t="n">
-        <v>6833909</v>
+        <v>6834572</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469155</v>
+        <v>121469117</v>
       </c>
       <c r="B19" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482892</v>
+        <v>483119</v>
       </c>
       <c r="R19" t="n">
-        <v>6834282</v>
+        <v>6834405</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469145</v>
+        <v>121469342</v>
       </c>
       <c r="B20" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483387</v>
+        <v>483160</v>
       </c>
       <c r="R20" t="n">
-        <v>6833994</v>
+        <v>6834377</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469136</v>
+        <v>121469132</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483198</v>
+        <v>483255</v>
       </c>
       <c r="R21" t="n">
-        <v>6834484</v>
+        <v>6834077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469342</v>
+        <v>121469114</v>
       </c>
       <c r="B22" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483160</v>
+        <v>483434</v>
       </c>
       <c r="R22" t="n">
-        <v>6834377</v>
+        <v>6833855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469334</v>
+        <v>121469118</v>
       </c>
       <c r="B23" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483084</v>
+        <v>483210</v>
       </c>
       <c r="R23" t="n">
-        <v>6833901</v>
+        <v>6834456</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469135</v>
+        <v>121469152</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483205</v>
+        <v>483169</v>
       </c>
       <c r="R24" t="n">
-        <v>6834490</v>
+        <v>6834491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469101</v>
+        <v>121469338</v>
       </c>
       <c r="B25" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483168</v>
+        <v>483246</v>
       </c>
       <c r="R25" t="n">
-        <v>6834333</v>
+        <v>6834122</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467007</v>
+        <v>121469103</v>
       </c>
       <c r="B26" t="n">
         <v>78346</v>
@@ -3163,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483082</v>
+        <v>483145</v>
       </c>
       <c r="R26" t="n">
-        <v>6834003</v>
+        <v>6834394</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3196,19 +3206,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3223,22 +3223,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467022</v>
+        <v>121469134</v>
       </c>
       <c r="B27" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483082</v>
+        <v>483277</v>
       </c>
       <c r="R27" t="n">
-        <v>6834003</v>
+        <v>6834451</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3308,19 +3308,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3335,22 +3325,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469337</v>
+        <v>121465202</v>
       </c>
       <c r="B28" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,37 +3353,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483413</v>
+        <v>483084</v>
       </c>
       <c r="R28" t="n">
-        <v>6834033</v>
+        <v>6833930</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3420,9 +3410,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3437,22 +3437,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469146</v>
+        <v>121469125</v>
       </c>
       <c r="B29" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483260</v>
+        <v>483307</v>
       </c>
       <c r="R29" t="n">
-        <v>6834060</v>
+        <v>6833983</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469336</v>
+        <v>121469124</v>
       </c>
       <c r="B30" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483492</v>
+        <v>482865</v>
       </c>
       <c r="R30" t="n">
-        <v>6834084</v>
+        <v>6834254</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469345</v>
+        <v>121469131</v>
       </c>
       <c r="B31" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483210</v>
+        <v>483261</v>
       </c>
       <c r="R31" t="n">
-        <v>6834457</v>
+        <v>6834030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469349</v>
+        <v>121469122</v>
       </c>
       <c r="B32" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483065</v>
+        <v>482967</v>
       </c>
       <c r="R32" t="n">
-        <v>6834469</v>
+        <v>6834340</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469117</v>
+        <v>121469144</v>
       </c>
       <c r="B33" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483119</v>
+        <v>483402</v>
       </c>
       <c r="R33" t="n">
-        <v>6834405</v>
+        <v>6834000</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469100</v>
+        <v>121469347</v>
       </c>
       <c r="B34" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483211</v>
+        <v>483261</v>
       </c>
       <c r="R34" t="n">
-        <v>6834254</v>
+        <v>6834535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469339</v>
+        <v>121469349</v>
       </c>
       <c r="B35" t="n">
         <v>79227</v>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483213</v>
+        <v>483065</v>
       </c>
       <c r="R35" t="n">
-        <v>6834252</v>
+        <v>6834469</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469134</v>
+        <v>121469107</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483277</v>
+        <v>482865</v>
       </c>
       <c r="R36" t="n">
-        <v>6834451</v>
+        <v>6834255</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469103</v>
+        <v>121469336</v>
       </c>
       <c r="B38" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483145</v>
+        <v>483492</v>
       </c>
       <c r="R38" t="n">
-        <v>6834394</v>
+        <v>6834084</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469347</v>
+        <v>121469333</v>
       </c>
       <c r="B39" t="n">
         <v>79227</v>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483261</v>
+        <v>483059</v>
       </c>
       <c r="R39" t="n">
-        <v>6834535</v>
+        <v>6833927</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469333</v>
+        <v>121469345</v>
       </c>
       <c r="B40" t="n">
         <v>79227</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483059</v>
+        <v>483210</v>
       </c>
       <c r="R40" t="n">
-        <v>6833927</v>
+        <v>6834457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469351</v>
+        <v>121467007</v>
       </c>
       <c r="B41" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,13 +4713,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>482864</v>
+        <v>483082</v>
       </c>
       <c r="R41" t="n">
-        <v>6834255</v>
+        <v>6834003</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4746,9 +4746,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,12 +4773,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4887,7 +4897,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121465189</v>
+        <v>121469099</v>
       </c>
       <c r="B43" t="n">
         <v>78346</v>
@@ -4923,17 +4933,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483204</v>
+        <v>483482</v>
       </c>
       <c r="R43" t="n">
-        <v>6833925</v>
+        <v>6833855</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4960,19 +4970,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4987,22 +4987,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469132</v>
+        <v>121469157</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>77993</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483255</v>
+        <v>483143</v>
       </c>
       <c r="R44" t="n">
-        <v>6834077</v>
+        <v>6833875</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469158</v>
+        <v>121469137</v>
       </c>
       <c r="B45" t="n">
-        <v>77993</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482967</v>
+        <v>483198</v>
       </c>
       <c r="R45" t="n">
-        <v>6834339</v>
+        <v>6834476</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469120</v>
+        <v>121469340</v>
       </c>
       <c r="B46" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483153</v>
+        <v>483211</v>
       </c>
       <c r="R46" t="n">
-        <v>6834504</v>
+        <v>6834254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121465604</v>
+        <v>121465159</v>
       </c>
       <c r="B47" t="n">
         <v>78345</v>
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483179</v>
+        <v>483204</v>
       </c>
       <c r="R47" t="n">
-        <v>6833973</v>
+        <v>6833925</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5405,22 +5405,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469150</v>
+        <v>121466253</v>
       </c>
       <c r="B48" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,37 +5433,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483294</v>
+        <v>483464</v>
       </c>
       <c r="R48" t="n">
-        <v>6834475</v>
+        <v>6833910</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5507,22 +5507,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469154</v>
+        <v>121465556</v>
       </c>
       <c r="B49" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,37 +5535,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483081</v>
+        <v>483536</v>
       </c>
       <c r="R49" t="n">
-        <v>6834496</v>
+        <v>6833990</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5609,22 +5609,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469143</v>
+        <v>121469145</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483038</v>
+        <v>483387</v>
       </c>
       <c r="R50" t="n">
-        <v>6834461</v>
+        <v>6833994</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469335</v>
+        <v>121469136</v>
       </c>
       <c r="B51" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483483</v>
+        <v>483198</v>
       </c>
       <c r="R51" t="n">
-        <v>6833854</v>
+        <v>6834484</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469140</v>
+        <v>121469100</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,21 +5943,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483106</v>
+        <v>483211</v>
       </c>
       <c r="R53" t="n">
-        <v>6834495</v>
+        <v>6834254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469104</v>
+        <v>121469069</v>
       </c>
       <c r="B54" t="n">
-        <v>78346</v>
+        <v>79198</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483265</v>
+        <v>483031</v>
       </c>
       <c r="R54" t="n">
-        <v>6834572</v>
+        <v>6834458</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,7 +6131,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469099</v>
+        <v>121469105</v>
       </c>
       <c r="B55" t="n">
         <v>78346</v>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483482</v>
+        <v>483153</v>
       </c>
       <c r="R55" t="n">
-        <v>6833855</v>
+        <v>6834504</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469119</v>
+        <v>121469096</v>
       </c>
       <c r="B56" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6249,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483265</v>
+        <v>483058</v>
       </c>
       <c r="R56" t="n">
-        <v>6834572</v>
+        <v>6833926</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469340</v>
+        <v>121469102</v>
       </c>
       <c r="B57" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483211</v>
+        <v>483161</v>
       </c>
       <c r="R57" t="n">
-        <v>6834254</v>
+        <v>6834377</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469116</v>
+        <v>121469095</v>
       </c>
       <c r="B58" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,21 +6453,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483484</v>
+        <v>482925</v>
       </c>
       <c r="R58" t="n">
-        <v>6833901</v>
+        <v>6833909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469343</v>
+        <v>121469148</v>
       </c>
       <c r="B59" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483155</v>
+        <v>483160</v>
       </c>
       <c r="R59" t="n">
-        <v>6834382</v>
+        <v>6834438</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469144</v>
+        <v>121469146</v>
       </c>
       <c r="B60" t="n">
         <v>78254</v>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483402</v>
+        <v>483260</v>
       </c>
       <c r="R60" t="n">
-        <v>6834000</v>
+        <v>6834060</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469131</v>
+        <v>121465615</v>
       </c>
       <c r="B61" t="n">
         <v>78609</v>
@@ -6779,14 +6779,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483261</v>
+        <v>483179</v>
       </c>
       <c r="R61" t="n">
-        <v>6834030</v>
+        <v>6833973</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6816,9 +6816,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,22 +6843,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469127</v>
+        <v>121469351</v>
       </c>
       <c r="B62" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6861,21 +6871,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6885,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483514</v>
+        <v>482864</v>
       </c>
       <c r="R62" t="n">
-        <v>6834064</v>
+        <v>6834255</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469128</v>
+        <v>121469343</v>
       </c>
       <c r="B63" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6963,21 +6973,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483524</v>
+        <v>483155</v>
       </c>
       <c r="R63" t="n">
-        <v>6834071</v>
+        <v>6834382</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7049,10 +7059,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469108</v>
+        <v>121469156</v>
       </c>
       <c r="B64" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7065,21 +7075,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7089,10 +7099,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>482925</v>
+        <v>482876</v>
       </c>
       <c r="R64" t="n">
-        <v>6833910</v>
+        <v>6834258</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7151,10 +7161,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469139</v>
+        <v>121469158</v>
       </c>
       <c r="B65" t="n">
-        <v>78609</v>
+        <v>77993</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7167,21 +7177,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483149</v>
+        <v>482967</v>
       </c>
       <c r="R65" t="n">
-        <v>6834501</v>
+        <v>6834339</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7253,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469115</v>
+        <v>121469337</v>
       </c>
       <c r="B66" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7269,21 +7279,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7293,10 +7303,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483445</v>
+        <v>483413</v>
       </c>
       <c r="R66" t="n">
-        <v>6833857</v>
+        <v>6834033</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7355,10 +7365,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469069</v>
+        <v>121469335</v>
       </c>
       <c r="B67" t="n">
-        <v>79198</v>
+        <v>79227</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,21 +7381,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7395,10 +7405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483031</v>
+        <v>483483</v>
       </c>
       <c r="R67" t="n">
-        <v>6834458</v>
+        <v>6833854</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7457,10 +7467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469097</v>
+        <v>121469143</v>
       </c>
       <c r="B68" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7473,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7497,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483408</v>
+        <v>483038</v>
       </c>
       <c r="R68" t="n">
-        <v>6833852</v>
+        <v>6834461</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7559,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121465556</v>
+        <v>121469142</v>
       </c>
       <c r="B69" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7575,37 +7585,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483536</v>
+        <v>483076</v>
       </c>
       <c r="R69" t="n">
-        <v>6833990</v>
+        <v>6834476</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7649,22 +7659,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469148</v>
+        <v>121469140</v>
       </c>
       <c r="B70" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7677,21 +7687,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7701,10 +7711,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483160</v>
+        <v>483106</v>
       </c>
       <c r="R70" t="n">
-        <v>6834438</v>
+        <v>6834495</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,10 +7773,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469157</v>
+        <v>121469112</v>
       </c>
       <c r="B71" t="n">
-        <v>77993</v>
+        <v>78345</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7779,21 +7789,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7803,10 +7813,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483143</v>
+        <v>483408</v>
       </c>
       <c r="R71" t="n">
-        <v>6833875</v>
+        <v>6833852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7865,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469107</v>
+        <v>121469128</v>
       </c>
       <c r="B72" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7881,21 +7891,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7905,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482865</v>
+        <v>483524</v>
       </c>
       <c r="R72" t="n">
-        <v>6834255</v>
+        <v>6834071</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7967,10 +7977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469156</v>
+        <v>121465664</v>
       </c>
       <c r="B73" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7983,37 +7993,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>482876</v>
+        <v>483498</v>
       </c>
       <c r="R73" t="n">
-        <v>6834258</v>
+        <v>6834031</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8057,22 +8067,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121465202</v>
+        <v>121467022</v>
       </c>
       <c r="B74" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8085,37 +8095,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483084</v>
+        <v>483082</v>
       </c>
       <c r="R74" t="n">
-        <v>6833930</v>
+        <v>6834003</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8144,7 +8154,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8154,7 +8164,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8169,22 +8179,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469350</v>
+        <v>121469127</v>
       </c>
       <c r="B75" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8197,21 +8207,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8221,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483033</v>
+        <v>483514</v>
       </c>
       <c r="R75" t="n">
-        <v>6834458</v>
+        <v>6834064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8283,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121465160</v>
+        <v>121469348</v>
       </c>
       <c r="B76" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8299,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8323,13 +8333,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483115</v>
+        <v>483153</v>
       </c>
       <c r="R76" t="n">
-        <v>6833942</v>
+        <v>6834505</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8356,19 +8366,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8383,22 +8383,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469105</v>
+        <v>121469350</v>
       </c>
       <c r="B77" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8411,21 +8411,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483153</v>
+        <v>483033</v>
       </c>
       <c r="R77" t="n">
-        <v>6834504</v>
+        <v>6834458</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8497,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469096</v>
+        <v>121469341</v>
       </c>
       <c r="B78" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,21 +8513,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483058</v>
+        <v>483181</v>
       </c>
       <c r="R78" t="n">
-        <v>6833926</v>
+        <v>6834299</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8599,10 +8599,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469137</v>
+        <v>121469101</v>
       </c>
       <c r="B79" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483198</v>
+        <v>483168</v>
       </c>
       <c r="R79" t="n">
-        <v>6834476</v>
+        <v>6834333</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469114</v>
+        <v>121469097</v>
       </c>
       <c r="B80" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483434</v>
+        <v>483408</v>
       </c>
       <c r="R80" t="n">
-        <v>6833855</v>
+        <v>6833852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469122</v>
+        <v>121469139</v>
       </c>
       <c r="B81" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>482967</v>
+        <v>483149</v>
       </c>
       <c r="R81" t="n">
-        <v>6834340</v>
+        <v>6834501</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8905,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121465246</v>
+        <v>121469071</v>
       </c>
       <c r="B82" t="n">
-        <v>78345</v>
+        <v>57509</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,37 +8921,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483187</v>
+        <v>483265</v>
       </c>
       <c r="R82" t="n">
-        <v>6833888</v>
+        <v>6834571</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8978,19 +8978,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9005,22 +8995,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121465615</v>
+        <v>121469116</v>
       </c>
       <c r="B83" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9033,34 +9023,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483179</v>
+        <v>483484</v>
       </c>
       <c r="R83" t="n">
-        <v>6833973</v>
+        <v>6833901</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9090,19 +9080,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9117,22 +9097,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469338</v>
+        <v>121469154</v>
       </c>
       <c r="B84" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9145,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9169,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483246</v>
+        <v>483081</v>
       </c>
       <c r="R84" t="n">
-        <v>6834122</v>
+        <v>6834496</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9231,10 +9211,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469106</v>
+        <v>121469149</v>
       </c>
       <c r="B85" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,21 +9227,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9271,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>482967</v>
+        <v>483268</v>
       </c>
       <c r="R85" t="n">
-        <v>6834340</v>
+        <v>6834459</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9333,10 +9313,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469071</v>
+        <v>121469334</v>
       </c>
       <c r="B86" t="n">
-        <v>57509</v>
+        <v>79227</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9349,21 +9329,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9373,10 +9353,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483265</v>
+        <v>483084</v>
       </c>
       <c r="R86" t="n">
-        <v>6834571</v>
+        <v>6833901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9435,10 +9415,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469070</v>
+        <v>121465246</v>
       </c>
       <c r="B87" t="n">
-        <v>79198</v>
+        <v>78345</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9451,37 +9431,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483031</v>
+        <v>483187</v>
       </c>
       <c r="R87" t="n">
-        <v>6834425</v>
+        <v>6833888</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,9 +9488,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9525,22 +9515,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469344</v>
+        <v>121465604</v>
       </c>
       <c r="B88" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9553,37 +9543,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483119</v>
+        <v>483179</v>
       </c>
       <c r="R88" t="n">
-        <v>6834405</v>
+        <v>6833973</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9610,9 +9600,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9627,22 +9627,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469133</v>
+        <v>121469108</v>
       </c>
       <c r="B89" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483241</v>
+        <v>482925</v>
       </c>
       <c r="R89" t="n">
-        <v>6834112</v>
+        <v>6833910</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469149</v>
+        <v>121469098</v>
       </c>
       <c r="B90" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9757,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483268</v>
+        <v>483445</v>
       </c>
       <c r="R90" t="n">
-        <v>6834459</v>
+        <v>6833857</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469147</v>
+        <v>121465189</v>
       </c>
       <c r="B91" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9859,37 +9859,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483181</v>
+        <v>483204</v>
       </c>
       <c r="R91" t="n">
-        <v>6834299</v>
+        <v>6833925</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9916,9 +9916,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9933,22 +9943,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469348</v>
+        <v>121469115</v>
       </c>
       <c r="B92" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9961,21 +9971,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9985,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483153</v>
+        <v>483445</v>
       </c>
       <c r="R92" t="n">
-        <v>6834505</v>
+        <v>6833857</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,7 +10057,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469130</v>
+        <v>121469133</v>
       </c>
       <c r="B93" t="n">
         <v>78609</v>
@@ -10087,10 +10097,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483307</v>
+        <v>483241</v>
       </c>
       <c r="R93" t="n">
-        <v>6833983</v>
+        <v>6834112</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10149,7 +10159,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469152</v>
+        <v>121469147</v>
       </c>
       <c r="B94" t="n">
         <v>78254</v>
@@ -10189,10 +10199,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483169</v>
+        <v>483181</v>
       </c>
       <c r="R94" t="n">
-        <v>6834491</v>
+        <v>6834299</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10251,10 +10261,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121466253</v>
+        <v>121469339</v>
       </c>
       <c r="B95" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10267,37 +10277,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483464</v>
+        <v>483213</v>
       </c>
       <c r="R95" t="n">
-        <v>6833910</v>
+        <v>6834252</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10341,22 +10351,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469118</v>
+        <v>121469344</v>
       </c>
       <c r="B96" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10369,21 +10379,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10393,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483210</v>
+        <v>483119</v>
       </c>
       <c r="R96" t="n">
-        <v>6834456</v>
+        <v>6834405</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10455,10 +10465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121465159</v>
+        <v>121469135</v>
       </c>
       <c r="B97" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10471,37 +10481,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483204</v>
+        <v>483205</v>
       </c>
       <c r="R97" t="n">
-        <v>6833925</v>
+        <v>6834490</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10528,19 +10538,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465991</v>
+        <v>121466059</v>
       </c>
       <c r="B98" t="n">
-        <v>79719</v>
+        <v>79227</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,25 +10579,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483306</v>
+        <v>483350</v>
       </c>
       <c r="R98" t="n">
-        <v>6834009</v>
+        <v>6834071</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465426</v>
+        <v>121465024</v>
       </c>
       <c r="B99" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483209</v>
+        <v>482987</v>
       </c>
       <c r="R99" t="n">
-        <v>6833990</v>
+        <v>6833950</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121466096</v>
+        <v>121465991</v>
       </c>
       <c r="B100" t="n">
-        <v>78345</v>
+        <v>79719</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10803,25 +10803,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483350</v>
+        <v>483306</v>
       </c>
       <c r="R100" t="n">
-        <v>6834071</v>
+        <v>6834009</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465024</v>
+        <v>121465017</v>
       </c>
       <c r="B101" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465052</v>
+        <v>121465412</v>
       </c>
       <c r="B102" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>482987</v>
+        <v>483177</v>
       </c>
       <c r="R102" t="n">
-        <v>6833950</v>
+        <v>6833971</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121465266</v>
+        <v>121466096</v>
       </c>
       <c r="B103" t="n">
-        <v>79198</v>
+        <v>78345</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483204</v>
+        <v>483350</v>
       </c>
       <c r="R103" t="n">
-        <v>6833967</v>
+        <v>6834071</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465234</v>
+        <v>121465266</v>
       </c>
       <c r="B104" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483201</v>
+        <v>483204</v>
       </c>
       <c r="R104" t="n">
-        <v>6833961</v>
+        <v>6833967</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121466059</v>
+        <v>121465052</v>
       </c>
       <c r="B105" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483350</v>
+        <v>482987</v>
       </c>
       <c r="R105" t="n">
-        <v>6834071</v>
+        <v>6833950</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11463,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465412</v>
+        <v>121465234</v>
       </c>
       <c r="B106" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483177</v>
+        <v>483201</v>
       </c>
       <c r="R106" t="n">
-        <v>6833971</v>
+        <v>6833961</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121465017</v>
+        <v>121464931</v>
       </c>
       <c r="B107" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>482987</v>
+        <v>482985</v>
       </c>
       <c r="R107" t="n">
-        <v>6833950</v>
+        <v>6833943</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,7 +11687,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121464931</v>
+        <v>121465426</v>
       </c>
       <c r="B108" t="n">
         <v>78346</v>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>482985</v>
+        <v>483209</v>
       </c>
       <c r="R108" t="n">
-        <v>6833943</v>
+        <v>6833990</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469155</v>
+        <v>121469106</v>
       </c>
       <c r="B14" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482892</v>
+        <v>482967</v>
       </c>
       <c r="R14" t="n">
-        <v>6834282</v>
+        <v>6834340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469106</v>
+        <v>121469130</v>
       </c>
       <c r="B15" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482967</v>
+        <v>483307</v>
       </c>
       <c r="R15" t="n">
-        <v>6834340</v>
+        <v>6833983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469130</v>
+        <v>121469110</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483307</v>
+        <v>483144</v>
       </c>
       <c r="R16" t="n">
-        <v>6833983</v>
+        <v>6833875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469110</v>
+        <v>121469119</v>
       </c>
       <c r="B17" t="n">
         <v>78345</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483144</v>
+        <v>483265</v>
       </c>
       <c r="R17" t="n">
-        <v>6833875</v>
+        <v>6834572</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469119</v>
+        <v>121469117</v>
       </c>
       <c r="B18" t="n">
         <v>78345</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483265</v>
+        <v>483119</v>
       </c>
       <c r="R18" t="n">
-        <v>6834572</v>
+        <v>6834405</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469117</v>
+        <v>121469342</v>
       </c>
       <c r="B19" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483119</v>
+        <v>483160</v>
       </c>
       <c r="R19" t="n">
-        <v>6834405</v>
+        <v>6834377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469342</v>
+        <v>121469155</v>
       </c>
       <c r="B20" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483160</v>
+        <v>482892</v>
       </c>
       <c r="R20" t="n">
-        <v>6834377</v>
+        <v>6834282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -5101,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469137</v>
+        <v>121469340</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483198</v>
+        <v>483211</v>
       </c>
       <c r="R45" t="n">
-        <v>6834476</v>
+        <v>6834254</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469340</v>
+        <v>121465556</v>
       </c>
       <c r="B46" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,37 +5219,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483211</v>
+        <v>483536</v>
       </c>
       <c r="R46" t="n">
-        <v>6834254</v>
+        <v>6833990</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5293,22 +5293,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121465159</v>
+        <v>121466253</v>
       </c>
       <c r="B47" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483204</v>
+        <v>483464</v>
       </c>
       <c r="R47" t="n">
-        <v>6833925</v>
+        <v>6833910</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5378,19 +5378,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5405,22 +5395,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121466253</v>
+        <v>121465159</v>
       </c>
       <c r="B48" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5457,13 +5447,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483464</v>
+        <v>483204</v>
       </c>
       <c r="R48" t="n">
-        <v>6833910</v>
+        <v>6833925</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5490,9 +5480,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5507,22 +5507,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121465556</v>
+        <v>121469137</v>
       </c>
       <c r="B49" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,37 +5535,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483536</v>
+        <v>483198</v>
       </c>
       <c r="R49" t="n">
-        <v>6833990</v>
+        <v>6834476</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5609,22 +5609,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469145</v>
+        <v>121467080</v>
       </c>
       <c r="B50" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,37 +5637,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483387</v>
+        <v>483038</v>
       </c>
       <c r="R50" t="n">
-        <v>6833994</v>
+        <v>6834006</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5711,22 +5711,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469136</v>
+        <v>121469100</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483198</v>
+        <v>483211</v>
       </c>
       <c r="R51" t="n">
-        <v>6834484</v>
+        <v>6834254</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121467080</v>
+        <v>121469145</v>
       </c>
       <c r="B52" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,37 +5841,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483038</v>
+        <v>483387</v>
       </c>
       <c r="R52" t="n">
-        <v>6834006</v>
+        <v>6833994</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5915,22 +5915,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469100</v>
+        <v>121469069</v>
       </c>
       <c r="B53" t="n">
-        <v>78346</v>
+        <v>79198</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,21 +5943,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483211</v>
+        <v>483031</v>
       </c>
       <c r="R53" t="n">
-        <v>6834254</v>
+        <v>6834458</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469069</v>
+        <v>121469136</v>
       </c>
       <c r="B54" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483031</v>
+        <v>483198</v>
       </c>
       <c r="R54" t="n">
-        <v>6834458</v>
+        <v>6834484</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7875,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469128</v>
+        <v>121469101</v>
       </c>
       <c r="B72" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483524</v>
+        <v>483168</v>
       </c>
       <c r="R72" t="n">
-        <v>6834071</v>
+        <v>6834333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,10 +7977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121465664</v>
+        <v>121469097</v>
       </c>
       <c r="B73" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7993,37 +7993,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483498</v>
+        <v>483408</v>
       </c>
       <c r="R73" t="n">
-        <v>6834031</v>
+        <v>6833852</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8067,22 +8067,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121467022</v>
+        <v>121469348</v>
       </c>
       <c r="B74" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8095,21 +8095,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8119,13 +8119,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483082</v>
+        <v>483153</v>
       </c>
       <c r="R74" t="n">
-        <v>6834003</v>
+        <v>6834505</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8152,19 +8152,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8179,22 +8169,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469127</v>
+        <v>121469350</v>
       </c>
       <c r="B75" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8197,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8231,10 +8221,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483514</v>
+        <v>483033</v>
       </c>
       <c r="R75" t="n">
-        <v>6834064</v>
+        <v>6834458</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,7 +8283,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469348</v>
+        <v>121469341</v>
       </c>
       <c r="B76" t="n">
         <v>79227</v>
@@ -8333,10 +8323,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483153</v>
+        <v>483181</v>
       </c>
       <c r="R76" t="n">
-        <v>6834505</v>
+        <v>6834299</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,10 +8385,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469350</v>
+        <v>121469128</v>
       </c>
       <c r="B77" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8411,21 +8401,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8435,10 +8425,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483033</v>
+        <v>483524</v>
       </c>
       <c r="R77" t="n">
-        <v>6834458</v>
+        <v>6834071</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8487,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469341</v>
+        <v>121465664</v>
       </c>
       <c r="B78" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,37 +8503,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483181</v>
+        <v>483498</v>
       </c>
       <c r="R78" t="n">
-        <v>6834299</v>
+        <v>6834031</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8587,22 +8577,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469101</v>
+        <v>121467022</v>
       </c>
       <c r="B79" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8605,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,13 +8629,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483168</v>
+        <v>483082</v>
       </c>
       <c r="R79" t="n">
-        <v>6834333</v>
+        <v>6834003</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8672,9 +8662,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8689,22 +8689,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469097</v>
+        <v>121469127</v>
       </c>
       <c r="B80" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483408</v>
+        <v>483514</v>
       </c>
       <c r="R80" t="n">
-        <v>6833852</v>
+        <v>6834064</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469139</v>
+        <v>121469116</v>
       </c>
       <c r="B81" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483149</v>
+        <v>483484</v>
       </c>
       <c r="R81" t="n">
-        <v>6834501</v>
+        <v>6833901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8905,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469071</v>
+        <v>121469154</v>
       </c>
       <c r="B82" t="n">
-        <v>57509</v>
+        <v>78254</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483265</v>
+        <v>483081</v>
       </c>
       <c r="R82" t="n">
-        <v>6834571</v>
+        <v>6834496</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469116</v>
+        <v>121469149</v>
       </c>
       <c r="B83" t="n">
-        <v>78345</v>
+        <v>78254</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9023,21 +9023,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483484</v>
+        <v>483268</v>
       </c>
       <c r="R83" t="n">
-        <v>6833901</v>
+        <v>6834459</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469154</v>
+        <v>121469139</v>
       </c>
       <c r="B84" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483081</v>
+        <v>483149</v>
       </c>
       <c r="R84" t="n">
-        <v>6834496</v>
+        <v>6834501</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9211,10 +9211,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469149</v>
+        <v>121469071</v>
       </c>
       <c r="B85" t="n">
-        <v>78254</v>
+        <v>57509</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9227,21 +9227,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483268</v>
+        <v>483265</v>
       </c>
       <c r="R85" t="n">
-        <v>6834459</v>
+        <v>6834571</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465266</v>
+        <v>121465052</v>
       </c>
       <c r="B104" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483204</v>
+        <v>482987</v>
       </c>
       <c r="R104" t="n">
-        <v>6833967</v>
+        <v>6833950</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465052</v>
+        <v>121465266</v>
       </c>
       <c r="B105" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>482987</v>
+        <v>483204</v>
       </c>
       <c r="R105" t="n">
-        <v>6833950</v>
+        <v>6833967</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -6131,10 +6131,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469105</v>
+        <v>121469148</v>
       </c>
       <c r="B55" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483153</v>
+        <v>483160</v>
       </c>
       <c r="R55" t="n">
-        <v>6834504</v>
+        <v>6834438</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469096</v>
+        <v>121469146</v>
       </c>
       <c r="B56" t="n">
-        <v>78346</v>
+        <v>78254</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6249,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483058</v>
+        <v>483260</v>
       </c>
       <c r="R56" t="n">
-        <v>6833926</v>
+        <v>6834060</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469102</v>
+        <v>121465615</v>
       </c>
       <c r="B57" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,34 +6351,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483161</v>
+        <v>483179</v>
       </c>
       <c r="R57" t="n">
-        <v>6834377</v>
+        <v>6833973</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,9 +6408,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,22 +6435,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469095</v>
+        <v>121469351</v>
       </c>
       <c r="B58" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,21 +6463,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6477,10 +6487,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>482925</v>
+        <v>482864</v>
       </c>
       <c r="R58" t="n">
-        <v>6833909</v>
+        <v>6834255</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6539,10 +6549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469148</v>
+        <v>121469105</v>
       </c>
       <c r="B59" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6579,10 +6589,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483160</v>
+        <v>483153</v>
       </c>
       <c r="R59" t="n">
-        <v>6834438</v>
+        <v>6834504</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6641,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469146</v>
+        <v>121469096</v>
       </c>
       <c r="B60" t="n">
-        <v>78254</v>
+        <v>78346</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6657,21 +6667,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6681,10 +6691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483260</v>
+        <v>483058</v>
       </c>
       <c r="R60" t="n">
-        <v>6834060</v>
+        <v>6833926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,10 +6753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121465615</v>
+        <v>121469102</v>
       </c>
       <c r="B61" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,34 +6769,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483179</v>
+        <v>483161</v>
       </c>
       <c r="R61" t="n">
-        <v>6833973</v>
+        <v>6834377</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6816,19 +6826,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6843,22 +6843,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469351</v>
+        <v>121469095</v>
       </c>
       <c r="B62" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6871,21 +6871,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>482864</v>
+        <v>482925</v>
       </c>
       <c r="R62" t="n">
-        <v>6834255</v>
+        <v>6833909</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7875,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469101</v>
+        <v>121469128</v>
       </c>
       <c r="B72" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483168</v>
+        <v>483524</v>
       </c>
       <c r="R72" t="n">
-        <v>6834333</v>
+        <v>6834071</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,10 +7977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469097</v>
+        <v>121465664</v>
       </c>
       <c r="B73" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7993,37 +7993,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483408</v>
+        <v>483498</v>
       </c>
       <c r="R73" t="n">
-        <v>6833852</v>
+        <v>6834031</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8067,22 +8067,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469348</v>
+        <v>121467022</v>
       </c>
       <c r="B74" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8095,21 +8095,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8119,13 +8119,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483153</v>
+        <v>483082</v>
       </c>
       <c r="R74" t="n">
-        <v>6834505</v>
+        <v>6834003</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8152,9 +8152,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8169,22 +8179,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469350</v>
+        <v>121469127</v>
       </c>
       <c r="B75" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8197,21 +8207,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8221,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483033</v>
+        <v>483514</v>
       </c>
       <c r="R75" t="n">
-        <v>6834458</v>
+        <v>6834064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8283,7 +8293,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469341</v>
+        <v>121469348</v>
       </c>
       <c r="B76" t="n">
         <v>79227</v>
@@ -8323,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483181</v>
+        <v>483153</v>
       </c>
       <c r="R76" t="n">
-        <v>6834299</v>
+        <v>6834505</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8385,10 +8395,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469128</v>
+        <v>121469350</v>
       </c>
       <c r="B77" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8401,21 +8411,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8425,10 +8435,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483524</v>
+        <v>483033</v>
       </c>
       <c r="R77" t="n">
-        <v>6834071</v>
+        <v>6834458</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8487,10 +8497,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121465664</v>
+        <v>121469341</v>
       </c>
       <c r="B78" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8503,37 +8513,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483498</v>
+        <v>483181</v>
       </c>
       <c r="R78" t="n">
-        <v>6834031</v>
+        <v>6834299</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8577,22 +8587,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121467022</v>
+        <v>121469101</v>
       </c>
       <c r="B79" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8605,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8629,13 +8639,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483082</v>
+        <v>483168</v>
       </c>
       <c r="R79" t="n">
-        <v>6834003</v>
+        <v>6834333</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8662,19 +8672,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8689,22 +8689,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469127</v>
+        <v>121469097</v>
       </c>
       <c r="B80" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483514</v>
+        <v>483408</v>
       </c>
       <c r="R80" t="n">
-        <v>6834064</v>
+        <v>6833852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469116</v>
+        <v>121469139</v>
       </c>
       <c r="B81" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483484</v>
+        <v>483149</v>
       </c>
       <c r="R81" t="n">
-        <v>6833901</v>
+        <v>6834501</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8905,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469154</v>
+        <v>121469071</v>
       </c>
       <c r="B82" t="n">
-        <v>78254</v>
+        <v>57509</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483081</v>
+        <v>483265</v>
       </c>
       <c r="R82" t="n">
-        <v>6834496</v>
+        <v>6834571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469149</v>
+        <v>121469116</v>
       </c>
       <c r="B83" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9023,21 +9023,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483268</v>
+        <v>483484</v>
       </c>
       <c r="R83" t="n">
-        <v>6834459</v>
+        <v>6833901</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469139</v>
+        <v>121469154</v>
       </c>
       <c r="B84" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483149</v>
+        <v>483081</v>
       </c>
       <c r="R84" t="n">
-        <v>6834501</v>
+        <v>6834496</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9211,10 +9211,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469071</v>
+        <v>121469149</v>
       </c>
       <c r="B85" t="n">
-        <v>57509</v>
+        <v>78254</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9227,21 +9227,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483265</v>
+        <v>483268</v>
       </c>
       <c r="R85" t="n">
-        <v>6834571</v>
+        <v>6834459</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9313,10 +9313,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469334</v>
+        <v>121465246</v>
       </c>
       <c r="B86" t="n">
-        <v>79227</v>
+        <v>78345</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9329,37 +9329,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483084</v>
+        <v>483187</v>
       </c>
       <c r="R86" t="n">
-        <v>6833901</v>
+        <v>6833888</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9386,9 +9386,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9403,19 +9413,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121465246</v>
+        <v>121465604</v>
       </c>
       <c r="B87" t="n">
         <v>78345</v>
@@ -9455,13 +9465,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483187</v>
+        <v>483179</v>
       </c>
       <c r="R87" t="n">
-        <v>6833888</v>
+        <v>6833973</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9490,7 +9500,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9500,7 +9510,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9515,19 +9525,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121465604</v>
+        <v>121469108</v>
       </c>
       <c r="B88" t="n">
         <v>78345</v>
@@ -9563,17 +9573,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483179</v>
+        <v>482925</v>
       </c>
       <c r="R88" t="n">
-        <v>6833973</v>
+        <v>6833910</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9600,19 +9610,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9627,22 +9627,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469108</v>
+        <v>121469334</v>
       </c>
       <c r="B89" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>482925</v>
+        <v>483084</v>
       </c>
       <c r="R89" t="n">
-        <v>6833910</v>
+        <v>6833901</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9843,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121465189</v>
+        <v>121469339</v>
       </c>
       <c r="B91" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9859,37 +9859,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483204</v>
+        <v>483213</v>
       </c>
       <c r="R91" t="n">
-        <v>6833925</v>
+        <v>6834252</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9916,19 +9916,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9943,22 +9933,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469115</v>
+        <v>121469344</v>
       </c>
       <c r="B92" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9971,21 +9961,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9995,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483445</v>
+        <v>483119</v>
       </c>
       <c r="R92" t="n">
-        <v>6833857</v>
+        <v>6834405</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10057,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469133</v>
+        <v>121469115</v>
       </c>
       <c r="B93" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10073,21 +10063,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10097,10 +10087,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483241</v>
+        <v>483445</v>
       </c>
       <c r="R93" t="n">
-        <v>6834112</v>
+        <v>6833857</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10159,10 +10149,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469147</v>
+        <v>121469133</v>
       </c>
       <c r="B94" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10175,21 +10165,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10199,10 +10189,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483181</v>
+        <v>483241</v>
       </c>
       <c r="R94" t="n">
-        <v>6834299</v>
+        <v>6834112</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10261,10 +10251,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469339</v>
+        <v>121469147</v>
       </c>
       <c r="B95" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10277,21 +10267,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10301,10 +10291,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483213</v>
+        <v>483181</v>
       </c>
       <c r="R95" t="n">
-        <v>6834252</v>
+        <v>6834299</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10363,10 +10353,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469344</v>
+        <v>121465189</v>
       </c>
       <c r="B96" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10379,37 +10369,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483119</v>
+        <v>483204</v>
       </c>
       <c r="R96" t="n">
-        <v>6834405</v>
+        <v>6833925</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10436,9 +10426,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10453,12 +10453,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465052</v>
+        <v>121465266</v>
       </c>
       <c r="B104" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>482987</v>
+        <v>483204</v>
       </c>
       <c r="R104" t="n">
-        <v>6833950</v>
+        <v>6833967</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465266</v>
+        <v>121465052</v>
       </c>
       <c r="B105" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483204</v>
+        <v>482987</v>
       </c>
       <c r="R105" t="n">
-        <v>6833967</v>
+        <v>6833950</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326921</v>
+        <v>121326404</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483134</v>
+        <v>483018</v>
       </c>
       <c r="R2" t="n">
-        <v>6833995</v>
+        <v>6834214</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326800</v>
+        <v>121326179</v>
       </c>
       <c r="B3" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483205</v>
+        <v>482925</v>
       </c>
       <c r="R3" t="n">
-        <v>6834165</v>
+        <v>6834028</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326179</v>
+        <v>121326800</v>
       </c>
       <c r="B4" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482925</v>
+        <v>483205</v>
       </c>
       <c r="R4" t="n">
-        <v>6834028</v>
+        <v>6834165</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121326737</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326438</v>
+        <v>121326433</v>
       </c>
       <c r="B6" t="n">
-        <v>78346</v>
+        <v>79205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483043</v>
+        <v>483040</v>
       </c>
       <c r="R6" t="n">
-        <v>6834195</v>
+        <v>6834198</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121326404</v>
+        <v>121326438</v>
       </c>
       <c r="B7" t="n">
-        <v>78346</v>
+        <v>78353</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483018</v>
+        <v>483043</v>
       </c>
       <c r="R7" t="n">
-        <v>6834214</v>
+        <v>6834195</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326433</v>
+        <v>121326921</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483040</v>
+        <v>483134</v>
       </c>
       <c r="R8" t="n">
-        <v>6834198</v>
+        <v>6833995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121465160</v>
+        <v>121469150</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78261</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483115</v>
+        <v>483294</v>
       </c>
       <c r="R9" t="n">
-        <v>6833942</v>
+        <v>6834475</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,19 +1462,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469120</v>
+        <v>121469156</v>
       </c>
       <c r="B10" t="n">
-        <v>78345</v>
+        <v>78261</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483153</v>
+        <v>482876</v>
       </c>
       <c r="R10" t="n">
-        <v>6834504</v>
+        <v>6834258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469070</v>
+        <v>121469116</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>78352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483031</v>
+        <v>483484</v>
       </c>
       <c r="R11" t="n">
-        <v>6834425</v>
+        <v>6833901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469104</v>
+        <v>121469119</v>
       </c>
       <c r="B12" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469150</v>
+        <v>121469118</v>
       </c>
       <c r="B13" t="n">
-        <v>78254</v>
+        <v>78352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483294</v>
+        <v>483210</v>
       </c>
       <c r="R13" t="n">
-        <v>6834475</v>
+        <v>6834456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469106</v>
+        <v>121469348</v>
       </c>
       <c r="B14" t="n">
-        <v>78346</v>
+        <v>79234</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482967</v>
+        <v>483153</v>
       </c>
       <c r="R14" t="n">
-        <v>6834340</v>
+        <v>6834505</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469130</v>
+        <v>121469338</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483307</v>
+        <v>483246</v>
       </c>
       <c r="R15" t="n">
-        <v>6833983</v>
+        <v>6834122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469110</v>
+        <v>121469102</v>
       </c>
       <c r="B16" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483144</v>
+        <v>483161</v>
       </c>
       <c r="R16" t="n">
-        <v>6833875</v>
+        <v>6834377</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469119</v>
+        <v>121469117</v>
       </c>
       <c r="B17" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483265</v>
+        <v>483119</v>
       </c>
       <c r="R17" t="n">
-        <v>6834572</v>
+        <v>6834405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469117</v>
+        <v>121469343</v>
       </c>
       <c r="B18" t="n">
-        <v>78345</v>
+        <v>79234</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483119</v>
+        <v>483155</v>
       </c>
       <c r="R18" t="n">
-        <v>6834405</v>
+        <v>6834382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469342</v>
+        <v>121469114</v>
       </c>
       <c r="B19" t="n">
-        <v>79227</v>
+        <v>78352</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483160</v>
+        <v>483434</v>
       </c>
       <c r="R19" t="n">
-        <v>6834377</v>
+        <v>6833855</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469155</v>
+        <v>121469127</v>
       </c>
       <c r="B20" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482892</v>
+        <v>483514</v>
       </c>
       <c r="R20" t="n">
-        <v>6834282</v>
+        <v>6834064</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469132</v>
+        <v>121469126</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483255</v>
+        <v>483476</v>
       </c>
       <c r="R21" t="n">
-        <v>6834077</v>
+        <v>6834017</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469114</v>
+        <v>121469071</v>
       </c>
       <c r="B22" t="n">
-        <v>78345</v>
+        <v>57510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483434</v>
+        <v>483265</v>
       </c>
       <c r="R22" t="n">
-        <v>6833855</v>
+        <v>6834571</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469118</v>
+        <v>121467007</v>
       </c>
       <c r="B23" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,13 +2857,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483210</v>
+        <v>483082</v>
       </c>
       <c r="R23" t="n">
-        <v>6834456</v>
+        <v>6834003</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2900,9 +2890,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2917,22 +2917,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469152</v>
+        <v>121469099</v>
       </c>
       <c r="B24" t="n">
-        <v>78254</v>
+        <v>78353</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483169</v>
+        <v>483482</v>
       </c>
       <c r="R24" t="n">
-        <v>6834491</v>
+        <v>6833855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469338</v>
+        <v>121469349</v>
       </c>
       <c r="B25" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483246</v>
+        <v>483065</v>
       </c>
       <c r="R25" t="n">
-        <v>6834122</v>
+        <v>6834469</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469103</v>
+        <v>121469124</v>
       </c>
       <c r="B26" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483145</v>
+        <v>482865</v>
       </c>
       <c r="R26" t="n">
-        <v>6834394</v>
+        <v>6834254</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469134</v>
+        <v>121469335</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483277</v>
+        <v>483483</v>
       </c>
       <c r="R27" t="n">
-        <v>6834451</v>
+        <v>6833854</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121465202</v>
+        <v>121465160</v>
       </c>
       <c r="B28" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,37 +3353,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483084</v>
+        <v>483115</v>
       </c>
       <c r="R28" t="n">
-        <v>6833930</v>
+        <v>6833942</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3437,22 +3437,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469125</v>
+        <v>121469101</v>
       </c>
       <c r="B29" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483307</v>
+        <v>483168</v>
       </c>
       <c r="R29" t="n">
-        <v>6833983</v>
+        <v>6834333</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469124</v>
+        <v>121469105</v>
       </c>
       <c r="B30" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>482865</v>
+        <v>483153</v>
       </c>
       <c r="R30" t="n">
-        <v>6834254</v>
+        <v>6834504</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469131</v>
+        <v>121469140</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483261</v>
+        <v>483106</v>
       </c>
       <c r="R31" t="n">
-        <v>6834030</v>
+        <v>6834495</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469122</v>
+        <v>121469144</v>
       </c>
       <c r="B32" t="n">
-        <v>78345</v>
+        <v>78261</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482967</v>
+        <v>483402</v>
       </c>
       <c r="R32" t="n">
-        <v>6834340</v>
+        <v>6834000</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469144</v>
+        <v>121469142</v>
       </c>
       <c r="B33" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483402</v>
+        <v>483076</v>
       </c>
       <c r="R33" t="n">
-        <v>6834000</v>
+        <v>6834476</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469347</v>
+        <v>121469342</v>
       </c>
       <c r="B34" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483261</v>
+        <v>483160</v>
       </c>
       <c r="R34" t="n">
-        <v>6834535</v>
+        <v>6834377</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469349</v>
+        <v>121469112</v>
       </c>
       <c r="B35" t="n">
-        <v>79227</v>
+        <v>78352</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483065</v>
+        <v>483408</v>
       </c>
       <c r="R35" t="n">
-        <v>6834469</v>
+        <v>6833852</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469107</v>
+        <v>121469106</v>
       </c>
       <c r="B36" t="n">
-        <v>78346</v>
+        <v>78353</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>482865</v>
+        <v>482967</v>
       </c>
       <c r="R36" t="n">
-        <v>6834255</v>
+        <v>6834340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469126</v>
+        <v>121469097</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483476</v>
+        <v>483408</v>
       </c>
       <c r="R37" t="n">
-        <v>6834017</v>
+        <v>6833852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469336</v>
+        <v>121469103</v>
       </c>
       <c r="B38" t="n">
-        <v>79227</v>
+        <v>78353</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483492</v>
+        <v>483145</v>
       </c>
       <c r="R38" t="n">
-        <v>6834084</v>
+        <v>6834394</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469333</v>
+        <v>121469100</v>
       </c>
       <c r="B39" t="n">
-        <v>79227</v>
+        <v>78353</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483059</v>
+        <v>483211</v>
       </c>
       <c r="R39" t="n">
-        <v>6833927</v>
+        <v>6834254</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469345</v>
+        <v>121469132</v>
       </c>
       <c r="B40" t="n">
-        <v>79227</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483210</v>
+        <v>483255</v>
       </c>
       <c r="R40" t="n">
-        <v>6834457</v>
+        <v>6834077</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121467007</v>
+        <v>121469125</v>
       </c>
       <c r="B41" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,13 +4713,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483082</v>
+        <v>483307</v>
       </c>
       <c r="R41" t="n">
-        <v>6834003</v>
+        <v>6833983</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4746,19 +4746,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,22 +4763,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121465603</v>
+        <v>121465159</v>
       </c>
       <c r="B42" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4791,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483561</v>
+        <v>483204</v>
       </c>
       <c r="R42" t="n">
-        <v>6833992</v>
+        <v>6833925</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -4860,7 +4850,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4870,7 +4860,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4897,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469099</v>
+        <v>121469120</v>
       </c>
       <c r="B43" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4903,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483482</v>
+        <v>483153</v>
       </c>
       <c r="R43" t="n">
-        <v>6833855</v>
+        <v>6834504</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469157</v>
+        <v>121469108</v>
       </c>
       <c r="B44" t="n">
-        <v>77993</v>
+        <v>78352</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483143</v>
+        <v>482925</v>
       </c>
       <c r="R44" t="n">
-        <v>6833875</v>
+        <v>6833910</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5104,7 +5094,7 @@
         <v>121469340</v>
       </c>
       <c r="B45" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,10 +5193,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121465556</v>
+        <v>121469128</v>
       </c>
       <c r="B46" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,37 +5209,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483536</v>
+        <v>483524</v>
       </c>
       <c r="R46" t="n">
-        <v>6833990</v>
+        <v>6834071</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5293,22 +5283,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121466253</v>
+        <v>121469107</v>
       </c>
       <c r="B47" t="n">
-        <v>78346</v>
+        <v>78353</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,17 +5331,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483464</v>
+        <v>482865</v>
       </c>
       <c r="R47" t="n">
-        <v>6833910</v>
+        <v>6834255</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5395,22 +5385,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121465159</v>
+        <v>121469069</v>
       </c>
       <c r="B48" t="n">
-        <v>78345</v>
+        <v>79205</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,37 +5413,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483204</v>
+        <v>483031</v>
       </c>
       <c r="R48" t="n">
-        <v>6833925</v>
+        <v>6834458</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5480,19 +5470,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5507,22 +5487,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469137</v>
+        <v>121469133</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5559,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483198</v>
+        <v>483241</v>
       </c>
       <c r="R49" t="n">
-        <v>6834476</v>
+        <v>6834112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121467080</v>
+        <v>121469110</v>
       </c>
       <c r="B50" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,37 +5617,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483038</v>
+        <v>483144</v>
       </c>
       <c r="R50" t="n">
-        <v>6834006</v>
+        <v>6833875</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5711,22 +5691,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469100</v>
+        <v>121469136</v>
       </c>
       <c r="B51" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,21 +5719,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5743,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483211</v>
+        <v>483198</v>
       </c>
       <c r="R51" t="n">
-        <v>6834254</v>
+        <v>6834484</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469145</v>
+        <v>121465556</v>
       </c>
       <c r="B52" t="n">
-        <v>78254</v>
+        <v>78353</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,37 +5821,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483387</v>
+        <v>483536</v>
       </c>
       <c r="R52" t="n">
-        <v>6833994</v>
+        <v>6833990</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5915,22 +5895,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469069</v>
+        <v>121465603</v>
       </c>
       <c r="B53" t="n">
-        <v>79198</v>
+        <v>78353</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,37 +5923,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483031</v>
+        <v>483561</v>
       </c>
       <c r="R53" t="n">
-        <v>6834458</v>
+        <v>6833992</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6000,9 +5980,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6017,22 +6007,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469136</v>
+        <v>121469351</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6035,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6059,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483198</v>
+        <v>482864</v>
       </c>
       <c r="R54" t="n">
-        <v>6834484</v>
+        <v>6834255</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,10 +6121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469148</v>
+        <v>121469122</v>
       </c>
       <c r="B55" t="n">
-        <v>78254</v>
+        <v>78352</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,21 +6137,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483160</v>
+        <v>482967</v>
       </c>
       <c r="R55" t="n">
-        <v>6834438</v>
+        <v>6834340</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469146</v>
+        <v>121469098</v>
       </c>
       <c r="B56" t="n">
-        <v>78254</v>
+        <v>78353</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6239,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483260</v>
+        <v>483445</v>
       </c>
       <c r="R56" t="n">
-        <v>6834060</v>
+        <v>6833857</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121465615</v>
+        <v>121469337</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,34 +6341,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483179</v>
+        <v>483413</v>
       </c>
       <c r="R57" t="n">
-        <v>6833973</v>
+        <v>6834033</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,19 +6398,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6435,22 +6415,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469351</v>
+        <v>121469333</v>
       </c>
       <c r="B58" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6487,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>482864</v>
+        <v>483059</v>
       </c>
       <c r="R58" t="n">
-        <v>6834255</v>
+        <v>6833927</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6549,10 +6529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469105</v>
+        <v>121469157</v>
       </c>
       <c r="B59" t="n">
-        <v>78346</v>
+        <v>78000</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6565,21 +6545,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6589,10 +6569,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483153</v>
+        <v>483143</v>
       </c>
       <c r="R59" t="n">
-        <v>6834504</v>
+        <v>6833875</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,10 +6631,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469096</v>
+        <v>121469104</v>
       </c>
       <c r="B60" t="n">
-        <v>78346</v>
+        <v>78353</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6691,10 +6671,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483058</v>
+        <v>483265</v>
       </c>
       <c r="R60" t="n">
-        <v>6833926</v>
+        <v>6834572</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6753,10 +6733,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469102</v>
+        <v>121469096</v>
       </c>
       <c r="B61" t="n">
-        <v>78346</v>
+        <v>78353</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6793,10 +6773,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483161</v>
+        <v>483058</v>
       </c>
       <c r="R61" t="n">
-        <v>6834377</v>
+        <v>6833926</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,10 +6835,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469095</v>
+        <v>121469135</v>
       </c>
       <c r="B62" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6871,21 +6851,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6895,10 +6875,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>482925</v>
+        <v>483205</v>
       </c>
       <c r="R62" t="n">
-        <v>6833909</v>
+        <v>6834490</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,10 +6937,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469343</v>
+        <v>121469152</v>
       </c>
       <c r="B63" t="n">
-        <v>79227</v>
+        <v>78261</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6973,21 +6953,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6997,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483155</v>
+        <v>483169</v>
       </c>
       <c r="R63" t="n">
-        <v>6834382</v>
+        <v>6834491</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7059,10 +7039,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469156</v>
+        <v>121469148</v>
       </c>
       <c r="B64" t="n">
-        <v>78254</v>
+        <v>78261</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7099,10 +7079,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>482876</v>
+        <v>483160</v>
       </c>
       <c r="R64" t="n">
-        <v>6834258</v>
+        <v>6834438</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,10 +7141,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469158</v>
+        <v>121469345</v>
       </c>
       <c r="B65" t="n">
-        <v>77993</v>
+        <v>79234</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7177,21 +7157,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7201,10 +7181,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>482967</v>
+        <v>483210</v>
       </c>
       <c r="R65" t="n">
-        <v>6834339</v>
+        <v>6834457</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,10 +7243,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469337</v>
+        <v>121465615</v>
       </c>
       <c r="B66" t="n">
-        <v>79227</v>
+        <v>78616</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7279,34 +7259,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483413</v>
+        <v>483179</v>
       </c>
       <c r="R66" t="n">
-        <v>6834033</v>
+        <v>6833973</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7336,9 +7316,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7353,22 +7343,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469335</v>
+        <v>121469146</v>
       </c>
       <c r="B67" t="n">
-        <v>79227</v>
+        <v>78261</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7381,21 +7371,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7405,10 +7395,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483483</v>
+        <v>483260</v>
       </c>
       <c r="R67" t="n">
-        <v>6833854</v>
+        <v>6834060</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,10 +7457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469143</v>
+        <v>121469336</v>
       </c>
       <c r="B68" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,21 +7473,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7507,10 +7497,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483038</v>
+        <v>483492</v>
       </c>
       <c r="R68" t="n">
-        <v>6834461</v>
+        <v>6834084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7559,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469142</v>
+        <v>121465664</v>
       </c>
       <c r="B69" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,37 +7575,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483076</v>
+        <v>483498</v>
       </c>
       <c r="R69" t="n">
-        <v>6834476</v>
+        <v>6834031</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7659,22 +7649,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469140</v>
+        <v>121469143</v>
       </c>
       <c r="B70" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7711,10 +7701,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483106</v>
+        <v>483038</v>
       </c>
       <c r="R70" t="n">
-        <v>6834495</v>
+        <v>6834461</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7773,10 +7763,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469112</v>
+        <v>121469154</v>
       </c>
       <c r="B71" t="n">
-        <v>78345</v>
+        <v>78261</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7789,21 +7779,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7813,10 +7803,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483408</v>
+        <v>483081</v>
       </c>
       <c r="R71" t="n">
-        <v>6833852</v>
+        <v>6834496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7875,10 +7865,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469128</v>
+        <v>121469145</v>
       </c>
       <c r="B72" t="n">
-        <v>78609</v>
+        <v>78261</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7891,21 +7881,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7915,10 +7905,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483524</v>
+        <v>483387</v>
       </c>
       <c r="R72" t="n">
-        <v>6834071</v>
+        <v>6833994</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,10 +7967,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121465664</v>
+        <v>121469344</v>
       </c>
       <c r="B73" t="n">
-        <v>78345</v>
+        <v>79234</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7993,37 +7983,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483498</v>
+        <v>483119</v>
       </c>
       <c r="R73" t="n">
-        <v>6834031</v>
+        <v>6834405</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8067,22 +8057,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121467022</v>
+        <v>121467080</v>
       </c>
       <c r="B74" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8095,37 +8085,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483082</v>
+        <v>483038</v>
       </c>
       <c r="R74" t="n">
-        <v>6834003</v>
+        <v>6834006</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8152,19 +8142,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8179,22 +8159,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469127</v>
+        <v>121465202</v>
       </c>
       <c r="B75" t="n">
-        <v>78609</v>
+        <v>78261</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,37 +8187,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483514</v>
+        <v>483084</v>
       </c>
       <c r="R75" t="n">
-        <v>6834064</v>
+        <v>6833930</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8264,9 +8244,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8281,22 +8271,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469348</v>
+        <v>121469070</v>
       </c>
       <c r="B76" t="n">
-        <v>79227</v>
+        <v>79205</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8299,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8323,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483153</v>
+        <v>483031</v>
       </c>
       <c r="R76" t="n">
-        <v>6834505</v>
+        <v>6834425</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,10 +8385,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469350</v>
+        <v>121469155</v>
       </c>
       <c r="B77" t="n">
-        <v>79227</v>
+        <v>78261</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8411,21 +8401,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8435,10 +8425,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483033</v>
+        <v>482892</v>
       </c>
       <c r="R77" t="n">
-        <v>6834458</v>
+        <v>6834282</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8487,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469341</v>
+        <v>121469147</v>
       </c>
       <c r="B78" t="n">
-        <v>79227</v>
+        <v>78261</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,21 +8503,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8599,10 +8589,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469101</v>
+        <v>121469139</v>
       </c>
       <c r="B79" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8605,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,10 +8629,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483168</v>
+        <v>483149</v>
       </c>
       <c r="R79" t="n">
-        <v>6834333</v>
+        <v>6834501</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8701,10 +8691,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469097</v>
+        <v>121469137</v>
       </c>
       <c r="B80" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8707,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8731,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483408</v>
+        <v>483198</v>
       </c>
       <c r="R80" t="n">
-        <v>6833852</v>
+        <v>6834476</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,10 +8793,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469139</v>
+        <v>121465604</v>
       </c>
       <c r="B81" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,37 +8809,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483149</v>
+        <v>483179</v>
       </c>
       <c r="R81" t="n">
-        <v>6834501</v>
+        <v>6833973</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8876,9 +8866,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8893,22 +8893,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469071</v>
+        <v>121469149</v>
       </c>
       <c r="B82" t="n">
-        <v>57509</v>
+        <v>78261</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483265</v>
+        <v>483268</v>
       </c>
       <c r="R82" t="n">
-        <v>6834571</v>
+        <v>6834459</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469116</v>
+        <v>121465246</v>
       </c>
       <c r="B83" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9043,17 +9043,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483484</v>
+        <v>483187</v>
       </c>
       <c r="R83" t="n">
-        <v>6833901</v>
+        <v>6833888</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9080,9 +9080,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9097,22 +9107,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469154</v>
+        <v>121469341</v>
       </c>
       <c r="B84" t="n">
-        <v>78254</v>
+        <v>79234</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,21 +9135,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9149,10 +9159,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483081</v>
+        <v>483181</v>
       </c>
       <c r="R84" t="n">
-        <v>6834496</v>
+        <v>6834299</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9211,10 +9221,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469149</v>
+        <v>121469334</v>
       </c>
       <c r="B85" t="n">
-        <v>78254</v>
+        <v>79234</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9227,21 +9237,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9251,10 +9261,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483268</v>
+        <v>483084</v>
       </c>
       <c r="R85" t="n">
-        <v>6834459</v>
+        <v>6833901</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9313,10 +9323,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121465246</v>
+        <v>121469095</v>
       </c>
       <c r="B86" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9329,37 +9339,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483187</v>
+        <v>482925</v>
       </c>
       <c r="R86" t="n">
-        <v>6833888</v>
+        <v>6833909</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9386,19 +9396,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9413,22 +9413,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121465604</v>
+        <v>121469134</v>
       </c>
       <c r="B87" t="n">
-        <v>78345</v>
+        <v>78616</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9441,37 +9441,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483179</v>
+        <v>483277</v>
       </c>
       <c r="R87" t="n">
-        <v>6833973</v>
+        <v>6834451</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9498,19 +9498,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9525,22 +9515,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469108</v>
+        <v>121469347</v>
       </c>
       <c r="B88" t="n">
-        <v>78345</v>
+        <v>79234</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9553,21 +9543,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9577,10 +9567,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482925</v>
+        <v>483261</v>
       </c>
       <c r="R88" t="n">
-        <v>6833910</v>
+        <v>6834535</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9639,10 +9629,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469334</v>
+        <v>121469350</v>
       </c>
       <c r="B89" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9679,10 +9669,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483084</v>
+        <v>483033</v>
       </c>
       <c r="R89" t="n">
-        <v>6833901</v>
+        <v>6834458</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9731,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469098</v>
+        <v>121469158</v>
       </c>
       <c r="B90" t="n">
-        <v>78346</v>
+        <v>78000</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9757,21 +9747,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,10 +9771,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483445</v>
+        <v>482967</v>
       </c>
       <c r="R90" t="n">
-        <v>6833857</v>
+        <v>6834339</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,10 +9833,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469339</v>
+        <v>121469131</v>
       </c>
       <c r="B91" t="n">
-        <v>79227</v>
+        <v>78616</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9859,21 +9849,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9883,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483213</v>
+        <v>483261</v>
       </c>
       <c r="R91" t="n">
-        <v>6834252</v>
+        <v>6834030</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9945,10 +9935,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469344</v>
+        <v>121469115</v>
       </c>
       <c r="B92" t="n">
-        <v>79227</v>
+        <v>78352</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9961,21 +9951,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9985,10 +9975,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483119</v>
+        <v>483445</v>
       </c>
       <c r="R92" t="n">
-        <v>6834405</v>
+        <v>6833857</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,10 +10037,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469115</v>
+        <v>121465189</v>
       </c>
       <c r="B93" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10063,37 +10053,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483445</v>
+        <v>483204</v>
       </c>
       <c r="R93" t="n">
-        <v>6833857</v>
+        <v>6833925</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10120,9 +10110,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10137,22 +10137,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469133</v>
+        <v>121466253</v>
       </c>
       <c r="B94" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,37 +10165,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483241</v>
+        <v>483464</v>
       </c>
       <c r="R94" t="n">
-        <v>6834112</v>
+        <v>6833910</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10239,22 +10239,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469147</v>
+        <v>121469130</v>
       </c>
       <c r="B95" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483181</v>
+        <v>483307</v>
       </c>
       <c r="R95" t="n">
-        <v>6834299</v>
+        <v>6833983</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121465189</v>
+        <v>121469339</v>
       </c>
       <c r="B96" t="n">
-        <v>78346</v>
+        <v>79234</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10369,37 +10369,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483204</v>
+        <v>483213</v>
       </c>
       <c r="R96" t="n">
-        <v>6833925</v>
+        <v>6834252</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10426,19 +10426,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10453,22 +10443,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121469135</v>
+        <v>121467022</v>
       </c>
       <c r="B97" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10481,21 +10471,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10505,13 +10495,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483205</v>
+        <v>483082</v>
       </c>
       <c r="R97" t="n">
-        <v>6834490</v>
+        <v>6834003</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10538,9 +10528,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121466059</v>
+        <v>121465426</v>
       </c>
       <c r="B98" t="n">
-        <v>79227</v>
+        <v>78353</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483350</v>
+        <v>483209</v>
       </c>
       <c r="R98" t="n">
-        <v>6834071</v>
+        <v>6833990</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465024</v>
+        <v>121464931</v>
       </c>
       <c r="B99" t="n">
-        <v>79227</v>
+        <v>78353</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>482987</v>
+        <v>482985</v>
       </c>
       <c r="R99" t="n">
-        <v>6833950</v>
+        <v>6833943</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121465991</v>
+        <v>121465017</v>
       </c>
       <c r="B100" t="n">
-        <v>79719</v>
+        <v>78352</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10803,25 +10803,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483306</v>
+        <v>482987</v>
       </c>
       <c r="R100" t="n">
-        <v>6834009</v>
+        <v>6833950</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465017</v>
+        <v>121466059</v>
       </c>
       <c r="B101" t="n">
-        <v>78345</v>
+        <v>79234</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>482987</v>
+        <v>483350</v>
       </c>
       <c r="R101" t="n">
-        <v>6833950</v>
+        <v>6834071</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121465412</v>
+        <v>121465234</v>
       </c>
       <c r="B102" t="n">
-        <v>78345</v>
+        <v>78616</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11031,21 +11031,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483177</v>
+        <v>483201</v>
       </c>
       <c r="R102" t="n">
-        <v>6833971</v>
+        <v>6833961</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11130,7 +11130,7 @@
         <v>121466096</v>
       </c>
       <c r="B103" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11239,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121465266</v>
+        <v>121465412</v>
       </c>
       <c r="B104" t="n">
-        <v>79198</v>
+        <v>78352</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483204</v>
+        <v>483177</v>
       </c>
       <c r="R104" t="n">
-        <v>6833967</v>
+        <v>6833971</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465052</v>
+        <v>121465024</v>
       </c>
       <c r="B105" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11463,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465234</v>
+        <v>121465991</v>
       </c>
       <c r="B106" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11475,25 +11475,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483201</v>
+        <v>483306</v>
       </c>
       <c r="R106" t="n">
-        <v>6833961</v>
+        <v>6834009</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121464931</v>
+        <v>121465052</v>
       </c>
       <c r="B107" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>482985</v>
+        <v>482987</v>
       </c>
       <c r="R107" t="n">
-        <v>6833943</v>
+        <v>6833950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121465426</v>
+        <v>121465266</v>
       </c>
       <c r="B108" t="n">
-        <v>78346</v>
+        <v>79205</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483209</v>
+        <v>483204</v>
       </c>
       <c r="R108" t="n">
-        <v>6833990</v>
+        <v>6833967</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326737</v>
+        <v>121326433</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483242</v>
+        <v>483040</v>
       </c>
       <c r="R5" t="n">
-        <v>6834570</v>
+        <v>6834198</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326433</v>
+        <v>121326737</v>
       </c>
       <c r="B6" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483040</v>
+        <v>483242</v>
       </c>
       <c r="R6" t="n">
-        <v>6834198</v>
+        <v>6834570</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469144</v>
+        <v>121469142</v>
       </c>
       <c r="B32" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483402</v>
+        <v>483076</v>
       </c>
       <c r="R32" t="n">
-        <v>6834000</v>
+        <v>6834476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469142</v>
+        <v>121469144</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483076</v>
+        <v>483402</v>
       </c>
       <c r="R33" t="n">
-        <v>6834476</v>
+        <v>6834000</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469100</v>
+        <v>121469120</v>
       </c>
       <c r="B39" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483211</v>
+        <v>483153</v>
       </c>
       <c r="R39" t="n">
-        <v>6834254</v>
+        <v>6834504</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469120</v>
+        <v>121469108</v>
       </c>
       <c r="B43" t="n">
         <v>78352</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483153</v>
+        <v>482925</v>
       </c>
       <c r="R43" t="n">
-        <v>6834504</v>
+        <v>6833910</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469108</v>
+        <v>121469340</v>
       </c>
       <c r="B44" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>482925</v>
+        <v>483211</v>
       </c>
       <c r="R44" t="n">
-        <v>6833910</v>
+        <v>6834254</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469340</v>
+        <v>121469100</v>
       </c>
       <c r="B45" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469133</v>
+        <v>121469110</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483241</v>
+        <v>483144</v>
       </c>
       <c r="R49" t="n">
-        <v>6834112</v>
+        <v>6833875</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469110</v>
+        <v>121469133</v>
       </c>
       <c r="B50" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483144</v>
+        <v>483241</v>
       </c>
       <c r="R50" t="n">
-        <v>6833875</v>
+        <v>6834112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6019,10 +6019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469351</v>
+        <v>121469098</v>
       </c>
       <c r="B54" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6035,21 +6035,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>482864</v>
+        <v>483445</v>
       </c>
       <c r="R54" t="n">
-        <v>6834255</v>
+        <v>6833857</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6121,10 +6121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469122</v>
+        <v>121469351</v>
       </c>
       <c r="B55" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6137,21 +6137,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>482967</v>
+        <v>482864</v>
       </c>
       <c r="R55" t="n">
-        <v>6834340</v>
+        <v>6834255</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469098</v>
+        <v>121469122</v>
       </c>
       <c r="B56" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6239,21 +6239,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483445</v>
+        <v>482967</v>
       </c>
       <c r="R56" t="n">
-        <v>6833857</v>
+        <v>6834340</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7661,10 +7661,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469143</v>
+        <v>121469154</v>
       </c>
       <c r="B70" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7677,21 +7677,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483038</v>
+        <v>483081</v>
       </c>
       <c r="R70" t="n">
-        <v>6834461</v>
+        <v>6834496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469154</v>
+        <v>121469145</v>
       </c>
       <c r="B71" t="n">
         <v>78261</v>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483081</v>
+        <v>483387</v>
       </c>
       <c r="R71" t="n">
-        <v>6834496</v>
+        <v>6833994</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7865,10 +7865,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469145</v>
+        <v>121469143</v>
       </c>
       <c r="B72" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7905,10 +7905,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483387</v>
+        <v>483038</v>
       </c>
       <c r="R72" t="n">
-        <v>6833994</v>
+        <v>6834461</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8905,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469149</v>
+        <v>121465246</v>
       </c>
       <c r="B82" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,37 +8921,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483268</v>
+        <v>483187</v>
       </c>
       <c r="R82" t="n">
-        <v>6834459</v>
+        <v>6833888</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8978,9 +8978,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8995,22 +9005,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121465246</v>
+        <v>121469341</v>
       </c>
       <c r="B83" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9023,37 +9033,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483187</v>
+        <v>483181</v>
       </c>
       <c r="R83" t="n">
-        <v>6833888</v>
+        <v>6834299</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9080,19 +9090,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9107,19 +9107,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469341</v>
+        <v>121469334</v>
       </c>
       <c r="B84" t="n">
         <v>79234</v>
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483181</v>
+        <v>483084</v>
       </c>
       <c r="R84" t="n">
-        <v>6834299</v>
+        <v>6833901</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9221,10 +9221,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469334</v>
+        <v>121469149</v>
       </c>
       <c r="B85" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9237,21 +9237,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9261,10 +9261,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483084</v>
+        <v>483268</v>
       </c>
       <c r="R85" t="n">
-        <v>6833901</v>
+        <v>6834459</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469134</v>
+        <v>121465189</v>
       </c>
       <c r="B87" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9441,37 +9441,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483277</v>
+        <v>483204</v>
       </c>
       <c r="R87" t="n">
-        <v>6834451</v>
+        <v>6833925</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9498,9 +9498,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9515,22 +9525,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469347</v>
+        <v>121466253</v>
       </c>
       <c r="B88" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9543,37 +9553,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483261</v>
+        <v>483464</v>
       </c>
       <c r="R88" t="n">
-        <v>6834535</v>
+        <v>6833910</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9617,19 +9627,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469350</v>
+        <v>121469347</v>
       </c>
       <c r="B89" t="n">
         <v>79234</v>
@@ -9669,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483033</v>
+        <v>483261</v>
       </c>
       <c r="R89" t="n">
-        <v>6834458</v>
+        <v>6834535</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9731,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469158</v>
+        <v>121469350</v>
       </c>
       <c r="B90" t="n">
-        <v>78000</v>
+        <v>79234</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9747,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9771,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482967</v>
+        <v>483033</v>
       </c>
       <c r="R90" t="n">
-        <v>6834339</v>
+        <v>6834458</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9833,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469131</v>
+        <v>121469158</v>
       </c>
       <c r="B91" t="n">
-        <v>78616</v>
+        <v>78000</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9849,21 +9859,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9883,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483261</v>
+        <v>482967</v>
       </c>
       <c r="R91" t="n">
-        <v>6834030</v>
+        <v>6834339</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9935,10 +9945,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469115</v>
+        <v>121469131</v>
       </c>
       <c r="B92" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9951,21 +9961,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9975,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483445</v>
+        <v>483261</v>
       </c>
       <c r="R92" t="n">
-        <v>6833857</v>
+        <v>6834030</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10037,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121465189</v>
+        <v>121469134</v>
       </c>
       <c r="B93" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10053,37 +10063,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483204</v>
+        <v>483277</v>
       </c>
       <c r="R93" t="n">
-        <v>6833925</v>
+        <v>6834451</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10110,19 +10120,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10137,22 +10137,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121466253</v>
+        <v>121469115</v>
       </c>
       <c r="B94" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,37 +10165,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483464</v>
+        <v>483445</v>
       </c>
       <c r="R94" t="n">
-        <v>6833910</v>
+        <v>6833857</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10239,22 +10239,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121469130</v>
+        <v>121469339</v>
       </c>
       <c r="B95" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483307</v>
+        <v>483213</v>
       </c>
       <c r="R95" t="n">
-        <v>6833983</v>
+        <v>6834252</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469339</v>
+        <v>121467022</v>
       </c>
       <c r="B96" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10369,21 +10369,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10393,13 +10393,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483213</v>
+        <v>483082</v>
       </c>
       <c r="R96" t="n">
-        <v>6834252</v>
+        <v>6834003</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10426,9 +10426,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10443,22 +10453,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121467022</v>
+        <v>121469130</v>
       </c>
       <c r="B97" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10471,21 +10481,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10495,13 +10505,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483082</v>
+        <v>483307</v>
       </c>
       <c r="R97" t="n">
-        <v>6834003</v>
+        <v>6833983</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10528,19 +10538,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,12 +10555,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326433</v>
+        <v>121326737</v>
       </c>
       <c r="B5" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappstaden, Lappstaden, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483040</v>
+        <v>483242</v>
       </c>
       <c r="R5" t="n">
-        <v>6834198</v>
+        <v>6834570</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326737</v>
+        <v>121326433</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lappstaden, Lappstaden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483242</v>
+        <v>483040</v>
       </c>
       <c r="R6" t="n">
-        <v>6834570</v>
+        <v>6834198</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469119</v>
+        <v>121469102</v>
       </c>
       <c r="B12" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483265</v>
+        <v>483161</v>
       </c>
       <c r="R12" t="n">
-        <v>6834572</v>
+        <v>6834377</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469118</v>
+        <v>121469119</v>
       </c>
       <c r="B13" t="n">
         <v>78352</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483210</v>
+        <v>483265</v>
       </c>
       <c r="R13" t="n">
-        <v>6834456</v>
+        <v>6834572</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469348</v>
+        <v>121469118</v>
       </c>
       <c r="B14" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483153</v>
+        <v>483210</v>
       </c>
       <c r="R14" t="n">
-        <v>6834505</v>
+        <v>6834456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469338</v>
+        <v>121469348</v>
       </c>
       <c r="B15" t="n">
         <v>79234</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483246</v>
+        <v>483153</v>
       </c>
       <c r="R15" t="n">
-        <v>6834122</v>
+        <v>6834505</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469102</v>
+        <v>121469338</v>
       </c>
       <c r="B16" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483161</v>
+        <v>483246</v>
       </c>
       <c r="R16" t="n">
-        <v>6834377</v>
+        <v>6834122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3755,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469142</v>
+        <v>121469144</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483076</v>
+        <v>483402</v>
       </c>
       <c r="R32" t="n">
-        <v>6834476</v>
+        <v>6834000</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469144</v>
+        <v>121469142</v>
       </c>
       <c r="B33" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483402</v>
+        <v>483076</v>
       </c>
       <c r="R33" t="n">
-        <v>6834000</v>
+        <v>6834476</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469136</v>
+        <v>121465556</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5719,37 +5719,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483198</v>
+        <v>483536</v>
       </c>
       <c r="R51" t="n">
-        <v>6834484</v>
+        <v>6833990</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5793,19 +5793,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121465556</v>
+        <v>121465603</v>
       </c>
       <c r="B52" t="n">
         <v>78353</v>
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483536</v>
+        <v>483561</v>
       </c>
       <c r="R52" t="n">
-        <v>6833990</v>
+        <v>6833992</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5878,9 +5878,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5895,22 +5905,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121465603</v>
+        <v>121469136</v>
       </c>
       <c r="B53" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5923,37 +5933,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483561</v>
+        <v>483198</v>
       </c>
       <c r="R53" t="n">
-        <v>6833992</v>
+        <v>6834484</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5980,19 +5990,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6007,12 +6007,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469337</v>
+        <v>121469135</v>
       </c>
       <c r="B57" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483413</v>
+        <v>483205</v>
       </c>
       <c r="R57" t="n">
-        <v>6834033</v>
+        <v>6834490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469333</v>
+        <v>121469152</v>
       </c>
       <c r="B58" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6443,21 +6443,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483059</v>
+        <v>483169</v>
       </c>
       <c r="R58" t="n">
-        <v>6833927</v>
+        <v>6834491</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,10 +6529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469157</v>
+        <v>121469337</v>
       </c>
       <c r="B59" t="n">
-        <v>78000</v>
+        <v>79234</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6545,21 +6545,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483143</v>
+        <v>483413</v>
       </c>
       <c r="R59" t="n">
-        <v>6833875</v>
+        <v>6834033</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,10 +6631,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469104</v>
+        <v>121469333</v>
       </c>
       <c r="B60" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6647,21 +6647,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483265</v>
+        <v>483059</v>
       </c>
       <c r="R60" t="n">
-        <v>6834572</v>
+        <v>6833927</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6733,10 +6733,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469096</v>
+        <v>121469157</v>
       </c>
       <c r="B61" t="n">
-        <v>78353</v>
+        <v>78000</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483058</v>
+        <v>483143</v>
       </c>
       <c r="R61" t="n">
-        <v>6833926</v>
+        <v>6833875</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469135</v>
+        <v>121469104</v>
       </c>
       <c r="B62" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6851,21 +6851,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483205</v>
+        <v>483265</v>
       </c>
       <c r="R62" t="n">
-        <v>6834490</v>
+        <v>6834572</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469152</v>
+        <v>121469096</v>
       </c>
       <c r="B63" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6953,21 +6953,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483169</v>
+        <v>483058</v>
       </c>
       <c r="R63" t="n">
-        <v>6834491</v>
+        <v>6833926</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7661,10 +7661,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469154</v>
+        <v>121469143</v>
       </c>
       <c r="B70" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7677,21 +7677,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483081</v>
+        <v>483038</v>
       </c>
       <c r="R70" t="n">
-        <v>6834496</v>
+        <v>6834461</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469145</v>
+        <v>121469154</v>
       </c>
       <c r="B71" t="n">
         <v>78261</v>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483387</v>
+        <v>483081</v>
       </c>
       <c r="R71" t="n">
-        <v>6833994</v>
+        <v>6834496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7865,10 +7865,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469143</v>
+        <v>121469145</v>
       </c>
       <c r="B72" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7905,10 +7905,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483038</v>
+        <v>483387</v>
       </c>
       <c r="R72" t="n">
-        <v>6834461</v>
+        <v>6833994</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469333</v>
+        <v>121469128</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483059</v>
+        <v>483524</v>
       </c>
       <c r="R9" t="n">
-        <v>6833927</v>
+        <v>6834071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469145</v>
+        <v>121469333</v>
       </c>
       <c r="B10" t="n">
-        <v>78261</v>
+        <v>79234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483387</v>
+        <v>483059</v>
       </c>
       <c r="R10" t="n">
-        <v>6833994</v>
+        <v>6833927</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469126</v>
+        <v>121469114</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483476</v>
+        <v>483434</v>
       </c>
       <c r="R11" t="n">
-        <v>6834017</v>
+        <v>6833855</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469125</v>
+        <v>121469117</v>
       </c>
       <c r="B12" t="n">
         <v>78352</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483307</v>
+        <v>483119</v>
       </c>
       <c r="R12" t="n">
-        <v>6833983</v>
+        <v>6834405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469115</v>
+        <v>121469103</v>
       </c>
       <c r="B13" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483445</v>
+        <v>483145</v>
       </c>
       <c r="R13" t="n">
-        <v>6833857</v>
+        <v>6834394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469337</v>
+        <v>121469115</v>
       </c>
       <c r="B14" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483413</v>
+        <v>483445</v>
       </c>
       <c r="R14" t="n">
-        <v>6834033</v>
+        <v>6833857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469343</v>
+        <v>121469350</v>
       </c>
       <c r="B15" t="n">
         <v>79234</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483155</v>
+        <v>483033</v>
       </c>
       <c r="R15" t="n">
-        <v>6834382</v>
+        <v>6834458</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469119</v>
+        <v>121469144</v>
       </c>
       <c r="B16" t="n">
-        <v>78352</v>
+        <v>78261</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483265</v>
+        <v>483402</v>
       </c>
       <c r="R16" t="n">
-        <v>6834572</v>
+        <v>6834000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469345</v>
+        <v>121469100</v>
       </c>
       <c r="B17" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483210</v>
+        <v>483211</v>
       </c>
       <c r="R17" t="n">
-        <v>6834457</v>
+        <v>6834254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121465159</v>
+        <v>121469118</v>
       </c>
       <c r="B18" t="n">
         <v>78352</v>
@@ -2343,17 +2343,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483204</v>
+        <v>483210</v>
       </c>
       <c r="R18" t="n">
-        <v>6833925</v>
+        <v>6834456</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,19 +2380,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,12 +2397,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2521,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469335</v>
+        <v>121469344</v>
       </c>
       <c r="B20" t="n">
         <v>79234</v>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483483</v>
+        <v>483119</v>
       </c>
       <c r="R20" t="n">
-        <v>6833854</v>
+        <v>6834405</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469112</v>
+        <v>121469127</v>
       </c>
       <c r="B21" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483408</v>
+        <v>483514</v>
       </c>
       <c r="R21" t="n">
-        <v>6833852</v>
+        <v>6834064</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469140</v>
+        <v>121467080</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,37 +2731,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483106</v>
+        <v>483038</v>
       </c>
       <c r="R22" t="n">
-        <v>6834495</v>
+        <v>6834006</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2815,22 +2805,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469095</v>
+        <v>121469335</v>
       </c>
       <c r="B23" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482925</v>
+        <v>483483</v>
       </c>
       <c r="R23" t="n">
-        <v>6833909</v>
+        <v>6833854</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469099</v>
+        <v>121469348</v>
       </c>
       <c r="B24" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483482</v>
+        <v>483153</v>
       </c>
       <c r="R24" t="n">
-        <v>6833855</v>
+        <v>6834505</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469156</v>
+        <v>121469097</v>
       </c>
       <c r="B25" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482876</v>
+        <v>483408</v>
       </c>
       <c r="R25" t="n">
-        <v>6834258</v>
+        <v>6833852</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121465160</v>
+        <v>121469071</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3163,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483115</v>
+        <v>483265</v>
       </c>
       <c r="R26" t="n">
-        <v>6833942</v>
+        <v>6834571</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3206,19 +3196,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3233,19 +3213,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469344</v>
+        <v>121469343</v>
       </c>
       <c r="B27" t="n">
         <v>79234</v>
@@ -3285,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483119</v>
+        <v>483155</v>
       </c>
       <c r="R27" t="n">
-        <v>6834405</v>
+        <v>6834382</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469130</v>
+        <v>121469351</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483307</v>
+        <v>482864</v>
       </c>
       <c r="R28" t="n">
-        <v>6833983</v>
+        <v>6834255</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469127</v>
+        <v>121469339</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483514</v>
+        <v>483213</v>
       </c>
       <c r="R29" t="n">
-        <v>6834064</v>
+        <v>6834252</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469103</v>
+        <v>121469340</v>
       </c>
       <c r="B30" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483145</v>
+        <v>483211</v>
       </c>
       <c r="R30" t="n">
-        <v>6834394</v>
+        <v>6834254</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469124</v>
+        <v>121469142</v>
       </c>
       <c r="B31" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482865</v>
+        <v>483076</v>
       </c>
       <c r="R31" t="n">
-        <v>6834254</v>
+        <v>6834476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469157</v>
+        <v>121467007</v>
       </c>
       <c r="B32" t="n">
-        <v>78000</v>
+        <v>78353</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,13 +3775,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483143</v>
+        <v>483082</v>
       </c>
       <c r="R32" t="n">
-        <v>6833875</v>
+        <v>6834003</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3828,9 +3808,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3845,22 +3835,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469152</v>
+        <v>121465603</v>
       </c>
       <c r="B33" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,37 +3863,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483169</v>
+        <v>483561</v>
       </c>
       <c r="R33" t="n">
-        <v>6834491</v>
+        <v>6833992</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3930,9 +3920,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,22 +3947,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469114</v>
+        <v>121469098</v>
       </c>
       <c r="B34" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483434</v>
+        <v>483445</v>
       </c>
       <c r="R34" t="n">
-        <v>6833855</v>
+        <v>6833857</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469348</v>
+        <v>121469146</v>
       </c>
       <c r="B35" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483153</v>
+        <v>483260</v>
       </c>
       <c r="R35" t="n">
-        <v>6834505</v>
+        <v>6834060</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469101</v>
+        <v>121469136</v>
       </c>
       <c r="B36" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483168</v>
+        <v>483198</v>
       </c>
       <c r="R36" t="n">
-        <v>6834333</v>
+        <v>6834484</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469105</v>
+        <v>121469102</v>
       </c>
       <c r="B37" t="n">
         <v>78353</v>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483153</v>
+        <v>483161</v>
       </c>
       <c r="R37" t="n">
-        <v>6834504</v>
+        <v>6834377</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469144</v>
+        <v>121469155</v>
       </c>
       <c r="B38" t="n">
         <v>78261</v>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483402</v>
+        <v>482892</v>
       </c>
       <c r="R38" t="n">
-        <v>6834000</v>
+        <v>6834282</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121465604</v>
+        <v>121469147</v>
       </c>
       <c r="B39" t="n">
-        <v>78352</v>
+        <v>78261</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,37 +4485,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483179</v>
+        <v>483181</v>
       </c>
       <c r="R39" t="n">
-        <v>6833973</v>
+        <v>6834299</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4542,19 +4542,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4569,22 +4559,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469155</v>
+        <v>121465160</v>
       </c>
       <c r="B40" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,13 +4611,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>482892</v>
+        <v>483115</v>
       </c>
       <c r="R40" t="n">
-        <v>6834282</v>
+        <v>6833942</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4654,9 +4644,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4671,19 +4671,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469131</v>
+        <v>121469140</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483261</v>
+        <v>483106</v>
       </c>
       <c r="R41" t="n">
-        <v>6834030</v>
+        <v>6834495</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121467007</v>
+        <v>121469341</v>
       </c>
       <c r="B42" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,13 +4825,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483082</v>
+        <v>483181</v>
       </c>
       <c r="R42" t="n">
-        <v>6834003</v>
+        <v>6834299</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4858,19 +4858,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4885,19 +4875,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121465556</v>
+        <v>121466253</v>
       </c>
       <c r="B43" t="n">
         <v>78353</v>
@@ -4937,13 +4927,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483536</v>
+        <v>483464</v>
       </c>
       <c r="R43" t="n">
-        <v>6833990</v>
+        <v>6833910</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4999,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469097</v>
+        <v>121469158</v>
       </c>
       <c r="B44" t="n">
-        <v>78353</v>
+        <v>78000</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483408</v>
+        <v>482967</v>
       </c>
       <c r="R44" t="n">
-        <v>6833852</v>
+        <v>6834339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469117</v>
+        <v>121469336</v>
       </c>
       <c r="B45" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,21 +5107,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483119</v>
+        <v>483492</v>
       </c>
       <c r="R45" t="n">
-        <v>6834405</v>
+        <v>6834084</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,10 +5295,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469133</v>
+        <v>121469125</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5311,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483241</v>
+        <v>483307</v>
       </c>
       <c r="R47" t="n">
-        <v>6834112</v>
+        <v>6833983</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5407,10 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469150</v>
+        <v>121469119</v>
       </c>
       <c r="B48" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,21 +5413,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5447,10 +5437,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483294</v>
+        <v>483265</v>
       </c>
       <c r="R48" t="n">
-        <v>6834475</v>
+        <v>6834572</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469154</v>
+        <v>121469137</v>
       </c>
       <c r="B49" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,21 +5515,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483081</v>
+        <v>483198</v>
       </c>
       <c r="R49" t="n">
-        <v>6834496</v>
+        <v>6834476</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469349</v>
+        <v>121469132</v>
       </c>
       <c r="B50" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5627,21 +5617,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5651,10 +5641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483065</v>
+        <v>483255</v>
       </c>
       <c r="R50" t="n">
-        <v>6834469</v>
+        <v>6834077</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469118</v>
+        <v>121469104</v>
       </c>
       <c r="B51" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5729,21 +5719,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5753,10 +5743,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483210</v>
+        <v>483265</v>
       </c>
       <c r="R51" t="n">
-        <v>6834456</v>
+        <v>6834572</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5815,10 +5805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469148</v>
+        <v>121469096</v>
       </c>
       <c r="B52" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5831,21 +5821,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5855,10 +5845,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483160</v>
+        <v>483058</v>
       </c>
       <c r="R52" t="n">
-        <v>6834438</v>
+        <v>6833926</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5917,7 +5907,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469143</v>
+        <v>121465615</v>
       </c>
       <c r="B53" t="n">
         <v>78616</v>
@@ -5953,14 +5943,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483038</v>
+        <v>483179</v>
       </c>
       <c r="R53" t="n">
-        <v>6834461</v>
+        <v>6833973</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5990,9 +5980,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6007,22 +6007,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469070</v>
+        <v>121469139</v>
       </c>
       <c r="B54" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6035,21 +6035,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483031</v>
+        <v>483149</v>
       </c>
       <c r="R54" t="n">
-        <v>6834425</v>
+        <v>6834501</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6121,10 +6121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469135</v>
+        <v>121469345</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6137,21 +6137,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483205</v>
+        <v>483210</v>
       </c>
       <c r="R55" t="n">
-        <v>6834490</v>
+        <v>6834457</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469104</v>
+        <v>121469334</v>
       </c>
       <c r="B56" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6239,21 +6239,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483265</v>
+        <v>483084</v>
       </c>
       <c r="R56" t="n">
-        <v>6834572</v>
+        <v>6833901</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121466253</v>
+        <v>121467022</v>
       </c>
       <c r="B57" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,37 +6341,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483464</v>
+        <v>483082</v>
       </c>
       <c r="R57" t="n">
-        <v>6833910</v>
+        <v>6834003</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6398,9 +6398,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6415,19 +6425,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121465246</v>
+        <v>121469116</v>
       </c>
       <c r="B58" t="n">
         <v>78352</v>
@@ -6463,17 +6473,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483187</v>
+        <v>483484</v>
       </c>
       <c r="R58" t="n">
-        <v>6833888</v>
+        <v>6833901</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6500,19 +6510,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6527,22 +6527,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469347</v>
+        <v>121469105</v>
       </c>
       <c r="B59" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483261</v>
+        <v>483153</v>
       </c>
       <c r="R59" t="n">
-        <v>6834535</v>
+        <v>6834504</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469122</v>
+        <v>121469110</v>
       </c>
       <c r="B60" t="n">
         <v>78352</v>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>482967</v>
+        <v>483144</v>
       </c>
       <c r="R60" t="n">
-        <v>6834340</v>
+        <v>6833875</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469096</v>
+        <v>121465604</v>
       </c>
       <c r="B61" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,37 +6759,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483058</v>
+        <v>483179</v>
       </c>
       <c r="R61" t="n">
-        <v>6833926</v>
+        <v>6833973</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6816,9 +6816,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,22 +6843,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469128</v>
+        <v>121469112</v>
       </c>
       <c r="B62" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6861,21 +6871,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6885,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483524</v>
+        <v>483408</v>
       </c>
       <c r="R62" t="n">
-        <v>6834071</v>
+        <v>6833852</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469142</v>
+        <v>121465202</v>
       </c>
       <c r="B63" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6963,37 +6973,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483076</v>
+        <v>483084</v>
       </c>
       <c r="R63" t="n">
-        <v>6834476</v>
+        <v>6833930</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7020,9 +7030,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7037,22 +7057,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469342</v>
+        <v>121469149</v>
       </c>
       <c r="B64" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7065,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7089,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483160</v>
+        <v>483268</v>
       </c>
       <c r="R64" t="n">
-        <v>6834377</v>
+        <v>6834459</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7151,7 +7171,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469110</v>
+        <v>121469108</v>
       </c>
       <c r="B65" t="n">
         <v>78352</v>
@@ -7191,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483144</v>
+        <v>482925</v>
       </c>
       <c r="R65" t="n">
-        <v>6833875</v>
+        <v>6833910</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7253,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469069</v>
+        <v>121469157</v>
       </c>
       <c r="B66" t="n">
-        <v>79205</v>
+        <v>78000</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7269,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7293,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483031</v>
+        <v>483143</v>
       </c>
       <c r="R66" t="n">
-        <v>6834458</v>
+        <v>6833875</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7355,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469158</v>
+        <v>121469145</v>
       </c>
       <c r="B67" t="n">
-        <v>78000</v>
+        <v>78261</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7395,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>482967</v>
+        <v>483387</v>
       </c>
       <c r="R67" t="n">
-        <v>6834339</v>
+        <v>6833994</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7457,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469106</v>
+        <v>121469143</v>
       </c>
       <c r="B68" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7473,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7497,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>482967</v>
+        <v>483038</v>
       </c>
       <c r="R68" t="n">
-        <v>6834340</v>
+        <v>6834461</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7559,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469098</v>
+        <v>121469337</v>
       </c>
       <c r="B69" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7575,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7599,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483445</v>
+        <v>483413</v>
       </c>
       <c r="R69" t="n">
-        <v>6833857</v>
+        <v>6834033</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7661,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469341</v>
+        <v>121469130</v>
       </c>
       <c r="B70" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7677,21 +7697,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7701,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483181</v>
+        <v>483307</v>
       </c>
       <c r="R70" t="n">
-        <v>6834299</v>
+        <v>6833983</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469334</v>
+        <v>121469124</v>
       </c>
       <c r="B71" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7779,21 +7799,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7803,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483084</v>
+        <v>482865</v>
       </c>
       <c r="R71" t="n">
-        <v>6833901</v>
+        <v>6834254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7865,10 +7885,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121465603</v>
+        <v>121469338</v>
       </c>
       <c r="B72" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7881,37 +7901,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483561</v>
+        <v>483246</v>
       </c>
       <c r="R72" t="n">
-        <v>6833992</v>
+        <v>6834122</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7938,19 +7958,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7965,22 +7975,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469338</v>
+        <v>121469150</v>
       </c>
       <c r="B73" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7993,21 +8003,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8017,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483246</v>
+        <v>483294</v>
       </c>
       <c r="R73" t="n">
-        <v>6834122</v>
+        <v>6834475</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8079,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469340</v>
+        <v>121469152</v>
       </c>
       <c r="B74" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8095,21 +8105,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8119,10 +8129,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483211</v>
+        <v>483169</v>
       </c>
       <c r="R74" t="n">
-        <v>6834254</v>
+        <v>6834491</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,10 +8191,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469137</v>
+        <v>121469101</v>
       </c>
       <c r="B75" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8197,21 +8207,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8221,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483198</v>
+        <v>483168</v>
       </c>
       <c r="R75" t="n">
-        <v>6834476</v>
+        <v>6834333</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8283,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469136</v>
+        <v>121469107</v>
       </c>
       <c r="B76" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8299,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8323,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483198</v>
+        <v>482865</v>
       </c>
       <c r="R76" t="n">
-        <v>6834484</v>
+        <v>6834255</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8385,10 +8395,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469351</v>
+        <v>121465159</v>
       </c>
       <c r="B77" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8401,37 +8411,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>482864</v>
+        <v>483204</v>
       </c>
       <c r="R77" t="n">
-        <v>6834255</v>
+        <v>6833925</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8458,9 +8468,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8475,22 +8495,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469339</v>
+        <v>121469095</v>
       </c>
       <c r="B78" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8503,21 +8523,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8527,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483213</v>
+        <v>482925</v>
       </c>
       <c r="R78" t="n">
-        <v>6834252</v>
+        <v>6833909</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8589,10 +8609,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469350</v>
+        <v>121469126</v>
       </c>
       <c r="B79" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8605,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8629,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483033</v>
+        <v>483476</v>
       </c>
       <c r="R79" t="n">
-        <v>6834458</v>
+        <v>6834017</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8691,10 +8711,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469139</v>
+        <v>121469347</v>
       </c>
       <c r="B80" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8707,21 +8727,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8731,10 +8751,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483149</v>
+        <v>483261</v>
       </c>
       <c r="R80" t="n">
-        <v>6834501</v>
+        <v>6834535</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8793,10 +8813,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469100</v>
+        <v>121469133</v>
       </c>
       <c r="B81" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8809,21 +8829,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8833,10 +8853,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483211</v>
+        <v>483241</v>
       </c>
       <c r="R81" t="n">
-        <v>6834254</v>
+        <v>6834112</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8895,10 +8915,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121465189</v>
+        <v>121469131</v>
       </c>
       <c r="B82" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8911,37 +8931,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483204</v>
+        <v>483261</v>
       </c>
       <c r="R82" t="n">
-        <v>6833925</v>
+        <v>6834030</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8968,19 +8988,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8995,22 +9005,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469336</v>
+        <v>121465246</v>
       </c>
       <c r="B83" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9023,37 +9033,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483492</v>
+        <v>483187</v>
       </c>
       <c r="R83" t="n">
-        <v>6834084</v>
+        <v>6833888</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9080,9 +9090,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9097,22 +9117,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121467022</v>
+        <v>121469342</v>
       </c>
       <c r="B84" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,21 +9145,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9149,13 +9169,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483082</v>
+        <v>483160</v>
       </c>
       <c r="R84" t="n">
-        <v>6834003</v>
+        <v>6834377</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9182,19 +9202,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9209,22 +9219,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121465202</v>
+        <v>121469099</v>
       </c>
       <c r="B85" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9237,37 +9247,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483084</v>
+        <v>483482</v>
       </c>
       <c r="R85" t="n">
-        <v>6833930</v>
+        <v>6833855</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9294,19 +9304,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9321,22 +9321,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469132</v>
+        <v>121469148</v>
       </c>
       <c r="B86" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9349,21 +9349,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483255</v>
+        <v>483160</v>
       </c>
       <c r="R86" t="n">
-        <v>6834077</v>
+        <v>6834438</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9435,7 +9435,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469147</v>
+        <v>121469156</v>
       </c>
       <c r="B87" t="n">
         <v>78261</v>
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483181</v>
+        <v>482876</v>
       </c>
       <c r="R87" t="n">
-        <v>6834299</v>
+        <v>6834258</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9639,7 +9639,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469108</v>
+        <v>121469122</v>
       </c>
       <c r="B89" t="n">
         <v>78352</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>482925</v>
+        <v>482967</v>
       </c>
       <c r="R89" t="n">
-        <v>6833910</v>
+        <v>6834340</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469116</v>
+        <v>121469070</v>
       </c>
       <c r="B90" t="n">
-        <v>78352</v>
+        <v>79205</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9757,21 +9757,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483484</v>
+        <v>483031</v>
       </c>
       <c r="R90" t="n">
-        <v>6833901</v>
+        <v>6834425</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121469071</v>
+        <v>121465189</v>
       </c>
       <c r="B91" t="n">
-        <v>57510</v>
+        <v>78353</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9859,37 +9859,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483265</v>
+        <v>483204</v>
       </c>
       <c r="R91" t="n">
-        <v>6834571</v>
+        <v>6833925</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9916,9 +9916,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9933,22 +9943,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121469107</v>
+        <v>121469069</v>
       </c>
       <c r="B92" t="n">
-        <v>78353</v>
+        <v>79205</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9961,21 +9971,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9985,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>482865</v>
+        <v>483031</v>
       </c>
       <c r="R92" t="n">
-        <v>6834255</v>
+        <v>6834458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,7 +10057,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121469149</v>
+        <v>121469154</v>
       </c>
       <c r="B93" t="n">
         <v>78261</v>
@@ -10087,10 +10097,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483268</v>
+        <v>483081</v>
       </c>
       <c r="R93" t="n">
-        <v>6834459</v>
+        <v>6834496</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10149,10 +10159,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121469146</v>
+        <v>121469135</v>
       </c>
       <c r="B94" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,21 +10175,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10189,10 +10199,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483260</v>
+        <v>483205</v>
       </c>
       <c r="R94" t="n">
-        <v>6834060</v>
+        <v>6834490</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10251,10 +10261,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121467080</v>
+        <v>121469349</v>
       </c>
       <c r="B95" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10267,37 +10277,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483038</v>
+        <v>483065</v>
       </c>
       <c r="R95" t="n">
-        <v>6834006</v>
+        <v>6834469</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10341,19 +10351,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121469102</v>
+        <v>121469106</v>
       </c>
       <c r="B96" t="n">
         <v>78353</v>
@@ -10393,10 +10403,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483161</v>
+        <v>482967</v>
       </c>
       <c r="R96" t="n">
-        <v>6834377</v>
+        <v>6834340</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10455,10 +10465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121465615</v>
+        <v>121465556</v>
       </c>
       <c r="B97" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10471,21 +10481,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10495,13 +10505,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483179</v>
+        <v>483536</v>
       </c>
       <c r="R97" t="n">
-        <v>6833973</v>
+        <v>6833990</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10528,19 +10538,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,22 +10555,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121465266</v>
+        <v>121466059</v>
       </c>
       <c r="B98" t="n">
-        <v>79205</v>
+        <v>79234</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483204</v>
+        <v>483350</v>
       </c>
       <c r="R98" t="n">
-        <v>6833967</v>
+        <v>6834071</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121465024</v>
+        <v>121465234</v>
       </c>
       <c r="B99" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>482987</v>
+        <v>483201</v>
       </c>
       <c r="R99" t="n">
-        <v>6833950</v>
+        <v>6833961</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10791,10 +10791,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121465426</v>
+        <v>121465266</v>
       </c>
       <c r="B100" t="n">
-        <v>78353</v>
+        <v>79205</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483209</v>
+        <v>483204</v>
       </c>
       <c r="R100" t="n">
-        <v>6833990</v>
+        <v>6833967</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121465052</v>
+        <v>121465426</v>
       </c>
       <c r="B101" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10919,21 +10919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>482987</v>
+        <v>483209</v>
       </c>
       <c r="R101" t="n">
-        <v>6833950</v>
+        <v>6833990</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11015,7 +11015,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121466096</v>
+        <v>121465412</v>
       </c>
       <c r="B102" t="n">
         <v>78352</v>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483350</v>
+        <v>483177</v>
       </c>
       <c r="R102" t="n">
-        <v>6834071</v>
+        <v>6833971</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121464931</v>
+        <v>121465017</v>
       </c>
       <c r="B103" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11143,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>482985</v>
+        <v>482987</v>
       </c>
       <c r="R103" t="n">
-        <v>6833943</v>
+        <v>6833950</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121465412</v>
+        <v>121464931</v>
       </c>
       <c r="B105" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483177</v>
+        <v>482985</v>
       </c>
       <c r="R105" t="n">
-        <v>6833971</v>
+        <v>6833943</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11463,7 +11463,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121465017</v>
+        <v>121466096</v>
       </c>
       <c r="B106" t="n">
         <v>78352</v>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>482987</v>
+        <v>483350</v>
       </c>
       <c r="R106" t="n">
-        <v>6833950</v>
+        <v>6834071</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121465234</v>
+        <v>121465024</v>
       </c>
       <c r="B107" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11591,21 +11591,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483201</v>
+        <v>482987</v>
       </c>
       <c r="R107" t="n">
-        <v>6833961</v>
+        <v>6833950</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121466059</v>
+        <v>121465052</v>
       </c>
       <c r="B108" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11703,21 +11703,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483350</v>
+        <v>482987</v>
       </c>
       <c r="R108" t="n">
-        <v>6834071</v>
+        <v>6833950</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469343</v>
+        <v>121469142</v>
       </c>
       <c r="B27" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483155</v>
+        <v>483076</v>
       </c>
       <c r="R27" t="n">
-        <v>6834382</v>
+        <v>6834476</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469351</v>
+        <v>121469343</v>
       </c>
       <c r="B28" t="n">
         <v>79234</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482864</v>
+        <v>483155</v>
       </c>
       <c r="R28" t="n">
-        <v>6834255</v>
+        <v>6834382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469339</v>
+        <v>121469351</v>
       </c>
       <c r="B29" t="n">
         <v>79234</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483213</v>
+        <v>482864</v>
       </c>
       <c r="R29" t="n">
-        <v>6834252</v>
+        <v>6834255</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469340</v>
+        <v>121469339</v>
       </c>
       <c r="B30" t="n">
         <v>79234</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483211</v>
+        <v>483213</v>
       </c>
       <c r="R30" t="n">
-        <v>6834254</v>
+        <v>6834252</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469142</v>
+        <v>121469340</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483076</v>
+        <v>483211</v>
       </c>
       <c r="R31" t="n">
-        <v>6834476</v>
+        <v>6834254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469136</v>
+        <v>121469102</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483198</v>
+        <v>483161</v>
       </c>
       <c r="R36" t="n">
-        <v>6834484</v>
+        <v>6834377</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469102</v>
+        <v>121469136</v>
       </c>
       <c r="B37" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483161</v>
+        <v>483198</v>
       </c>
       <c r="R37" t="n">
-        <v>6834377</v>
+        <v>6834484</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469110</v>
+        <v>121465604</v>
       </c>
       <c r="B60" t="n">
         <v>78352</v>
@@ -6677,17 +6677,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483144</v>
+        <v>483179</v>
       </c>
       <c r="R60" t="n">
-        <v>6833875</v>
+        <v>6833973</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6714,9 +6714,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6731,22 +6741,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121465604</v>
+        <v>121465202</v>
       </c>
       <c r="B61" t="n">
-        <v>78352</v>
+        <v>78261</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,21 +6769,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6783,13 +6793,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483179</v>
+        <v>483084</v>
       </c>
       <c r="R61" t="n">
-        <v>6833973</v>
+        <v>6833930</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6818,7 +6828,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6828,7 +6838,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6855,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469112</v>
+        <v>121469149</v>
       </c>
       <c r="B62" t="n">
-        <v>78352</v>
+        <v>78261</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6871,21 +6881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6895,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483408</v>
+        <v>483268</v>
       </c>
       <c r="R62" t="n">
-        <v>6833852</v>
+        <v>6834459</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121465202</v>
+        <v>121469110</v>
       </c>
       <c r="B63" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6973,37 +6983,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483084</v>
+        <v>483144</v>
       </c>
       <c r="R63" t="n">
-        <v>6833930</v>
+        <v>6833875</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7030,19 +7040,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7057,22 +7057,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469149</v>
+        <v>121469112</v>
       </c>
       <c r="B64" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483268</v>
+        <v>483408</v>
       </c>
       <c r="R64" t="n">
-        <v>6834459</v>
+        <v>6833852</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469108</v>
+        <v>121469145</v>
       </c>
       <c r="B65" t="n">
-        <v>78352</v>
+        <v>78261</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7187,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>482925</v>
+        <v>483387</v>
       </c>
       <c r="R65" t="n">
-        <v>6833910</v>
+        <v>6833994</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469157</v>
+        <v>121469108</v>
       </c>
       <c r="B66" t="n">
-        <v>78000</v>
+        <v>78352</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483143</v>
+        <v>482925</v>
       </c>
       <c r="R66" t="n">
-        <v>6833875</v>
+        <v>6833910</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469145</v>
+        <v>121469157</v>
       </c>
       <c r="B67" t="n">
-        <v>78261</v>
+        <v>78000</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483387</v>
+        <v>483143</v>
       </c>
       <c r="R67" t="n">
-        <v>6833994</v>
+        <v>6833875</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469150</v>
+        <v>121469101</v>
       </c>
       <c r="B73" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483294</v>
+        <v>483168</v>
       </c>
       <c r="R73" t="n">
-        <v>6834475</v>
+        <v>6834333</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469152</v>
+        <v>121469107</v>
       </c>
       <c r="B74" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8105,21 +8105,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483169</v>
+        <v>482865</v>
       </c>
       <c r="R74" t="n">
-        <v>6834491</v>
+        <v>6834255</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,10 +8191,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469101</v>
+        <v>121469150</v>
       </c>
       <c r="B75" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8207,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483168</v>
+        <v>483294</v>
       </c>
       <c r="R75" t="n">
-        <v>6834333</v>
+        <v>6834475</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469107</v>
+        <v>121469152</v>
       </c>
       <c r="B76" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482865</v>
+        <v>483169</v>
       </c>
       <c r="R76" t="n">
-        <v>6834255</v>
+        <v>6834491</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469095</v>
+        <v>121469126</v>
       </c>
       <c r="B78" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8523,21 +8523,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>482925</v>
+        <v>483476</v>
       </c>
       <c r="R78" t="n">
-        <v>6833909</v>
+        <v>6834017</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8609,10 +8609,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469126</v>
+        <v>121469347</v>
       </c>
       <c r="B79" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483476</v>
+        <v>483261</v>
       </c>
       <c r="R79" t="n">
-        <v>6834017</v>
+        <v>6834535</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8711,10 +8711,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469347</v>
+        <v>121469095</v>
       </c>
       <c r="B80" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8727,21 +8727,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483261</v>
+        <v>482925</v>
       </c>
       <c r="R80" t="n">
-        <v>6834535</v>
+        <v>6833909</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469133</v>
+        <v>121469099</v>
       </c>
       <c r="B81" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8829,21 +8829,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483241</v>
+        <v>483482</v>
       </c>
       <c r="R81" t="n">
-        <v>6834112</v>
+        <v>6833855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8915,10 +8915,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469131</v>
+        <v>121465246</v>
       </c>
       <c r="B82" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8931,37 +8931,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483261</v>
+        <v>483187</v>
       </c>
       <c r="R82" t="n">
-        <v>6834030</v>
+        <v>6833888</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8988,9 +8988,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9005,22 +9015,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121465246</v>
+        <v>121469342</v>
       </c>
       <c r="B83" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9033,37 +9043,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483187</v>
+        <v>483160</v>
       </c>
       <c r="R83" t="n">
-        <v>6833888</v>
+        <v>6834377</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9090,19 +9100,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9117,22 +9117,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469342</v>
+        <v>121469133</v>
       </c>
       <c r="B84" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9145,21 +9145,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9169,10 +9169,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483160</v>
+        <v>483241</v>
       </c>
       <c r="R84" t="n">
-        <v>6834377</v>
+        <v>6834112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9231,10 +9231,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469099</v>
+        <v>121469131</v>
       </c>
       <c r="B85" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9247,21 +9247,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483482</v>
+        <v>483261</v>
       </c>
       <c r="R85" t="n">
-        <v>6833855</v>
+        <v>6834030</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 40225-2023 artfynd.xlsx
+++ b/artfynd/A 40225-2023 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469128</v>
+        <v>121469342</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483524</v>
+        <v>483160</v>
       </c>
       <c r="R9" t="n">
-        <v>6834071</v>
+        <v>6834377</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469333</v>
+        <v>121469127</v>
       </c>
       <c r="B10" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483059</v>
+        <v>483514</v>
       </c>
       <c r="R10" t="n">
-        <v>6833927</v>
+        <v>6834064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469114</v>
+        <v>121469117</v>
       </c>
       <c r="B11" t="n">
         <v>78352</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483434</v>
+        <v>483119</v>
       </c>
       <c r="R11" t="n">
-        <v>6833855</v>
+        <v>6834405</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469117</v>
+        <v>121469112</v>
       </c>
       <c r="B12" t="n">
         <v>78352</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483119</v>
+        <v>483408</v>
       </c>
       <c r="R12" t="n">
-        <v>6834405</v>
+        <v>6833852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469103</v>
+        <v>121465202</v>
       </c>
       <c r="B13" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,37 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483145</v>
+        <v>483084</v>
       </c>
       <c r="R13" t="n">
-        <v>6834394</v>
+        <v>6833930</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1870,9 +1870,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,22 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469115</v>
+        <v>121469152</v>
       </c>
       <c r="B14" t="n">
-        <v>78352</v>
+        <v>78261</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483445</v>
+        <v>483169</v>
       </c>
       <c r="R14" t="n">
-        <v>6833857</v>
+        <v>6834491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469350</v>
+        <v>121469343</v>
       </c>
       <c r="B15" t="n">
         <v>79234</v>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483033</v>
+        <v>483155</v>
       </c>
       <c r="R15" t="n">
-        <v>6834458</v>
+        <v>6834382</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469144</v>
+        <v>121469140</v>
       </c>
       <c r="B16" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483402</v>
+        <v>483106</v>
       </c>
       <c r="R16" t="n">
-        <v>6834000</v>
+        <v>6834495</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469100</v>
+        <v>121469124</v>
       </c>
       <c r="B17" t="n">
-        <v>78353</v>
+        <v>78352</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,7 +2255,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483211</v>
+        <v>482865</v>
       </c>
       <c r="R17" t="n">
         <v>6834254</v>
@@ -2307,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469118</v>
+        <v>121469128</v>
       </c>
       <c r="B18" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483210</v>
+        <v>483524</v>
       </c>
       <c r="R18" t="n">
-        <v>6834456</v>
+        <v>6834071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121465664</v>
+        <v>121469336</v>
       </c>
       <c r="B19" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,37 +2435,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483498</v>
+        <v>483492</v>
       </c>
       <c r="R19" t="n">
-        <v>6834031</v>
+        <v>6834084</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469344</v>
+        <v>121469118</v>
       </c>
       <c r="B20" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483119</v>
+        <v>483210</v>
       </c>
       <c r="R20" t="n">
-        <v>6834405</v>
+        <v>6834456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469127</v>
+        <v>121469132</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483514</v>
+        <v>483255</v>
       </c>
       <c r="R21" t="n">
-        <v>6834064</v>
+        <v>6834077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467080</v>
+        <v>121469146</v>
       </c>
       <c r="B22" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,37 +2741,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483038</v>
+        <v>483260</v>
       </c>
       <c r="R22" t="n">
-        <v>6834006</v>
+        <v>6834060</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,22 +2815,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469335</v>
+        <v>121469103</v>
       </c>
       <c r="B23" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483483</v>
+        <v>483145</v>
       </c>
       <c r="R23" t="n">
-        <v>6833854</v>
+        <v>6834394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469348</v>
+        <v>121469347</v>
       </c>
       <c r="B24" t="n">
         <v>79234</v>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483153</v>
+        <v>483261</v>
       </c>
       <c r="R24" t="n">
-        <v>6834505</v>
+        <v>6834535</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469097</v>
+        <v>121469126</v>
       </c>
       <c r="B25" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483408</v>
+        <v>483476</v>
       </c>
       <c r="R25" t="n">
-        <v>6833852</v>
+        <v>6834017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469071</v>
+        <v>121469102</v>
       </c>
       <c r="B26" t="n">
-        <v>57510</v>
+        <v>78353</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483265</v>
+        <v>483161</v>
       </c>
       <c r="R26" t="n">
-        <v>6834571</v>
+        <v>6834377</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469142</v>
+        <v>121469099</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483076</v>
+        <v>483482</v>
       </c>
       <c r="R27" t="n">
-        <v>6834476</v>
+        <v>6833855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469343</v>
+        <v>121469349</v>
       </c>
       <c r="B28" t="n">
         <v>79234</v>
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483155</v>
+        <v>483065</v>
       </c>
       <c r="R28" t="n">
-        <v>6834382</v>
+        <v>6834469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469351</v>
+        <v>121469339</v>
       </c>
       <c r="B29" t="n">
         <v>79234</v>
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482864</v>
+        <v>483213</v>
       </c>
       <c r="R29" t="n">
-        <v>6834255</v>
+        <v>6834252</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469339</v>
+        <v>121469345</v>
       </c>
       <c r="B30" t="n">
         <v>79234</v>
@@ -3571,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483213</v>
+        <v>483210</v>
       </c>
       <c r="R30" t="n">
-        <v>6834252</v>
+        <v>6834457</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469340</v>
+        <v>121469155</v>
       </c>
       <c r="B31" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483211</v>
+        <v>482892</v>
       </c>
       <c r="R31" t="n">
-        <v>6834254</v>
+        <v>6834282</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121467007</v>
+        <v>121469156</v>
       </c>
       <c r="B32" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,13 +3785,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483082</v>
+        <v>482876</v>
       </c>
       <c r="R32" t="n">
-        <v>6834003</v>
+        <v>6834258</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3808,19 +3818,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3835,19 +3835,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121465603</v>
+        <v>121469098</v>
       </c>
       <c r="B33" t="n">
         <v>78353</v>
@@ -3883,17 +3883,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483561</v>
+        <v>483445</v>
       </c>
       <c r="R33" t="n">
-        <v>6833992</v>
+        <v>6833857</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3920,19 +3920,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,22 +3937,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469098</v>
+        <v>121469351</v>
       </c>
       <c r="B34" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483445</v>
+        <v>482864</v>
       </c>
       <c r="R34" t="n">
-        <v>6833857</v>
+        <v>6834255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469146</v>
+        <v>121465615</v>
       </c>
       <c r="B35" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,34 +4067,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483260</v>
+        <v>483179</v>
       </c>
       <c r="R35" t="n">
-        <v>6834060</v>
+        <v>6833973</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4134,9 +4124,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4151,22 +4151,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469102</v>
+        <v>121469149</v>
       </c>
       <c r="B36" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483161</v>
+        <v>483268</v>
       </c>
       <c r="R36" t="n">
-        <v>6834377</v>
+        <v>6834459</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469136</v>
+        <v>121469106</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483198</v>
+        <v>482967</v>
       </c>
       <c r="R37" t="n">
-        <v>6834484</v>
+        <v>6834340</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469155</v>
+        <v>121467022</v>
       </c>
       <c r="B38" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,13 +4407,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>482892</v>
+        <v>483082</v>
       </c>
       <c r="R38" t="n">
-        <v>6834282</v>
+        <v>6834003</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4440,9 +4440,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4457,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469147</v>
+        <v>121469122</v>
       </c>
       <c r="B39" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4495,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483181</v>
+        <v>482967</v>
       </c>
       <c r="R39" t="n">
-        <v>6834299</v>
+        <v>6834340</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121465160</v>
+        <v>121469145</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,13 +4621,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483115</v>
+        <v>483387</v>
       </c>
       <c r="R40" t="n">
-        <v>6833942</v>
+        <v>6833994</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4644,19 +4654,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4671,22 +4671,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469140</v>
+        <v>121469070</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483106</v>
+        <v>483031</v>
       </c>
       <c r="R41" t="n">
-        <v>6834495</v>
+        <v>6834425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469341</v>
+        <v>121469154</v>
       </c>
       <c r="B42" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483181</v>
+        <v>483081</v>
       </c>
       <c r="R42" t="n">
-        <v>6834299</v>
+        <v>6834496</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121466253</v>
+        <v>121469147</v>
       </c>
       <c r="B43" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4903,37 +4903,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483464</v>
+        <v>483181</v>
       </c>
       <c r="R43" t="n">
-        <v>6833910</v>
+        <v>6834299</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4977,22 +4977,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469158</v>
+        <v>121467080</v>
       </c>
       <c r="B44" t="n">
-        <v>78000</v>
+        <v>78353</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5005,37 +5005,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>482967</v>
+        <v>483038</v>
       </c>
       <c r="R44" t="n">
-        <v>6834339</v>
+        <v>6834006</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5079,22 +5079,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469336</v>
+        <v>121469108</v>
       </c>
       <c r="B45" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483492</v>
+        <v>482925</v>
       </c>
       <c r="R45" t="n">
-        <v>6834084</v>
+        <v>6833910</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,10 +5193,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469134</v>
+        <v>121469344</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5209,21 +5209,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483277</v>
+        <v>483119</v>
       </c>
       <c r="R46" t="n">
-        <v>6834451</v>
+        <v>6834405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469125</v>
+        <v>121465246</v>
       </c>
       <c r="B47" t="n">
         <v>78352</v>
@@ -5331,17 +5331,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483307</v>
+        <v>483187</v>
       </c>
       <c r="R47" t="n">
-        <v>6833983</v>
+        <v>6833888</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5368,9 +5368,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,22 +5395,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469119</v>
+        <v>121469334</v>
       </c>
       <c r="B48" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5413,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5437,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483265</v>
+        <v>483084</v>
       </c>
       <c r="R48" t="n">
-        <v>6834572</v>
+        <v>6833901</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5499,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469137</v>
+        <v>121469144</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,21 +5525,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5539,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483198</v>
+        <v>483402</v>
       </c>
       <c r="R49" t="n">
-        <v>6834476</v>
+        <v>6834000</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469132</v>
+        <v>121469333</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5617,21 +5627,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5641,10 +5651,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483255</v>
+        <v>483059</v>
       </c>
       <c r="R50" t="n">
-        <v>6834077</v>
+        <v>6833927</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5703,10 +5713,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469104</v>
+        <v>121469348</v>
       </c>
       <c r="B51" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5719,21 +5729,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5743,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483265</v>
+        <v>483153</v>
       </c>
       <c r="R51" t="n">
-        <v>6834572</v>
+        <v>6834505</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5805,10 +5815,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469096</v>
+        <v>121469137</v>
       </c>
       <c r="B52" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,21 +5831,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5845,10 +5855,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483058</v>
+        <v>483198</v>
       </c>
       <c r="R52" t="n">
-        <v>6833926</v>
+        <v>6834476</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,10 +5917,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121465615</v>
+        <v>121469125</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5923,34 +5933,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483179</v>
+        <v>483307</v>
       </c>
       <c r="R53" t="n">
-        <v>6833973</v>
+        <v>6833983</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5980,19 +5990,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6007,19 +6007,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469139</v>
+        <v>121465160</v>
       </c>
       <c r="B54" t="n">
         <v>78616</v>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483149</v>
+        <v>483115</v>
       </c>
       <c r="R54" t="n">
-        <v>6834501</v>
+        <v>6833942</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6092,9 +6092,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6109,22 +6119,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469345</v>
+        <v>121469150</v>
       </c>
       <c r="B55" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6137,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6161,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483210</v>
+        <v>483294</v>
       </c>
       <c r="R55" t="n">
-        <v>6834457</v>
+        <v>6834475</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469334</v>
+        <v>121469104</v>
       </c>
       <c r="B56" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6239,21 +6249,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6263,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483084</v>
+        <v>483265</v>
       </c>
       <c r="R56" t="n">
-        <v>6833901</v>
+        <v>6834572</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121467022</v>
+        <v>121469069</v>
       </c>
       <c r="B57" t="n">
-        <v>78352</v>
+        <v>79205</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,13 +6375,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483082</v>
+        <v>483031</v>
       </c>
       <c r="R57" t="n">
-        <v>6834003</v>
+        <v>6834458</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6398,19 +6408,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,19 +6425,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469116</v>
+        <v>121465159</v>
       </c>
       <c r="B58" t="n">
         <v>78352</v>
@@ -6473,17 +6473,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483484</v>
+        <v>483204</v>
       </c>
       <c r="R58" t="n">
-        <v>6833901</v>
+        <v>6833925</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6510,9 +6510,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6527,22 +6537,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469105</v>
+        <v>121469142</v>
       </c>
       <c r="B59" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6579,10 +6589,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483153</v>
+        <v>483076</v>
       </c>
       <c r="R59" t="n">
-        <v>6834504</v>
+        <v>6834476</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6641,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121465604</v>
+        <v>121469071</v>
       </c>
       <c r="B60" t="n">
-        <v>78352</v>
+        <v>57510</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6657,37 +6667,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483179</v>
+        <v>483265</v>
       </c>
       <c r="R60" t="n">
-        <v>6833973</v>
+        <v>6834571</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6714,19 +6724,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6741,22 +6741,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121465202</v>
+        <v>121469097</v>
       </c>
       <c r="B61" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6769,37 +6769,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483084</v>
+        <v>483408</v>
       </c>
       <c r="R61" t="n">
-        <v>6833930</v>
+        <v>6833852</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6826,19 +6826,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6853,22 +6843,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469149</v>
+        <v>121465556</v>
       </c>
       <c r="B62" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,37 +6871,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483268</v>
+        <v>483536</v>
       </c>
       <c r="R62" t="n">
-        <v>6834459</v>
+        <v>6833990</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6955,19 +6945,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469110</v>
+        <v>121469115</v>
       </c>
       <c r="B63" t="n">
         <v>78352</v>
@@ -7007,10 +6997,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483144</v>
+        <v>483445</v>
       </c>
       <c r="R63" t="n">
-        <v>6833875</v>
+        <v>6833857</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,10 +7059,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469112</v>
+        <v>121469135</v>
       </c>
       <c r="B64" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,21 +7075,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7109,10 +7099,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483408</v>
+        <v>483205</v>
       </c>
       <c r="R64" t="n">
-        <v>6833852</v>
+        <v>6834490</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7161,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469145</v>
+        <v>121469119</v>
       </c>
       <c r="B65" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7177,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483387</v>
+        <v>483265</v>
       </c>
       <c r="R65" t="n">
-        <v>6833994</v>
+        <v>6834572</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469108</v>
+        <v>121469340</v>
       </c>
       <c r="B66" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7279,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7303,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>482925</v>
+        <v>483211</v>
       </c>
       <c r="R66" t="n">
-        <v>6833910</v>
+        <v>6834254</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7365,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469157</v>
+        <v>121469337</v>
       </c>
       <c r="B67" t="n">
-        <v>78000</v>
+        <v>79234</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7381,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483143</v>
+        <v>483413</v>
       </c>
       <c r="R67" t="n">
-        <v>6833875</v>
+        <v>6834033</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469143</v>
+        <v>121469120</v>
       </c>
       <c r="B68" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483038</v>
+        <v>483153</v>
       </c>
       <c r="R68" t="n">
-        <v>6834461</v>
+        <v>6834504</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469337</v>
+        <v>121465664</v>
       </c>
       <c r="B69" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7595,37 +7585,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sundsjöberget, Dlr</t>
+          <t>Lilla Sundsjöberget, Lilla Sundsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483413</v>
+        <v>483498</v>
       </c>
       <c r="R69" t="n">
-        <v>6834033</v>
+        <v>6834031</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7669,19 +7659,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469130</v>
+        <v>121469133</v>
       </c>
       <c r="B70" t="n">
         <v>78616</v>
@@ -7721,10 +7711,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483307</v>
+        <v>483241</v>
       </c>
       <c r="R70" t="n">
-        <v>6833983</v>
+        <v>6834112</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,10 +7773,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469124</v>
+        <v>121469131</v>
       </c>
       <c r="B71" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7799,21 +7789,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7823,10 +7813,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>482865</v>
+        <v>483261</v>
       </c>
       <c r="R71" t="n">
-        <v>6834254</v>
+        <v>6834030</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469338</v>
+        <v>121469107</v>
       </c>
       <c r="B72" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7891,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483246</v>
+        <v>482865</v>
       </c>
       <c r="R72" t="n">
-        <v>6834122</v>
+        <v>6834255</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469101</v>
+        <v>121469139</v>
       </c>
       <c r="B73" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +7993,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8017,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483168</v>
+        <v>483149</v>
       </c>
       <c r="R73" t="n">
-        <v>6834333</v>
+        <v>6834501</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8079,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469107</v>
+        <v>121469338</v>
       </c>
       <c r="B74" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8105,21 +8095,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8129,10 +8119,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>482865</v>
+        <v>483246</v>
       </c>
       <c r="R74" t="n">
-        <v>6834255</v>
+        <v>6834122</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,10 +8181,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469150</v>
+        <v>121469100</v>
       </c>
       <c r="B75" t="n">
-        <v>78261</v>
+        <v>78353</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8197,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="i